--- a/vignettes/vignette-2/distribution_plot_data.xlsx
+++ b/vignettes/vignette-2/distribution_plot_data.xlsx
@@ -6826,7 +6826,7 @@
         <v>0</v>
       </c>
       <c r="C493" t="n">
-        <v>-0.907012</v>
+        <v>-0.485188</v>
       </c>
     </row>
     <row r="494">
@@ -6839,7 +6839,7 @@
         <v>1</v>
       </c>
       <c r="C494" t="n">
-        <v>-0.697536</v>
+        <v>-0.405921</v>
       </c>
     </row>
     <row r="495">
@@ -6852,7 +6852,7 @@
         <v>2</v>
       </c>
       <c r="C495" t="n">
-        <v>-0.366779</v>
+        <v>-0.296256</v>
       </c>
     </row>
     <row r="496">
@@ -6865,7 +6865,7 @@
         <v>3</v>
       </c>
       <c r="C496" t="n">
-        <v>-0.27801</v>
+        <v>-0.282125</v>
       </c>
     </row>
     <row r="497">
@@ -6878,7 +6878,7 @@
         <v>4</v>
       </c>
       <c r="C497" t="n">
-        <v>-0.227564</v>
+        <v>-0.278791</v>
       </c>
     </row>
     <row r="498">
@@ -6891,7 +6891,7 @@
         <v>5</v>
       </c>
       <c r="C498" t="n">
-        <v>-0.226816</v>
+        <v>-0.208697</v>
       </c>
     </row>
     <row r="499">
@@ -6904,7 +6904,7 @@
         <v>6</v>
       </c>
       <c r="C499" t="n">
-        <v>-0.200417</v>
+        <v>-0.193737</v>
       </c>
     </row>
     <row r="500">
@@ -6917,7 +6917,7 @@
         <v>7</v>
       </c>
       <c r="C500" t="n">
-        <v>-0.184227</v>
+        <v>-0.186286</v>
       </c>
     </row>
     <row r="501">
@@ -6930,7 +6930,7 @@
         <v>8</v>
       </c>
       <c r="C501" t="n">
-        <v>-0.148967</v>
+        <v>-0.142237</v>
       </c>
     </row>
     <row r="502">
@@ -6943,7 +6943,7 @@
         <v>9</v>
       </c>
       <c r="C502" t="n">
-        <v>-0.137124</v>
+        <v>-0.130147</v>
       </c>
     </row>
     <row r="503">
@@ -6956,7 +6956,7 @@
         <v>10</v>
       </c>
       <c r="C503" t="n">
-        <v>-0.129207</v>
+        <v>-0.129419</v>
       </c>
     </row>
     <row r="504">
@@ -6969,7 +6969,7 @@
         <v>11</v>
       </c>
       <c r="C504" t="n">
-        <v>-0.126317</v>
+        <v>-0.125679</v>
       </c>
     </row>
     <row r="505">
@@ -6982,7 +6982,7 @@
         <v>12</v>
       </c>
       <c r="C505" t="n">
-        <v>-0.124025</v>
+        <v>-0.115116</v>
       </c>
     </row>
     <row r="506">
@@ -6995,7 +6995,7 @@
         <v>13</v>
       </c>
       <c r="C506" t="n">
-        <v>-0.115079</v>
+        <v>-0.111262</v>
       </c>
     </row>
     <row r="507">
@@ -7008,7 +7008,7 @@
         <v>14</v>
       </c>
       <c r="C507" t="n">
-        <v>-0.109823</v>
+        <v>-0.109501</v>
       </c>
     </row>
     <row r="508">
@@ -7021,7 +7021,7 @@
         <v>15</v>
       </c>
       <c r="C508" t="n">
-        <v>-0.109421</v>
+        <v>-0.108352</v>
       </c>
     </row>
     <row r="509">
@@ -7034,7 +7034,7 @@
         <v>16</v>
       </c>
       <c r="C509" t="n">
-        <v>-0.092621</v>
+        <v>-0.100999</v>
       </c>
     </row>
     <row r="510">
@@ -7047,7 +7047,7 @@
         <v>17</v>
       </c>
       <c r="C510" t="n">
-        <v>-0.09245100000000001</v>
+        <v>-0.098608</v>
       </c>
     </row>
     <row r="511">
@@ -7060,7 +7060,7 @@
         <v>18</v>
       </c>
       <c r="C511" t="n">
-        <v>-0.091445</v>
+        <v>-0.097909</v>
       </c>
     </row>
     <row r="512">
@@ -7073,7 +7073,7 @@
         <v>19</v>
       </c>
       <c r="C512" t="n">
-        <v>-0.086268</v>
+        <v>-0.097349</v>
       </c>
     </row>
     <row r="513">
@@ -7086,7 +7086,7 @@
         <v>20</v>
       </c>
       <c r="C513" t="n">
-        <v>-0.084402</v>
+        <v>-0.09714299999999999</v>
       </c>
     </row>
     <row r="514">
@@ -7099,7 +7099,7 @@
         <v>21</v>
       </c>
       <c r="C514" t="n">
-        <v>-0.082292</v>
+        <v>-0.095335</v>
       </c>
     </row>
     <row r="515">
@@ -7112,7 +7112,7 @@
         <v>22</v>
       </c>
       <c r="C515" t="n">
-        <v>-0.080275</v>
+        <v>-0.089602</v>
       </c>
     </row>
     <row r="516">
@@ -7125,7 +7125,7 @@
         <v>23</v>
       </c>
       <c r="C516" t="n">
-        <v>-0.077432</v>
+        <v>-0.088532</v>
       </c>
     </row>
     <row r="517">
@@ -7138,7 +7138,7 @@
         <v>24</v>
       </c>
       <c r="C517" t="n">
-        <v>-0.07203</v>
+        <v>-0.088357</v>
       </c>
     </row>
     <row r="518">
@@ -7151,7 +7151,7 @@
         <v>25</v>
       </c>
       <c r="C518" t="n">
-        <v>-0.071702</v>
+        <v>-0.085114</v>
       </c>
     </row>
     <row r="519">
@@ -7164,7 +7164,7 @@
         <v>26</v>
       </c>
       <c r="C519" t="n">
-        <v>-0.069801</v>
+        <v>-0.083666</v>
       </c>
     </row>
     <row r="520">
@@ -7177,7 +7177,7 @@
         <v>27</v>
       </c>
       <c r="C520" t="n">
-        <v>-0.067707</v>
+        <v>-0.082257</v>
       </c>
     </row>
     <row r="521">
@@ -7190,7 +7190,7 @@
         <v>28</v>
       </c>
       <c r="C521" t="n">
-        <v>-0.06688</v>
+        <v>-0.08093400000000001</v>
       </c>
     </row>
     <row r="522">
@@ -7203,7 +7203,7 @@
         <v>29</v>
       </c>
       <c r="C522" t="n">
-        <v>-0.066207</v>
+        <v>-0.078884</v>
       </c>
     </row>
     <row r="523">
@@ -7216,7 +7216,7 @@
         <v>30</v>
       </c>
       <c r="C523" t="n">
-        <v>-0.065359</v>
+        <v>-0.07874</v>
       </c>
     </row>
     <row r="524">
@@ -7229,7 +7229,7 @@
         <v>31</v>
       </c>
       <c r="C524" t="n">
-        <v>-0.06526999999999999</v>
+        <v>-0.078732</v>
       </c>
     </row>
     <row r="525">
@@ -7242,7 +7242,7 @@
         <v>32</v>
       </c>
       <c r="C525" t="n">
-        <v>-0.064543</v>
+        <v>-0.076514</v>
       </c>
     </row>
     <row r="526">
@@ -7255,7 +7255,7 @@
         <v>33</v>
       </c>
       <c r="C526" t="n">
-        <v>-0.061397</v>
+        <v>-0.076181</v>
       </c>
     </row>
     <row r="527">
@@ -7268,7 +7268,7 @@
         <v>34</v>
       </c>
       <c r="C527" t="n">
-        <v>-0.060229</v>
+        <v>-0.075714</v>
       </c>
     </row>
     <row r="528">
@@ -7281,7 +7281,7 @@
         <v>35</v>
       </c>
       <c r="C528" t="n">
-        <v>-0.059977</v>
+        <v>-0.07489700000000001</v>
       </c>
     </row>
     <row r="529">
@@ -7294,7 +7294,7 @@
         <v>36</v>
       </c>
       <c r="C529" t="n">
-        <v>-0.057594</v>
+        <v>-0.072796</v>
       </c>
     </row>
     <row r="530">
@@ -7307,7 +7307,7 @@
         <v>37</v>
       </c>
       <c r="C530" t="n">
-        <v>-0.057425</v>
+        <v>-0.071711</v>
       </c>
     </row>
     <row r="531">
@@ -7320,7 +7320,7 @@
         <v>38</v>
       </c>
       <c r="C531" t="n">
-        <v>-0.056003</v>
+        <v>-0.069858</v>
       </c>
     </row>
     <row r="532">
@@ -7333,7 +7333,7 @@
         <v>39</v>
       </c>
       <c r="C532" t="n">
-        <v>-0.055909</v>
+        <v>-0.06890400000000001</v>
       </c>
     </row>
     <row r="533">
@@ -7346,7 +7346,7 @@
         <v>40</v>
       </c>
       <c r="C533" t="n">
-        <v>-0.054275</v>
+        <v>-0.06698</v>
       </c>
     </row>
     <row r="534">
@@ -7359,7 +7359,7 @@
         <v>41</v>
       </c>
       <c r="C534" t="n">
-        <v>-0.054135</v>
+        <v>-0.063346</v>
       </c>
     </row>
     <row r="535">
@@ -7372,7 +7372,7 @@
         <v>42</v>
       </c>
       <c r="C535" t="n">
-        <v>-0.053788</v>
+        <v>-0.06293</v>
       </c>
     </row>
     <row r="536">
@@ -7385,7 +7385,7 @@
         <v>43</v>
       </c>
       <c r="C536" t="n">
-        <v>-0.053447</v>
+        <v>-0.061689</v>
       </c>
     </row>
     <row r="537">
@@ -7398,7 +7398,7 @@
         <v>44</v>
       </c>
       <c r="C537" t="n">
-        <v>-0.052083</v>
+        <v>-0.061057</v>
       </c>
     </row>
     <row r="538">
@@ -7411,7 +7411,7 @@
         <v>45</v>
       </c>
       <c r="C538" t="n">
-        <v>-0.049453</v>
+        <v>-0.058051</v>
       </c>
     </row>
     <row r="539">
@@ -7424,7 +7424,7 @@
         <v>46</v>
       </c>
       <c r="C539" t="n">
-        <v>-0.048188</v>
+        <v>-0.057773</v>
       </c>
     </row>
     <row r="540">
@@ -7437,7 +7437,7 @@
         <v>47</v>
       </c>
       <c r="C540" t="n">
-        <v>-0.046171</v>
+        <v>-0.057545</v>
       </c>
     </row>
     <row r="541">
@@ -7450,7 +7450,7 @@
         <v>48</v>
       </c>
       <c r="C541" t="n">
-        <v>-0.0461</v>
+        <v>-0.057373</v>
       </c>
     </row>
     <row r="542">
@@ -7463,7 +7463,7 @@
         <v>49</v>
       </c>
       <c r="C542" t="n">
-        <v>-0.045946</v>
+        <v>-0.056219</v>
       </c>
     </row>
     <row r="543">
@@ -7476,7 +7476,7 @@
         <v>50</v>
       </c>
       <c r="C543" t="n">
-        <v>-0.045864</v>
+        <v>-0.056039</v>
       </c>
     </row>
     <row r="544">
@@ -7489,7 +7489,7 @@
         <v>51</v>
       </c>
       <c r="C544" t="n">
-        <v>-0.044357</v>
+        <v>-0.056001</v>
       </c>
     </row>
     <row r="545">
@@ -7502,7 +7502,7 @@
         <v>52</v>
       </c>
       <c r="C545" t="n">
-        <v>-0.04432</v>
+        <v>-0.055813</v>
       </c>
     </row>
     <row r="546">
@@ -7515,7 +7515,7 @@
         <v>53</v>
       </c>
       <c r="C546" t="n">
-        <v>-0.044307</v>
+        <v>-0.053767</v>
       </c>
     </row>
     <row r="547">
@@ -7528,7 +7528,7 @@
         <v>54</v>
       </c>
       <c r="C547" t="n">
-        <v>-0.042428</v>
+        <v>-0.053504</v>
       </c>
     </row>
     <row r="548">
@@ -7541,7 +7541,7 @@
         <v>55</v>
       </c>
       <c r="C548" t="n">
-        <v>-0.041386</v>
+        <v>-0.052145</v>
       </c>
     </row>
     <row r="549">
@@ -7554,7 +7554,7 @@
         <v>56</v>
       </c>
       <c r="C549" t="n">
-        <v>-0.040872</v>
+        <v>-0.05177</v>
       </c>
     </row>
     <row r="550">
@@ -7567,7 +7567,7 @@
         <v>57</v>
       </c>
       <c r="C550" t="n">
-        <v>-0.040586</v>
+        <v>-0.050989</v>
       </c>
     </row>
     <row r="551">
@@ -7580,7 +7580,7 @@
         <v>58</v>
       </c>
       <c r="C551" t="n">
-        <v>-0.039587</v>
+        <v>-0.050921</v>
       </c>
     </row>
     <row r="552">
@@ -7593,7 +7593,7 @@
         <v>59</v>
       </c>
       <c r="C552" t="n">
-        <v>-0.037197</v>
+        <v>-0.050524</v>
       </c>
     </row>
     <row r="553">
@@ -7606,7 +7606,7 @@
         <v>60</v>
       </c>
       <c r="C553" t="n">
-        <v>-0.036916</v>
+        <v>-0.049787</v>
       </c>
     </row>
     <row r="554">
@@ -7619,7 +7619,7 @@
         <v>61</v>
       </c>
       <c r="C554" t="n">
-        <v>-0.036666</v>
+        <v>-0.049346</v>
       </c>
     </row>
     <row r="555">
@@ -7632,7 +7632,7 @@
         <v>62</v>
       </c>
       <c r="C555" t="n">
-        <v>-0.036395</v>
+        <v>-0.048622</v>
       </c>
     </row>
     <row r="556">
@@ -7645,7 +7645,7 @@
         <v>63</v>
       </c>
       <c r="C556" t="n">
-        <v>-0.035764</v>
+        <v>-0.047956</v>
       </c>
     </row>
     <row r="557">
@@ -7658,7 +7658,7 @@
         <v>64</v>
       </c>
       <c r="C557" t="n">
-        <v>-0.035697</v>
+        <v>-0.047106</v>
       </c>
     </row>
     <row r="558">
@@ -7671,7 +7671,7 @@
         <v>65</v>
       </c>
       <c r="C558" t="n">
-        <v>-0.035672</v>
+        <v>-0.046621</v>
       </c>
     </row>
     <row r="559">
@@ -7684,7 +7684,7 @@
         <v>66</v>
       </c>
       <c r="C559" t="n">
-        <v>-0.035531</v>
+        <v>-0.045649</v>
       </c>
     </row>
     <row r="560">
@@ -7697,7 +7697,7 @@
         <v>67</v>
       </c>
       <c r="C560" t="n">
-        <v>-0.03541</v>
+        <v>-0.045536</v>
       </c>
     </row>
     <row r="561">
@@ -7710,7 +7710,7 @@
         <v>68</v>
       </c>
       <c r="C561" t="n">
-        <v>-0.034263</v>
+        <v>-0.045272</v>
       </c>
     </row>
     <row r="562">
@@ -7723,7 +7723,7 @@
         <v>69</v>
       </c>
       <c r="C562" t="n">
-        <v>-0.033367</v>
+        <v>-0.044511</v>
       </c>
     </row>
     <row r="563">
@@ -7736,7 +7736,7 @@
         <v>70</v>
       </c>
       <c r="C563" t="n">
-        <v>-0.033338</v>
+        <v>-0.044495</v>
       </c>
     </row>
     <row r="564">
@@ -7749,7 +7749,7 @@
         <v>71</v>
       </c>
       <c r="C564" t="n">
-        <v>-0.03297</v>
+        <v>-0.044367</v>
       </c>
     </row>
     <row r="565">
@@ -7762,7 +7762,7 @@
         <v>72</v>
       </c>
       <c r="C565" t="n">
-        <v>-0.032619</v>
+        <v>-0.04436</v>
       </c>
     </row>
     <row r="566">
@@ -7775,7 +7775,7 @@
         <v>73</v>
       </c>
       <c r="C566" t="n">
-        <v>-0.032383</v>
+        <v>-0.043757</v>
       </c>
     </row>
     <row r="567">
@@ -7788,7 +7788,7 @@
         <v>74</v>
       </c>
       <c r="C567" t="n">
-        <v>-0.032097</v>
+        <v>-0.043437</v>
       </c>
     </row>
     <row r="568">
@@ -7801,7 +7801,7 @@
         <v>75</v>
       </c>
       <c r="C568" t="n">
-        <v>-0.032038</v>
+        <v>-0.043022</v>
       </c>
     </row>
     <row r="569">
@@ -7814,7 +7814,7 @@
         <v>76</v>
       </c>
       <c r="C569" t="n">
-        <v>-0.031732</v>
+        <v>-0.042886</v>
       </c>
     </row>
     <row r="570">
@@ -7827,7 +7827,7 @@
         <v>77</v>
       </c>
       <c r="C570" t="n">
-        <v>-0.029714</v>
+        <v>-0.041925</v>
       </c>
     </row>
     <row r="571">
@@ -7840,7 +7840,7 @@
         <v>78</v>
       </c>
       <c r="C571" t="n">
-        <v>-0.029638</v>
+        <v>-0.041643</v>
       </c>
     </row>
     <row r="572">
@@ -7853,7 +7853,7 @@
         <v>79</v>
       </c>
       <c r="C572" t="n">
-        <v>-0.029353</v>
+        <v>-0.041609</v>
       </c>
     </row>
     <row r="573">
@@ -7866,7 +7866,7 @@
         <v>80</v>
       </c>
       <c r="C573" t="n">
-        <v>-0.02883</v>
+        <v>-0.041031</v>
       </c>
     </row>
     <row r="574">
@@ -7879,7 +7879,7 @@
         <v>81</v>
       </c>
       <c r="C574" t="n">
-        <v>-0.028758</v>
+        <v>-0.04098</v>
       </c>
     </row>
     <row r="575">
@@ -7892,7 +7892,7 @@
         <v>82</v>
       </c>
       <c r="C575" t="n">
-        <v>-0.028724</v>
+        <v>-0.040763</v>
       </c>
     </row>
     <row r="576">
@@ -7905,7 +7905,7 @@
         <v>83</v>
       </c>
       <c r="C576" t="n">
-        <v>-0.027316</v>
+        <v>-0.04023</v>
       </c>
     </row>
     <row r="577">
@@ -7918,7 +7918,7 @@
         <v>84</v>
       </c>
       <c r="C577" t="n">
-        <v>-0.027222</v>
+        <v>-0.040177</v>
       </c>
     </row>
     <row r="578">
@@ -7931,7 +7931,7 @@
         <v>85</v>
       </c>
       <c r="C578" t="n">
-        <v>-0.026841</v>
+        <v>-0.039924</v>
       </c>
     </row>
     <row r="579">
@@ -7944,7 +7944,7 @@
         <v>86</v>
       </c>
       <c r="C579" t="n">
-        <v>-0.026835</v>
+        <v>-0.039726</v>
       </c>
     </row>
     <row r="580">
@@ -7957,7 +7957,7 @@
         <v>87</v>
       </c>
       <c r="C580" t="n">
-        <v>-0.02681</v>
+        <v>-0.038437</v>
       </c>
     </row>
     <row r="581">
@@ -7970,7 +7970,7 @@
         <v>88</v>
       </c>
       <c r="C581" t="n">
-        <v>-0.02676</v>
+        <v>-0.037966</v>
       </c>
     </row>
     <row r="582">
@@ -7983,7 +7983,7 @@
         <v>89</v>
       </c>
       <c r="C582" t="n">
-        <v>-0.026591</v>
+        <v>-0.037583</v>
       </c>
     </row>
     <row r="583">
@@ -7996,7 +7996,7 @@
         <v>90</v>
       </c>
       <c r="C583" t="n">
-        <v>-0.026566</v>
+        <v>-0.037355</v>
       </c>
     </row>
     <row r="584">
@@ -8009,7 +8009,7 @@
         <v>91</v>
       </c>
       <c r="C584" t="n">
-        <v>-0.026542</v>
+        <v>-0.036721</v>
       </c>
     </row>
     <row r="585">
@@ -8022,7 +8022,7 @@
         <v>92</v>
       </c>
       <c r="C585" t="n">
-        <v>-0.026494</v>
+        <v>-0.036633</v>
       </c>
     </row>
     <row r="586">
@@ -8035,7 +8035,7 @@
         <v>93</v>
       </c>
       <c r="C586" t="n">
-        <v>-0.02649</v>
+        <v>-0.036327</v>
       </c>
     </row>
     <row r="587">
@@ -8048,7 +8048,7 @@
         <v>94</v>
       </c>
       <c r="C587" t="n">
-        <v>-0.026115</v>
+        <v>-0.036275</v>
       </c>
     </row>
     <row r="588">
@@ -8061,7 +8061,7 @@
         <v>95</v>
       </c>
       <c r="C588" t="n">
-        <v>-0.026055</v>
+        <v>-0.035928</v>
       </c>
     </row>
     <row r="589">
@@ -8074,7 +8074,7 @@
         <v>96</v>
       </c>
       <c r="C589" t="n">
-        <v>-0.02535</v>
+        <v>-0.035142</v>
       </c>
     </row>
     <row r="590">
@@ -8087,7 +8087,7 @@
         <v>97</v>
       </c>
       <c r="C590" t="n">
-        <v>-0.023766</v>
+        <v>-0.033264</v>
       </c>
     </row>
     <row r="591">
@@ -8100,7 +8100,7 @@
         <v>98</v>
       </c>
       <c r="C591" t="n">
-        <v>-0.023287</v>
+        <v>-0.032956</v>
       </c>
     </row>
     <row r="592">
@@ -8113,7 +8113,7 @@
         <v>99</v>
       </c>
       <c r="C592" t="n">
-        <v>-0.022985</v>
+        <v>-0.032731</v>
       </c>
     </row>
     <row r="593">
@@ -8126,7 +8126,7 @@
         <v>100</v>
       </c>
       <c r="C593" t="n">
-        <v>-0.022848</v>
+        <v>-0.032609</v>
       </c>
     </row>
     <row r="594">
@@ -8139,7 +8139,7 @@
         <v>101</v>
       </c>
       <c r="C594" t="n">
-        <v>-0.02278</v>
+        <v>-0.031382</v>
       </c>
     </row>
     <row r="595">
@@ -8152,7 +8152,7 @@
         <v>102</v>
       </c>
       <c r="C595" t="n">
-        <v>-0.022547</v>
+        <v>-0.030331</v>
       </c>
     </row>
     <row r="596">
@@ -8165,7 +8165,7 @@
         <v>103</v>
       </c>
       <c r="C596" t="n">
-        <v>-0.022509</v>
+        <v>-0.029637</v>
       </c>
     </row>
     <row r="597">
@@ -8178,7 +8178,7 @@
         <v>104</v>
       </c>
       <c r="C597" t="n">
-        <v>-0.022415</v>
+        <v>-0.028995</v>
       </c>
     </row>
     <row r="598">
@@ -8191,7 +8191,7 @@
         <v>105</v>
       </c>
       <c r="C598" t="n">
-        <v>-0.021931</v>
+        <v>-0.028859</v>
       </c>
     </row>
     <row r="599">
@@ -8204,7 +8204,7 @@
         <v>106</v>
       </c>
       <c r="C599" t="n">
-        <v>-0.021817</v>
+        <v>-0.028841</v>
       </c>
     </row>
     <row r="600">
@@ -8217,7 +8217,7 @@
         <v>107</v>
       </c>
       <c r="C600" t="n">
-        <v>-0.02173</v>
+        <v>-0.028687</v>
       </c>
     </row>
     <row r="601">
@@ -8230,7 +8230,7 @@
         <v>108</v>
       </c>
       <c r="C601" t="n">
-        <v>-0.021663</v>
+        <v>-0.028676</v>
       </c>
     </row>
     <row r="602">
@@ -8243,7 +8243,7 @@
         <v>109</v>
       </c>
       <c r="C602" t="n">
-        <v>-0.02161</v>
+        <v>-0.02852</v>
       </c>
     </row>
     <row r="603">
@@ -8256,7 +8256,7 @@
         <v>110</v>
       </c>
       <c r="C603" t="n">
-        <v>-0.02129</v>
+        <v>-0.027746</v>
       </c>
     </row>
     <row r="604">
@@ -8269,7 +8269,7 @@
         <v>111</v>
       </c>
       <c r="C604" t="n">
-        <v>-0.0212</v>
+        <v>-0.027089</v>
       </c>
     </row>
     <row r="605">
@@ -8282,7 +8282,7 @@
         <v>112</v>
       </c>
       <c r="C605" t="n">
-        <v>-0.021046</v>
+        <v>-0.026954</v>
       </c>
     </row>
     <row r="606">
@@ -8295,7 +8295,7 @@
         <v>113</v>
       </c>
       <c r="C606" t="n">
-        <v>-0.020914</v>
+        <v>-0.026479</v>
       </c>
     </row>
     <row r="607">
@@ -8308,7 +8308,7 @@
         <v>114</v>
       </c>
       <c r="C607" t="n">
-        <v>-0.02066</v>
+        <v>-0.026085</v>
       </c>
     </row>
     <row r="608">
@@ -8321,7 +8321,7 @@
         <v>115</v>
       </c>
       <c r="C608" t="n">
-        <v>-0.020438</v>
+        <v>-0.025419</v>
       </c>
     </row>
     <row r="609">
@@ -8334,7 +8334,7 @@
         <v>116</v>
       </c>
       <c r="C609" t="n">
-        <v>-0.020088</v>
+        <v>-0.025053</v>
       </c>
     </row>
     <row r="610">
@@ -8347,7 +8347,7 @@
         <v>117</v>
       </c>
       <c r="C610" t="n">
-        <v>-0.019799</v>
+        <v>-0.025011</v>
       </c>
     </row>
     <row r="611">
@@ -8360,7 +8360,7 @@
         <v>118</v>
       </c>
       <c r="C611" t="n">
-        <v>-0.01978</v>
+        <v>-0.024822</v>
       </c>
     </row>
     <row r="612">
@@ -8373,7 +8373,7 @@
         <v>119</v>
       </c>
       <c r="C612" t="n">
-        <v>-0.01965</v>
+        <v>-0.02434</v>
       </c>
     </row>
     <row r="613">
@@ -8386,7 +8386,7 @@
         <v>120</v>
       </c>
       <c r="C613" t="n">
-        <v>-0.019171</v>
+        <v>-0.024053</v>
       </c>
     </row>
     <row r="614">
@@ -8399,7 +8399,7 @@
         <v>121</v>
       </c>
       <c r="C614" t="n">
-        <v>-0.01908</v>
+        <v>-0.023863</v>
       </c>
     </row>
     <row r="615">
@@ -8412,7 +8412,7 @@
         <v>122</v>
       </c>
       <c r="C615" t="n">
-        <v>-0.018948</v>
+        <v>-0.023663</v>
       </c>
     </row>
     <row r="616">
@@ -8425,7 +8425,7 @@
         <v>123</v>
       </c>
       <c r="C616" t="n">
-        <v>-0.018242</v>
+        <v>-0.023183</v>
       </c>
     </row>
     <row r="617">
@@ -8438,7 +8438,7 @@
         <v>124</v>
       </c>
       <c r="C617" t="n">
-        <v>-0.017976</v>
+        <v>-0.02297</v>
       </c>
     </row>
     <row r="618">
@@ -8451,7 +8451,7 @@
         <v>125</v>
       </c>
       <c r="C618" t="n">
-        <v>-0.017953</v>
+        <v>-0.022821</v>
       </c>
     </row>
     <row r="619">
@@ -8464,7 +8464,7 @@
         <v>126</v>
       </c>
       <c r="C619" t="n">
-        <v>-0.017607</v>
+        <v>-0.022576</v>
       </c>
     </row>
     <row r="620">
@@ -8477,7 +8477,7 @@
         <v>127</v>
       </c>
       <c r="C620" t="n">
-        <v>-0.017163</v>
+        <v>-0.022352</v>
       </c>
     </row>
     <row r="621">
@@ -8490,7 +8490,7 @@
         <v>128</v>
       </c>
       <c r="C621" t="n">
-        <v>-0.017156</v>
+        <v>-0.022057</v>
       </c>
     </row>
     <row r="622">
@@ -8503,7 +8503,7 @@
         <v>129</v>
       </c>
       <c r="C622" t="n">
-        <v>-0.017105</v>
+        <v>-0.021913</v>
       </c>
     </row>
     <row r="623">
@@ -8516,7 +8516,7 @@
         <v>130</v>
       </c>
       <c r="C623" t="n">
-        <v>-0.016952</v>
+        <v>-0.021497</v>
       </c>
     </row>
     <row r="624">
@@ -8529,7 +8529,7 @@
         <v>131</v>
       </c>
       <c r="C624" t="n">
-        <v>-0.016569</v>
+        <v>-0.019864</v>
       </c>
     </row>
     <row r="625">
@@ -8542,7 +8542,7 @@
         <v>132</v>
       </c>
       <c r="C625" t="n">
-        <v>-0.016517</v>
+        <v>-0.019242</v>
       </c>
     </row>
     <row r="626">
@@ -8555,7 +8555,7 @@
         <v>133</v>
       </c>
       <c r="C626" t="n">
-        <v>-0.016474</v>
+        <v>-0.018877</v>
       </c>
     </row>
     <row r="627">
@@ -8568,7 +8568,7 @@
         <v>134</v>
       </c>
       <c r="C627" t="n">
-        <v>-0.01634</v>
+        <v>-0.017826</v>
       </c>
     </row>
     <row r="628">
@@ -8581,7 +8581,7 @@
         <v>135</v>
       </c>
       <c r="C628" t="n">
-        <v>-0.015854</v>
+        <v>-0.017757</v>
       </c>
     </row>
     <row r="629">
@@ -8594,7 +8594,7 @@
         <v>136</v>
       </c>
       <c r="C629" t="n">
-        <v>-0.01547</v>
+        <v>-0.017123</v>
       </c>
     </row>
     <row r="630">
@@ -8607,7 +8607,7 @@
         <v>137</v>
       </c>
       <c r="C630" t="n">
-        <v>-0.015173</v>
+        <v>-0.01711</v>
       </c>
     </row>
     <row r="631">
@@ -8620,7 +8620,7 @@
         <v>138</v>
       </c>
       <c r="C631" t="n">
-        <v>-0.015124</v>
+        <v>-0.017033</v>
       </c>
     </row>
     <row r="632">
@@ -8633,7 +8633,7 @@
         <v>139</v>
       </c>
       <c r="C632" t="n">
-        <v>-0.014944</v>
+        <v>-0.01691</v>
       </c>
     </row>
     <row r="633">
@@ -8646,7 +8646,7 @@
         <v>140</v>
       </c>
       <c r="C633" t="n">
-        <v>-0.014916</v>
+        <v>-0.016485</v>
       </c>
     </row>
     <row r="634">
@@ -8659,7 +8659,7 @@
         <v>141</v>
       </c>
       <c r="C634" t="n">
-        <v>-0.014639</v>
+        <v>-0.016391</v>
       </c>
     </row>
     <row r="635">
@@ -8672,7 +8672,7 @@
         <v>142</v>
       </c>
       <c r="C635" t="n">
-        <v>-0.014562</v>
+        <v>-0.01623</v>
       </c>
     </row>
     <row r="636">
@@ -8685,7 +8685,7 @@
         <v>143</v>
       </c>
       <c r="C636" t="n">
-        <v>-0.014336</v>
+        <v>-0.016185</v>
       </c>
     </row>
     <row r="637">
@@ -8698,7 +8698,7 @@
         <v>144</v>
       </c>
       <c r="C637" t="n">
-        <v>-0.014272</v>
+        <v>-0.01618</v>
       </c>
     </row>
     <row r="638">
@@ -8711,7 +8711,7 @@
         <v>145</v>
       </c>
       <c r="C638" t="n">
-        <v>-0.014139</v>
+        <v>-0.015914</v>
       </c>
     </row>
     <row r="639">
@@ -8724,7 +8724,7 @@
         <v>146</v>
       </c>
       <c r="C639" t="n">
-        <v>-0.013948</v>
+        <v>-0.015745</v>
       </c>
     </row>
     <row r="640">
@@ -8737,7 +8737,7 @@
         <v>147</v>
       </c>
       <c r="C640" t="n">
-        <v>-0.013749</v>
+        <v>-0.015676</v>
       </c>
     </row>
     <row r="641">
@@ -8750,7 +8750,7 @@
         <v>148</v>
       </c>
       <c r="C641" t="n">
-        <v>-0.013742</v>
+        <v>-0.015623</v>
       </c>
     </row>
     <row r="642">
@@ -8763,7 +8763,7 @@
         <v>149</v>
       </c>
       <c r="C642" t="n">
-        <v>-0.013427</v>
+        <v>-0.01558</v>
       </c>
     </row>
     <row r="643">
@@ -8776,7 +8776,7 @@
         <v>150</v>
       </c>
       <c r="C643" t="n">
-        <v>-0.012765</v>
+        <v>-0.015527</v>
       </c>
     </row>
     <row r="644">
@@ -8789,7 +8789,7 @@
         <v>151</v>
       </c>
       <c r="C644" t="n">
-        <v>-0.012619</v>
+        <v>-0.015427</v>
       </c>
     </row>
     <row r="645">
@@ -8802,7 +8802,7 @@
         <v>152</v>
       </c>
       <c r="C645" t="n">
-        <v>-0.012319</v>
+        <v>-0.01526</v>
       </c>
     </row>
     <row r="646">
@@ -8815,7 +8815,7 @@
         <v>153</v>
       </c>
       <c r="C646" t="n">
-        <v>-0.012215</v>
+        <v>-0.014952</v>
       </c>
     </row>
     <row r="647">
@@ -8828,7 +8828,7 @@
         <v>154</v>
       </c>
       <c r="C647" t="n">
-        <v>-0.011575</v>
+        <v>-0.013828</v>
       </c>
     </row>
     <row r="648">
@@ -8841,7 +8841,7 @@
         <v>155</v>
       </c>
       <c r="C648" t="n">
-        <v>-0.011174</v>
+        <v>-0.013655</v>
       </c>
     </row>
     <row r="649">
@@ -8854,7 +8854,7 @@
         <v>156</v>
       </c>
       <c r="C649" t="n">
-        <v>-0.010962</v>
+        <v>-0.013533</v>
       </c>
     </row>
     <row r="650">
@@ -8867,7 +8867,7 @@
         <v>157</v>
       </c>
       <c r="C650" t="n">
-        <v>-0.010714</v>
+        <v>-0.013421</v>
       </c>
     </row>
     <row r="651">
@@ -8880,7 +8880,7 @@
         <v>158</v>
       </c>
       <c r="C651" t="n">
-        <v>-0.010578</v>
+        <v>-0.013358</v>
       </c>
     </row>
     <row r="652">
@@ -8893,7 +8893,7 @@
         <v>159</v>
       </c>
       <c r="C652" t="n">
-        <v>-0.010286</v>
+        <v>-0.012983</v>
       </c>
     </row>
     <row r="653">
@@ -8906,7 +8906,7 @@
         <v>160</v>
       </c>
       <c r="C653" t="n">
-        <v>-0.010149</v>
+        <v>-0.012507</v>
       </c>
     </row>
     <row r="654">
@@ -8919,7 +8919,7 @@
         <v>161</v>
       </c>
       <c r="C654" t="n">
-        <v>-0.009815000000000001</v>
+        <v>-0.012033</v>
       </c>
     </row>
     <row r="655">
@@ -8932,7 +8932,7 @@
         <v>162</v>
       </c>
       <c r="C655" t="n">
-        <v>-0.009783999999999999</v>
+        <v>-0.011499</v>
       </c>
     </row>
     <row r="656">
@@ -8945,7 +8945,7 @@
         <v>163</v>
       </c>
       <c r="C656" t="n">
-        <v>-0.009762</v>
+        <v>-0.011485</v>
       </c>
     </row>
     <row r="657">
@@ -8958,7 +8958,7 @@
         <v>164</v>
       </c>
       <c r="C657" t="n">
-        <v>-0.009729</v>
+        <v>-0.011262</v>
       </c>
     </row>
     <row r="658">
@@ -8971,7 +8971,7 @@
         <v>165</v>
       </c>
       <c r="C658" t="n">
-        <v>-0.009686999999999999</v>
+        <v>-0.011217</v>
       </c>
     </row>
     <row r="659">
@@ -8984,7 +8984,7 @@
         <v>166</v>
       </c>
       <c r="C659" t="n">
-        <v>-0.009636</v>
+        <v>-0.011021</v>
       </c>
     </row>
     <row r="660">
@@ -8997,7 +8997,7 @@
         <v>167</v>
       </c>
       <c r="C660" t="n">
-        <v>-0.009483</v>
+        <v>-0.010214</v>
       </c>
     </row>
     <row r="661">
@@ -9010,7 +9010,7 @@
         <v>168</v>
       </c>
       <c r="C661" t="n">
-        <v>-0.009318999999999999</v>
+        <v>-0.009528</v>
       </c>
     </row>
     <row r="662">
@@ -9023,7 +9023,7 @@
         <v>169</v>
       </c>
       <c r="C662" t="n">
-        <v>-0.009162</v>
+        <v>-0.009280999999999999</v>
       </c>
     </row>
     <row r="663">
@@ -9036,7 +9036,7 @@
         <v>170</v>
       </c>
       <c r="C663" t="n">
-        <v>-0.008911000000000001</v>
+        <v>-0.008822999999999999</v>
       </c>
     </row>
     <row r="664">
@@ -9049,7 +9049,7 @@
         <v>171</v>
       </c>
       <c r="C664" t="n">
-        <v>-0.008742</v>
+        <v>-0.008704999999999999</v>
       </c>
     </row>
     <row r="665">
@@ -9062,7 +9062,7 @@
         <v>172</v>
       </c>
       <c r="C665" t="n">
-        <v>-0.008096000000000001</v>
+        <v>-0.008583</v>
       </c>
     </row>
     <row r="666">
@@ -9075,7 +9075,7 @@
         <v>173</v>
       </c>
       <c r="C666" t="n">
-        <v>-0.008045</v>
+        <v>-0.007846000000000001</v>
       </c>
     </row>
     <row r="667">
@@ -9088,7 +9088,7 @@
         <v>174</v>
       </c>
       <c r="C667" t="n">
-        <v>-0.007867000000000001</v>
+        <v>-0.007828999999999999</v>
       </c>
     </row>
     <row r="668">
@@ -9101,7 +9101,7 @@
         <v>175</v>
       </c>
       <c r="C668" t="n">
-        <v>-0.007527</v>
+        <v>-0.007423</v>
       </c>
     </row>
     <row r="669">
@@ -9114,7 +9114,7 @@
         <v>176</v>
       </c>
       <c r="C669" t="n">
-        <v>-0.007299</v>
+        <v>-0.007403</v>
       </c>
     </row>
     <row r="670">
@@ -9127,7 +9127,7 @@
         <v>177</v>
       </c>
       <c r="C670" t="n">
-        <v>-0.00726</v>
+        <v>-0.007383</v>
       </c>
     </row>
     <row r="671">
@@ -9140,7 +9140,7 @@
         <v>178</v>
       </c>
       <c r="C671" t="n">
-        <v>-0.007001</v>
+        <v>-0.007072</v>
       </c>
     </row>
     <row r="672">
@@ -9153,7 +9153,7 @@
         <v>179</v>
       </c>
       <c r="C672" t="n">
-        <v>-0.00689</v>
+        <v>-0.006721</v>
       </c>
     </row>
     <row r="673">
@@ -9166,7 +9166,7 @@
         <v>180</v>
       </c>
       <c r="C673" t="n">
-        <v>-0.006879</v>
+        <v>-0.00661</v>
       </c>
     </row>
     <row r="674">
@@ -9179,7 +9179,7 @@
         <v>181</v>
       </c>
       <c r="C674" t="n">
-        <v>-0.00683</v>
+        <v>-0.006511</v>
       </c>
     </row>
     <row r="675">
@@ -9192,7 +9192,7 @@
         <v>182</v>
       </c>
       <c r="C675" t="n">
-        <v>-0.006807</v>
+        <v>-0.006163</v>
       </c>
     </row>
     <row r="676">
@@ -9205,7 +9205,7 @@
         <v>183</v>
       </c>
       <c r="C676" t="n">
-        <v>-0.006113</v>
+        <v>-0.005992</v>
       </c>
     </row>
     <row r="677">
@@ -9218,7 +9218,7 @@
         <v>184</v>
       </c>
       <c r="C677" t="n">
-        <v>-0.00586</v>
+        <v>-0.00551</v>
       </c>
     </row>
     <row r="678">
@@ -9231,7 +9231,7 @@
         <v>185</v>
       </c>
       <c r="C678" t="n">
-        <v>-0.005753</v>
+        <v>-0.005502</v>
       </c>
     </row>
     <row r="679">
@@ -9244,7 +9244,7 @@
         <v>186</v>
       </c>
       <c r="C679" t="n">
-        <v>-0.005583</v>
+        <v>-0.005114</v>
       </c>
     </row>
     <row r="680">
@@ -9257,7 +9257,7 @@
         <v>187</v>
       </c>
       <c r="C680" t="n">
-        <v>-0.005504</v>
+        <v>-0.004565</v>
       </c>
     </row>
     <row r="681">
@@ -9270,7 +9270,7 @@
         <v>188</v>
       </c>
       <c r="C681" t="n">
-        <v>-0.005245</v>
+        <v>-0.004298</v>
       </c>
     </row>
     <row r="682">
@@ -9283,7 +9283,7 @@
         <v>189</v>
       </c>
       <c r="C682" t="n">
-        <v>-0.004885</v>
+        <v>-0.004124</v>
       </c>
     </row>
     <row r="683">
@@ -9296,7 +9296,7 @@
         <v>190</v>
       </c>
       <c r="C683" t="n">
-        <v>-0.004323</v>
+        <v>-0.004045</v>
       </c>
     </row>
     <row r="684">
@@ -9309,7 +9309,7 @@
         <v>191</v>
       </c>
       <c r="C684" t="n">
-        <v>-0.00432</v>
+        <v>-0.003717</v>
       </c>
     </row>
     <row r="685">
@@ -9322,7 +9322,7 @@
         <v>192</v>
       </c>
       <c r="C685" t="n">
-        <v>-0.004161</v>
+        <v>-0.003143</v>
       </c>
     </row>
     <row r="686">
@@ -9335,7 +9335,7 @@
         <v>193</v>
       </c>
       <c r="C686" t="n">
-        <v>-0.004146</v>
+        <v>-0.00282</v>
       </c>
     </row>
     <row r="687">
@@ -9348,7 +9348,7 @@
         <v>194</v>
       </c>
       <c r="C687" t="n">
-        <v>-0.003974</v>
+        <v>-0.002805</v>
       </c>
     </row>
     <row r="688">
@@ -9361,7 +9361,7 @@
         <v>195</v>
       </c>
       <c r="C688" t="n">
-        <v>-0.003811</v>
+        <v>-0.002554</v>
       </c>
     </row>
     <row r="689">
@@ -9374,7 +9374,7 @@
         <v>196</v>
       </c>
       <c r="C689" t="n">
-        <v>-0.003664</v>
+        <v>-0.002505</v>
       </c>
     </row>
     <row r="690">
@@ -9387,7 +9387,7 @@
         <v>197</v>
       </c>
       <c r="C690" t="n">
-        <v>-0.003635</v>
+        <v>-0.001993</v>
       </c>
     </row>
     <row r="691">
@@ -9400,7 +9400,7 @@
         <v>198</v>
       </c>
       <c r="C691" t="n">
-        <v>-0.00353</v>
+        <v>-0.001479</v>
       </c>
     </row>
     <row r="692">
@@ -9413,7 +9413,7 @@
         <v>199</v>
       </c>
       <c r="C692" t="n">
-        <v>-0.003349</v>
+        <v>-0.001359</v>
       </c>
     </row>
     <row r="693">
@@ -9426,7 +9426,7 @@
         <v>200</v>
       </c>
       <c r="C693" t="n">
-        <v>-0.003282</v>
+        <v>-0.0009700000000000001</v>
       </c>
     </row>
     <row r="694">
@@ -9439,7 +9439,7 @@
         <v>201</v>
       </c>
       <c r="C694" t="n">
-        <v>-0.003266</v>
+        <v>-0.000878</v>
       </c>
     </row>
     <row r="695">
@@ -9452,7 +9452,7 @@
         <v>202</v>
       </c>
       <c r="C695" t="n">
-        <v>-0.003069</v>
+        <v>-0.000769</v>
       </c>
     </row>
     <row r="696">
@@ -9465,7 +9465,7 @@
         <v>203</v>
       </c>
       <c r="C696" t="n">
-        <v>-0.003065</v>
+        <v>-0.000562</v>
       </c>
     </row>
     <row r="697">
@@ -9478,7 +9478,7 @@
         <v>204</v>
       </c>
       <c r="C697" t="n">
-        <v>-0.002679</v>
+        <v>-0.000384</v>
       </c>
     </row>
     <row r="698">
@@ -9491,7 +9491,7 @@
         <v>205</v>
       </c>
       <c r="C698" t="n">
-        <v>-0.002625</v>
+        <v>-0.000344</v>
       </c>
     </row>
     <row r="699">
@@ -9504,7 +9504,7 @@
         <v>206</v>
       </c>
       <c r="C699" t="n">
-        <v>-0.002552</v>
+        <v>0.000452</v>
       </c>
     </row>
     <row r="700">
@@ -9517,7 +9517,7 @@
         <v>207</v>
       </c>
       <c r="C700" t="n">
-        <v>-0.002529</v>
+        <v>0.000461</v>
       </c>
     </row>
     <row r="701">
@@ -9530,7 +9530,7 @@
         <v>208</v>
       </c>
       <c r="C701" t="n">
-        <v>-0.002451</v>
+        <v>0.001574</v>
       </c>
     </row>
     <row r="702">
@@ -9543,7 +9543,7 @@
         <v>209</v>
       </c>
       <c r="C702" t="n">
-        <v>-0.002332</v>
+        <v>0.001754</v>
       </c>
     </row>
     <row r="703">
@@ -9556,7 +9556,7 @@
         <v>210</v>
       </c>
       <c r="C703" t="n">
-        <v>-0.002109</v>
+        <v>0.00229</v>
       </c>
     </row>
     <row r="704">
@@ -9569,7 +9569,7 @@
         <v>211</v>
       </c>
       <c r="C704" t="n">
-        <v>-0.002098</v>
+        <v>0.002344</v>
       </c>
     </row>
     <row r="705">
@@ -9582,7 +9582,7 @@
         <v>212</v>
       </c>
       <c r="C705" t="n">
-        <v>-0.002043</v>
+        <v>0.002605</v>
       </c>
     </row>
     <row r="706">
@@ -9595,7 +9595,7 @@
         <v>213</v>
       </c>
       <c r="C706" t="n">
-        <v>-0.001602</v>
+        <v>0.003438</v>
       </c>
     </row>
     <row r="707">
@@ -9608,7 +9608,7 @@
         <v>214</v>
       </c>
       <c r="C707" t="n">
-        <v>-0.00128</v>
+        <v>0.003515</v>
       </c>
     </row>
     <row r="708">
@@ -9621,7 +9621,7 @@
         <v>215</v>
       </c>
       <c r="C708" t="n">
-        <v>-0.001233</v>
+        <v>0.003736</v>
       </c>
     </row>
     <row r="709">
@@ -9634,7 +9634,7 @@
         <v>216</v>
       </c>
       <c r="C709" t="n">
-        <v>-0.001172</v>
+        <v>0.003777</v>
       </c>
     </row>
     <row r="710">
@@ -9647,7 +9647,7 @@
         <v>217</v>
       </c>
       <c r="C710" t="n">
-        <v>-0.000883</v>
+        <v>0.003927</v>
       </c>
     </row>
     <row r="711">
@@ -9660,7 +9660,7 @@
         <v>218</v>
       </c>
       <c r="C711" t="n">
-        <v>-0.000399</v>
+        <v>0.003982</v>
       </c>
     </row>
     <row r="712">
@@ -9673,7 +9673,7 @@
         <v>219</v>
       </c>
       <c r="C712" t="n">
-        <v>-0.000355</v>
+        <v>0.004287</v>
       </c>
     </row>
     <row r="713">
@@ -9686,7 +9686,7 @@
         <v>220</v>
       </c>
       <c r="C713" t="n">
-        <v>-0.00026</v>
+        <v>0.004487</v>
       </c>
     </row>
     <row r="714">
@@ -9699,7 +9699,7 @@
         <v>221</v>
       </c>
       <c r="C714" t="n">
-        <v>0</v>
+        <v>0.004577</v>
       </c>
     </row>
     <row r="715">
@@ -9712,7 +9712,7 @@
         <v>222</v>
       </c>
       <c r="C715" t="n">
-        <v>0</v>
+        <v>0.004769</v>
       </c>
     </row>
     <row r="716">
@@ -9725,7 +9725,7 @@
         <v>223</v>
       </c>
       <c r="C716" t="n">
-        <v>0</v>
+        <v>0.004844</v>
       </c>
     </row>
     <row r="717">
@@ -9738,7 +9738,7 @@
         <v>224</v>
       </c>
       <c r="C717" t="n">
-        <v>0</v>
+        <v>0.004879</v>
       </c>
     </row>
     <row r="718">
@@ -9751,7 +9751,7 @@
         <v>225</v>
       </c>
       <c r="C718" t="n">
-        <v>0</v>
+        <v>0.004948</v>
       </c>
     </row>
     <row r="719">
@@ -9764,7 +9764,7 @@
         <v>226</v>
       </c>
       <c r="C719" t="n">
-        <v>0</v>
+        <v>0.005247</v>
       </c>
     </row>
     <row r="720">
@@ -9777,7 +9777,7 @@
         <v>227</v>
       </c>
       <c r="C720" t="n">
-        <v>0</v>
+        <v>0.005301</v>
       </c>
     </row>
     <row r="721">
@@ -9790,7 +9790,7 @@
         <v>228</v>
       </c>
       <c r="C721" t="n">
-        <v>0</v>
+        <v>0.005524</v>
       </c>
     </row>
     <row r="722">
@@ -9803,7 +9803,7 @@
         <v>229</v>
       </c>
       <c r="C722" t="n">
-        <v>0</v>
+        <v>0.007061</v>
       </c>
     </row>
     <row r="723">
@@ -9816,7 +9816,7 @@
         <v>230</v>
       </c>
       <c r="C723" t="n">
-        <v>0</v>
+        <v>0.007527</v>
       </c>
     </row>
     <row r="724">
@@ -9829,7 +9829,7 @@
         <v>231</v>
       </c>
       <c r="C724" t="n">
-        <v>0</v>
+        <v>0.007687</v>
       </c>
     </row>
     <row r="725">
@@ -9842,7 +9842,7 @@
         <v>232</v>
       </c>
       <c r="C725" t="n">
-        <v>0</v>
+        <v>0.007752</v>
       </c>
     </row>
     <row r="726">
@@ -9855,7 +9855,7 @@
         <v>233</v>
       </c>
       <c r="C726" t="n">
-        <v>0</v>
+        <v>0.008522999999999999</v>
       </c>
     </row>
     <row r="727">
@@ -9868,7 +9868,7 @@
         <v>234</v>
       </c>
       <c r="C727" t="n">
-        <v>0</v>
+        <v>0.008739</v>
       </c>
     </row>
     <row r="728">
@@ -9881,7 +9881,7 @@
         <v>235</v>
       </c>
       <c r="C728" t="n">
-        <v>0</v>
+        <v>0.008802000000000001</v>
       </c>
     </row>
     <row r="729">
@@ -9894,7 +9894,7 @@
         <v>236</v>
       </c>
       <c r="C729" t="n">
-        <v>0</v>
+        <v>0.008887000000000001</v>
       </c>
     </row>
     <row r="730">
@@ -9907,7 +9907,7 @@
         <v>237</v>
       </c>
       <c r="C730" t="n">
-        <v>0</v>
+        <v>0.008964</v>
       </c>
     </row>
     <row r="731">
@@ -9920,7 +9920,7 @@
         <v>238</v>
       </c>
       <c r="C731" t="n">
-        <v>0</v>
+        <v>0.009266999999999999</v>
       </c>
     </row>
     <row r="732">
@@ -9933,7 +9933,7 @@
         <v>239</v>
       </c>
       <c r="C732" t="n">
-        <v>0</v>
+        <v>0.009604</v>
       </c>
     </row>
     <row r="733">
@@ -9946,7 +9946,7 @@
         <v>240</v>
       </c>
       <c r="C733" t="n">
-        <v>0</v>
+        <v>0.009705999999999999</v>
       </c>
     </row>
     <row r="734">
@@ -9959,7 +9959,7 @@
         <v>241</v>
       </c>
       <c r="C734" t="n">
-        <v>0</v>
+        <v>0.009861</v>
       </c>
     </row>
     <row r="735">
@@ -9972,7 +9972,7 @@
         <v>242</v>
       </c>
       <c r="C735" t="n">
-        <v>0</v>
+        <v>0.009946999999999999</v>
       </c>
     </row>
     <row r="736">
@@ -9985,7 +9985,7 @@
         <v>243</v>
       </c>
       <c r="C736" t="n">
-        <v>0</v>
+        <v>0.009959000000000001</v>
       </c>
     </row>
     <row r="737">
@@ -9998,7 +9998,7 @@
         <v>244</v>
       </c>
       <c r="C737" t="n">
-        <v>0</v>
+        <v>0.010126</v>
       </c>
     </row>
     <row r="738">
@@ -10011,7 +10011,7 @@
         <v>245</v>
       </c>
       <c r="C738" t="n">
-        <v>0</v>
+        <v>0.010293</v>
       </c>
     </row>
     <row r="739">
@@ -10024,7 +10024,7 @@
         <v>246</v>
       </c>
       <c r="C739" t="n">
-        <v>2.2e-05</v>
+        <v>0.011219</v>
       </c>
     </row>
     <row r="740">
@@ -10037,7 +10037,7 @@
         <v>247</v>
       </c>
       <c r="C740" t="n">
-        <v>0.00011</v>
+        <v>0.011329</v>
       </c>
     </row>
     <row r="741">
@@ -10050,7 +10050,7 @@
         <v>248</v>
       </c>
       <c r="C741" t="n">
-        <v>0.000973</v>
+        <v>0.012007</v>
       </c>
     </row>
     <row r="742">
@@ -10063,7 +10063,7 @@
         <v>249</v>
       </c>
       <c r="C742" t="n">
-        <v>0.001354</v>
+        <v>0.012232</v>
       </c>
     </row>
     <row r="743">
@@ -10076,7 +10076,7 @@
         <v>250</v>
       </c>
       <c r="C743" t="n">
-        <v>0.001412</v>
+        <v>0.012299</v>
       </c>
     </row>
     <row r="744">
@@ -10089,7 +10089,7 @@
         <v>251</v>
       </c>
       <c r="C744" t="n">
-        <v>0.001425</v>
+        <v>0.012304</v>
       </c>
     </row>
     <row r="745">
@@ -10102,7 +10102,7 @@
         <v>252</v>
       </c>
       <c r="C745" t="n">
-        <v>0.001471</v>
+        <v>0.013077</v>
       </c>
     </row>
     <row r="746">
@@ -10115,7 +10115,7 @@
         <v>253</v>
       </c>
       <c r="C746" t="n">
-        <v>0.001554</v>
+        <v>0.013501</v>
       </c>
     </row>
     <row r="747">
@@ -10128,7 +10128,7 @@
         <v>254</v>
       </c>
       <c r="C747" t="n">
-        <v>0.001635</v>
+        <v>0.013505</v>
       </c>
     </row>
     <row r="748">
@@ -10141,7 +10141,7 @@
         <v>255</v>
       </c>
       <c r="C748" t="n">
-        <v>0.002083</v>
+        <v>0.014035</v>
       </c>
     </row>
     <row r="749">
@@ -10154,7 +10154,7 @@
         <v>256</v>
       </c>
       <c r="C749" t="n">
-        <v>0.002348</v>
+        <v>0.014144</v>
       </c>
     </row>
     <row r="750">
@@ -10167,7 +10167,7 @@
         <v>257</v>
       </c>
       <c r="C750" t="n">
-        <v>0.002366</v>
+        <v>0.014565</v>
       </c>
     </row>
     <row r="751">
@@ -10180,7 +10180,7 @@
         <v>258</v>
       </c>
       <c r="C751" t="n">
-        <v>0.002448</v>
+        <v>0.01468</v>
       </c>
     </row>
     <row r="752">
@@ -10193,7 +10193,7 @@
         <v>259</v>
       </c>
       <c r="C752" t="n">
-        <v>0.00246</v>
+        <v>0.014743</v>
       </c>
     </row>
     <row r="753">
@@ -10206,7 +10206,7 @@
         <v>260</v>
       </c>
       <c r="C753" t="n">
-        <v>0.002518</v>
+        <v>0.015002</v>
       </c>
     </row>
     <row r="754">
@@ -10219,7 +10219,7 @@
         <v>261</v>
       </c>
       <c r="C754" t="n">
-        <v>0.0027</v>
+        <v>0.0155</v>
       </c>
     </row>
     <row r="755">
@@ -10232,7 +10232,7 @@
         <v>262</v>
       </c>
       <c r="C755" t="n">
-        <v>0.003288</v>
+        <v>0.015672</v>
       </c>
     </row>
     <row r="756">
@@ -10245,7 +10245,7 @@
         <v>263</v>
       </c>
       <c r="C756" t="n">
-        <v>0.003602</v>
+        <v>0.015774</v>
       </c>
     </row>
     <row r="757">
@@ -10258,7 +10258,7 @@
         <v>264</v>
       </c>
       <c r="C757" t="n">
-        <v>0.00361</v>
+        <v>0.016348</v>
       </c>
     </row>
     <row r="758">
@@ -10271,7 +10271,7 @@
         <v>265</v>
       </c>
       <c r="C758" t="n">
-        <v>0.003871</v>
+        <v>0.01652</v>
       </c>
     </row>
     <row r="759">
@@ -10284,7 +10284,7 @@
         <v>266</v>
       </c>
       <c r="C759" t="n">
-        <v>0.004201</v>
+        <v>0.016694</v>
       </c>
     </row>
     <row r="760">
@@ -10297,7 +10297,7 @@
         <v>267</v>
       </c>
       <c r="C760" t="n">
-        <v>0.004348</v>
+        <v>0.017046</v>
       </c>
     </row>
     <row r="761">
@@ -10310,7 +10310,7 @@
         <v>268</v>
       </c>
       <c r="C761" t="n">
-        <v>0.004562</v>
+        <v>0.017107</v>
       </c>
     </row>
     <row r="762">
@@ -10323,7 +10323,7 @@
         <v>269</v>
       </c>
       <c r="C762" t="n">
-        <v>0.004655</v>
+        <v>0.017743</v>
       </c>
     </row>
     <row r="763">
@@ -10336,7 +10336,7 @@
         <v>270</v>
       </c>
       <c r="C763" t="n">
-        <v>0.004861</v>
+        <v>0.01794</v>
       </c>
     </row>
     <row r="764">
@@ -10349,7 +10349,7 @@
         <v>271</v>
       </c>
       <c r="C764" t="n">
-        <v>0.004872</v>
+        <v>0.018148</v>
       </c>
     </row>
     <row r="765">
@@ -10362,7 +10362,7 @@
         <v>272</v>
       </c>
       <c r="C765" t="n">
-        <v>0.005185</v>
+        <v>0.018696</v>
       </c>
     </row>
     <row r="766">
@@ -10375,7 +10375,7 @@
         <v>273</v>
       </c>
       <c r="C766" t="n">
-        <v>0.005419</v>
+        <v>0.019133</v>
       </c>
     </row>
     <row r="767">
@@ -10388,7 +10388,7 @@
         <v>274</v>
       </c>
       <c r="C767" t="n">
-        <v>0.005601</v>
+        <v>0.019373</v>
       </c>
     </row>
     <row r="768">
@@ -10401,7 +10401,7 @@
         <v>275</v>
       </c>
       <c r="C768" t="n">
-        <v>0.006023</v>
+        <v>0.019565</v>
       </c>
     </row>
     <row r="769">
@@ -10414,7 +10414,7 @@
         <v>276</v>
       </c>
       <c r="C769" t="n">
-        <v>0.006137</v>
+        <v>0.019806</v>
       </c>
     </row>
     <row r="770">
@@ -10427,7 +10427,7 @@
         <v>277</v>
       </c>
       <c r="C770" t="n">
-        <v>0.006169</v>
+        <v>0.020446</v>
       </c>
     </row>
     <row r="771">
@@ -10440,7 +10440,7 @@
         <v>278</v>
       </c>
       <c r="C771" t="n">
-        <v>0.006392</v>
+        <v>0.020682</v>
       </c>
     </row>
     <row r="772">
@@ -10453,7 +10453,7 @@
         <v>279</v>
       </c>
       <c r="C772" t="n">
-        <v>0.006438</v>
+        <v>0.021539</v>
       </c>
     </row>
     <row r="773">
@@ -10466,7 +10466,7 @@
         <v>280</v>
       </c>
       <c r="C773" t="n">
-        <v>0.006698</v>
+        <v>0.022018</v>
       </c>
     </row>
     <row r="774">
@@ -10479,7 +10479,7 @@
         <v>281</v>
       </c>
       <c r="C774" t="n">
-        <v>0.00689</v>
+        <v>0.022099</v>
       </c>
     </row>
     <row r="775">
@@ -10492,7 +10492,7 @@
         <v>282</v>
       </c>
       <c r="C775" t="n">
-        <v>0.006904</v>
+        <v>0.022296</v>
       </c>
     </row>
     <row r="776">
@@ -10505,7 +10505,7 @@
         <v>283</v>
       </c>
       <c r="C776" t="n">
-        <v>0.007396</v>
+        <v>0.022435</v>
       </c>
     </row>
     <row r="777">
@@ -10518,7 +10518,7 @@
         <v>284</v>
       </c>
       <c r="C777" t="n">
-        <v>0.007495</v>
+        <v>0.022533</v>
       </c>
     </row>
     <row r="778">
@@ -10531,7 +10531,7 @@
         <v>285</v>
       </c>
       <c r="C778" t="n">
-        <v>0.007496</v>
+        <v>0.022693</v>
       </c>
     </row>
     <row r="779">
@@ -10544,7 +10544,7 @@
         <v>286</v>
       </c>
       <c r="C779" t="n">
-        <v>0.007592</v>
+        <v>0.023044</v>
       </c>
     </row>
     <row r="780">
@@ -10557,7 +10557,7 @@
         <v>287</v>
       </c>
       <c r="C780" t="n">
-        <v>0.007698</v>
+        <v>0.024604</v>
       </c>
     </row>
     <row r="781">
@@ -10570,7 +10570,7 @@
         <v>288</v>
       </c>
       <c r="C781" t="n">
-        <v>0.00775</v>
+        <v>0.024963</v>
       </c>
     </row>
     <row r="782">
@@ -10583,7 +10583,7 @@
         <v>289</v>
       </c>
       <c r="C782" t="n">
-        <v>0.008033999999999999</v>
+        <v>0.025119</v>
       </c>
     </row>
     <row r="783">
@@ -10596,7 +10596,7 @@
         <v>290</v>
       </c>
       <c r="C783" t="n">
-        <v>0.008193000000000001</v>
+        <v>0.025607</v>
       </c>
     </row>
     <row r="784">
@@ -10609,7 +10609,7 @@
         <v>291</v>
       </c>
       <c r="C784" t="n">
-        <v>0.008435</v>
+        <v>0.025761</v>
       </c>
     </row>
     <row r="785">
@@ -10622,7 +10622,7 @@
         <v>292</v>
       </c>
       <c r="C785" t="n">
-        <v>0.008454</v>
+        <v>0.025857</v>
       </c>
     </row>
     <row r="786">
@@ -10635,7 +10635,7 @@
         <v>293</v>
       </c>
       <c r="C786" t="n">
-        <v>0.008539</v>
+        <v>0.025901</v>
       </c>
     </row>
     <row r="787">
@@ -10648,7 +10648,7 @@
         <v>294</v>
       </c>
       <c r="C787" t="n">
-        <v>0.008578000000000001</v>
+        <v>0.026283</v>
       </c>
     </row>
     <row r="788">
@@ -10661,7 +10661,7 @@
         <v>295</v>
       </c>
       <c r="C788" t="n">
-        <v>0.008682</v>
+        <v>0.027242</v>
       </c>
     </row>
     <row r="789">
@@ -10674,7 +10674,7 @@
         <v>296</v>
       </c>
       <c r="C789" t="n">
-        <v>0.008976</v>
+        <v>0.027324</v>
       </c>
     </row>
     <row r="790">
@@ -10687,7 +10687,7 @@
         <v>297</v>
       </c>
       <c r="C790" t="n">
-        <v>0.009186</v>
+        <v>0.027749</v>
       </c>
     </row>
     <row r="791">
@@ -10700,7 +10700,7 @@
         <v>298</v>
       </c>
       <c r="C791" t="n">
-        <v>0.009394</v>
+        <v>0.027976</v>
       </c>
     </row>
     <row r="792">
@@ -10713,7 +10713,7 @@
         <v>299</v>
       </c>
       <c r="C792" t="n">
-        <v>0.009468000000000001</v>
+        <v>0.028675</v>
       </c>
     </row>
     <row r="793">
@@ -10726,7 +10726,7 @@
         <v>300</v>
       </c>
       <c r="C793" t="n">
-        <v>0.009821</v>
+        <v>0.028688</v>
       </c>
     </row>
     <row r="794">
@@ -10739,7 +10739,7 @@
         <v>301</v>
       </c>
       <c r="C794" t="n">
-        <v>0.009874000000000001</v>
+        <v>0.028841</v>
       </c>
     </row>
     <row r="795">
@@ -10752,7 +10752,7 @@
         <v>302</v>
       </c>
       <c r="C795" t="n">
-        <v>0.009904</v>
+        <v>0.028896</v>
       </c>
     </row>
     <row r="796">
@@ -10765,7 +10765,7 @@
         <v>303</v>
       </c>
       <c r="C796" t="n">
-        <v>0.010009</v>
+        <v>0.029059</v>
       </c>
     </row>
     <row r="797">
@@ -10778,7 +10778,7 @@
         <v>304</v>
       </c>
       <c r="C797" t="n">
-        <v>0.010105</v>
+        <v>0.029677</v>
       </c>
     </row>
     <row r="798">
@@ -10791,7 +10791,7 @@
         <v>305</v>
       </c>
       <c r="C798" t="n">
-        <v>0.01021</v>
+        <v>0.029725</v>
       </c>
     </row>
     <row r="799">
@@ -10804,7 +10804,7 @@
         <v>306</v>
       </c>
       <c r="C799" t="n">
-        <v>0.010347</v>
+        <v>0.030268</v>
       </c>
     </row>
     <row r="800">
@@ -10817,7 +10817,7 @@
         <v>307</v>
       </c>
       <c r="C800" t="n">
-        <v>0.010502</v>
+        <v>0.030607</v>
       </c>
     </row>
     <row r="801">
@@ -10830,7 +10830,7 @@
         <v>308</v>
       </c>
       <c r="C801" t="n">
-        <v>0.010687</v>
+        <v>0.03104</v>
       </c>
     </row>
     <row r="802">
@@ -10843,7 +10843,7 @@
         <v>309</v>
       </c>
       <c r="C802" t="n">
-        <v>0.010703</v>
+        <v>0.031389</v>
       </c>
     </row>
     <row r="803">
@@ -10856,7 +10856,7 @@
         <v>310</v>
       </c>
       <c r="C803" t="n">
-        <v>0.011095</v>
+        <v>0.031453</v>
       </c>
     </row>
     <row r="804">
@@ -10869,7 +10869,7 @@
         <v>311</v>
       </c>
       <c r="C804" t="n">
-        <v>0.011177</v>
+        <v>0.032231</v>
       </c>
     </row>
     <row r="805">
@@ -10882,7 +10882,7 @@
         <v>312</v>
       </c>
       <c r="C805" t="n">
-        <v>0.011186</v>
+        <v>0.03226</v>
       </c>
     </row>
     <row r="806">
@@ -10895,7 +10895,7 @@
         <v>313</v>
       </c>
       <c r="C806" t="n">
-        <v>0.01167</v>
+        <v>0.032269</v>
       </c>
     </row>
     <row r="807">
@@ -10908,7 +10908,7 @@
         <v>314</v>
       </c>
       <c r="C807" t="n">
-        <v>0.01171</v>
+        <v>0.03275</v>
       </c>
     </row>
     <row r="808">
@@ -10921,7 +10921,7 @@
         <v>315</v>
       </c>
       <c r="C808" t="n">
-        <v>0.011723</v>
+        <v>0.033198</v>
       </c>
     </row>
     <row r="809">
@@ -10934,7 +10934,7 @@
         <v>316</v>
       </c>
       <c r="C809" t="n">
-        <v>0.011736</v>
+        <v>0.033267</v>
       </c>
     </row>
     <row r="810">
@@ -10947,7 +10947,7 @@
         <v>317</v>
       </c>
       <c r="C810" t="n">
-        <v>0.011939</v>
+        <v>0.033661</v>
       </c>
     </row>
     <row r="811">
@@ -10960,7 +10960,7 @@
         <v>318</v>
       </c>
       <c r="C811" t="n">
-        <v>0.012376</v>
+        <v>0.033966</v>
       </c>
     </row>
     <row r="812">
@@ -10973,7 +10973,7 @@
         <v>319</v>
       </c>
       <c r="C812" t="n">
-        <v>0.013163</v>
+        <v>0.034033</v>
       </c>
     </row>
     <row r="813">
@@ -10986,7 +10986,7 @@
         <v>320</v>
       </c>
       <c r="C813" t="n">
-        <v>0.013556</v>
+        <v>0.034366</v>
       </c>
     </row>
     <row r="814">
@@ -10999,7 +10999,7 @@
         <v>321</v>
       </c>
       <c r="C814" t="n">
-        <v>0.013596</v>
+        <v>0.034545</v>
       </c>
     </row>
     <row r="815">
@@ -11012,7 +11012,7 @@
         <v>322</v>
       </c>
       <c r="C815" t="n">
-        <v>0.013899</v>
+        <v>0.035126</v>
       </c>
     </row>
     <row r="816">
@@ -11025,7 +11025,7 @@
         <v>323</v>
       </c>
       <c r="C816" t="n">
-        <v>0.01432</v>
+        <v>0.035887</v>
       </c>
     </row>
     <row r="817">
@@ -11038,7 +11038,7 @@
         <v>324</v>
       </c>
       <c r="C817" t="n">
-        <v>0.014402</v>
+        <v>0.036121</v>
       </c>
     </row>
     <row r="818">
@@ -11051,7 +11051,7 @@
         <v>325</v>
       </c>
       <c r="C818" t="n">
-        <v>0.014474</v>
+        <v>0.036244</v>
       </c>
     </row>
     <row r="819">
@@ -11064,7 +11064,7 @@
         <v>326</v>
       </c>
       <c r="C819" t="n">
-        <v>0.01451</v>
+        <v>0.036398</v>
       </c>
     </row>
     <row r="820">
@@ -11077,7 +11077,7 @@
         <v>327</v>
       </c>
       <c r="C820" t="n">
-        <v>0.014902</v>
+        <v>0.036643</v>
       </c>
     </row>
     <row r="821">
@@ -11090,7 +11090,7 @@
         <v>328</v>
       </c>
       <c r="C821" t="n">
-        <v>0.01505</v>
+        <v>0.037064</v>
       </c>
     </row>
     <row r="822">
@@ -11103,7 +11103,7 @@
         <v>329</v>
       </c>
       <c r="C822" t="n">
-        <v>0.015424</v>
+        <v>0.037339</v>
       </c>
     </row>
     <row r="823">
@@ -11116,7 +11116,7 @@
         <v>330</v>
       </c>
       <c r="C823" t="n">
-        <v>0.015471</v>
+        <v>0.03744</v>
       </c>
     </row>
     <row r="824">
@@ -11129,7 +11129,7 @@
         <v>331</v>
       </c>
       <c r="C824" t="n">
-        <v>0.016198</v>
+        <v>0.037479</v>
       </c>
     </row>
     <row r="825">
@@ -11142,7 +11142,7 @@
         <v>332</v>
       </c>
       <c r="C825" t="n">
-        <v>0.016384</v>
+        <v>0.037994</v>
       </c>
     </row>
     <row r="826">
@@ -11155,7 +11155,7 @@
         <v>333</v>
       </c>
       <c r="C826" t="n">
-        <v>0.016469</v>
+        <v>0.038082</v>
       </c>
     </row>
     <row r="827">
@@ -11168,7 +11168,7 @@
         <v>334</v>
       </c>
       <c r="C827" t="n">
-        <v>0.016476</v>
+        <v>0.038506</v>
       </c>
     </row>
     <row r="828">
@@ -11181,7 +11181,7 @@
         <v>335</v>
       </c>
       <c r="C828" t="n">
-        <v>0.016746</v>
+        <v>0.038556</v>
       </c>
     </row>
     <row r="829">
@@ -11194,7 +11194,7 @@
         <v>336</v>
       </c>
       <c r="C829" t="n">
-        <v>0.0169</v>
+        <v>0.038648</v>
       </c>
     </row>
     <row r="830">
@@ -11207,7 +11207,7 @@
         <v>337</v>
       </c>
       <c r="C830" t="n">
-        <v>0.017083</v>
+        <v>0.03868</v>
       </c>
     </row>
     <row r="831">
@@ -11220,7 +11220,7 @@
         <v>338</v>
       </c>
       <c r="C831" t="n">
-        <v>0.017158</v>
+        <v>0.038692</v>
       </c>
     </row>
     <row r="832">
@@ -11233,7 +11233,7 @@
         <v>339</v>
       </c>
       <c r="C832" t="n">
-        <v>0.01729</v>
+        <v>0.038935</v>
       </c>
     </row>
     <row r="833">
@@ -11246,7 +11246,7 @@
         <v>340</v>
       </c>
       <c r="C833" t="n">
-        <v>0.017325</v>
+        <v>0.038951</v>
       </c>
     </row>
     <row r="834">
@@ -11259,7 +11259,7 @@
         <v>341</v>
       </c>
       <c r="C834" t="n">
-        <v>0.017425</v>
+        <v>0.040034</v>
       </c>
     </row>
     <row r="835">
@@ -11272,7 +11272,7 @@
         <v>342</v>
       </c>
       <c r="C835" t="n">
-        <v>0.017523</v>
+        <v>0.040038</v>
       </c>
     </row>
     <row r="836">
@@ -11285,7 +11285,7 @@
         <v>343</v>
       </c>
       <c r="C836" t="n">
-        <v>0.017913</v>
+        <v>0.040736</v>
       </c>
     </row>
     <row r="837">
@@ -11298,7 +11298,7 @@
         <v>344</v>
       </c>
       <c r="C837" t="n">
-        <v>0.017969</v>
+        <v>0.040938</v>
       </c>
     </row>
     <row r="838">
@@ -11311,7 +11311,7 @@
         <v>345</v>
       </c>
       <c r="C838" t="n">
-        <v>0.018248</v>
+        <v>0.041031</v>
       </c>
     </row>
     <row r="839">
@@ -11324,7 +11324,7 @@
         <v>346</v>
       </c>
       <c r="C839" t="n">
-        <v>0.018405</v>
+        <v>0.041347</v>
       </c>
     </row>
     <row r="840">
@@ -11337,7 +11337,7 @@
         <v>347</v>
       </c>
       <c r="C840" t="n">
-        <v>0.018882</v>
+        <v>0.041894</v>
       </c>
     </row>
     <row r="841">
@@ -11350,7 +11350,7 @@
         <v>348</v>
       </c>
       <c r="C841" t="n">
-        <v>0.019363</v>
+        <v>0.042205</v>
       </c>
     </row>
     <row r="842">
@@ -11363,7 +11363,7 @@
         <v>349</v>
       </c>
       <c r="C842" t="n">
-        <v>0.019403</v>
+        <v>0.042692</v>
       </c>
     </row>
     <row r="843">
@@ -11376,7 +11376,7 @@
         <v>350</v>
       </c>
       <c r="C843" t="n">
-        <v>0.019859</v>
+        <v>0.042771</v>
       </c>
     </row>
     <row r="844">
@@ -11389,7 +11389,7 @@
         <v>351</v>
       </c>
       <c r="C844" t="n">
-        <v>0.019903</v>
+        <v>0.043087</v>
       </c>
     </row>
     <row r="845">
@@ -11402,7 +11402,7 @@
         <v>352</v>
       </c>
       <c r="C845" t="n">
-        <v>0.020173</v>
+        <v>0.043245</v>
       </c>
     </row>
     <row r="846">
@@ -11415,7 +11415,7 @@
         <v>353</v>
       </c>
       <c r="C846" t="n">
-        <v>0.020338</v>
+        <v>0.043647</v>
       </c>
     </row>
     <row r="847">
@@ -11428,7 +11428,7 @@
         <v>354</v>
       </c>
       <c r="C847" t="n">
-        <v>0.020536</v>
+        <v>0.044492</v>
       </c>
     </row>
     <row r="848">
@@ -11441,7 +11441,7 @@
         <v>355</v>
       </c>
       <c r="C848" t="n">
-        <v>0.020582</v>
+        <v>0.044609</v>
       </c>
     </row>
     <row r="849">
@@ -11454,7 +11454,7 @@
         <v>356</v>
       </c>
       <c r="C849" t="n">
-        <v>0.020823</v>
+        <v>0.044755</v>
       </c>
     </row>
     <row r="850">
@@ -11467,7 +11467,7 @@
         <v>357</v>
       </c>
       <c r="C850" t="n">
-        <v>0.020882</v>
+        <v>0.045164</v>
       </c>
     </row>
     <row r="851">
@@ -11480,7 +11480,7 @@
         <v>358</v>
       </c>
       <c r="C851" t="n">
-        <v>0.021148</v>
+        <v>0.045556</v>
       </c>
     </row>
     <row r="852">
@@ -11493,7 +11493,7 @@
         <v>359</v>
       </c>
       <c r="C852" t="n">
-        <v>0.021414</v>
+        <v>0.045758</v>
       </c>
     </row>
     <row r="853">
@@ -11506,7 +11506,7 @@
         <v>360</v>
       </c>
       <c r="C853" t="n">
-        <v>0.021777</v>
+        <v>0.046124</v>
       </c>
     </row>
     <row r="854">
@@ -11519,7 +11519,7 @@
         <v>361</v>
       </c>
       <c r="C854" t="n">
-        <v>0.021828</v>
+        <v>0.046142</v>
       </c>
     </row>
     <row r="855">
@@ -11532,7 +11532,7 @@
         <v>362</v>
       </c>
       <c r="C855" t="n">
-        <v>0.02187</v>
+        <v>0.046645</v>
       </c>
     </row>
     <row r="856">
@@ -11545,7 +11545,7 @@
         <v>363</v>
       </c>
       <c r="C856" t="n">
-        <v>0.022573</v>
+        <v>0.04699</v>
       </c>
     </row>
     <row r="857">
@@ -11558,7 +11558,7 @@
         <v>364</v>
       </c>
       <c r="C857" t="n">
-        <v>0.023488</v>
+        <v>0.047072</v>
       </c>
     </row>
     <row r="858">
@@ -11571,7 +11571,7 @@
         <v>365</v>
       </c>
       <c r="C858" t="n">
-        <v>0.023758</v>
+        <v>0.047104</v>
       </c>
     </row>
     <row r="859">
@@ -11584,7 +11584,7 @@
         <v>366</v>
       </c>
       <c r="C859" t="n">
-        <v>0.02382</v>
+        <v>0.047467</v>
       </c>
     </row>
     <row r="860">
@@ -11597,7 +11597,7 @@
         <v>367</v>
       </c>
       <c r="C860" t="n">
-        <v>0.023993</v>
+        <v>0.047863</v>
       </c>
     </row>
     <row r="861">
@@ -11610,7 +11610,7 @@
         <v>368</v>
       </c>
       <c r="C861" t="n">
-        <v>0.024297</v>
+        <v>0.048008</v>
       </c>
     </row>
     <row r="862">
@@ -11623,7 +11623,7 @@
         <v>369</v>
       </c>
       <c r="C862" t="n">
-        <v>0.024584</v>
+        <v>0.048228</v>
       </c>
     </row>
     <row r="863">
@@ -11636,7 +11636,7 @@
         <v>370</v>
       </c>
       <c r="C863" t="n">
-        <v>0.025067</v>
+        <v>0.048519</v>
       </c>
     </row>
     <row r="864">
@@ -11649,7 +11649,7 @@
         <v>371</v>
       </c>
       <c r="C864" t="n">
-        <v>0.025282</v>
+        <v>0.049583</v>
       </c>
     </row>
     <row r="865">
@@ -11662,7 +11662,7 @@
         <v>372</v>
       </c>
       <c r="C865" t="n">
-        <v>0.025669</v>
+        <v>0.052319</v>
       </c>
     </row>
     <row r="866">
@@ -11675,7 +11675,7 @@
         <v>373</v>
       </c>
       <c r="C866" t="n">
-        <v>0.026051</v>
+        <v>0.052671</v>
       </c>
     </row>
     <row r="867">
@@ -11688,7 +11688,7 @@
         <v>374</v>
       </c>
       <c r="C867" t="n">
-        <v>0.026054</v>
+        <v>0.053622</v>
       </c>
     </row>
     <row r="868">
@@ -11701,7 +11701,7 @@
         <v>375</v>
       </c>
       <c r="C868" t="n">
-        <v>0.026435</v>
+        <v>0.054094</v>
       </c>
     </row>
     <row r="869">
@@ -11714,7 +11714,7 @@
         <v>376</v>
       </c>
       <c r="C869" t="n">
-        <v>0.026701</v>
+        <v>0.054436</v>
       </c>
     </row>
     <row r="870">
@@ -11727,7 +11727,7 @@
         <v>377</v>
       </c>
       <c r="C870" t="n">
-        <v>0.026748</v>
+        <v>0.054892</v>
       </c>
     </row>
     <row r="871">
@@ -11740,7 +11740,7 @@
         <v>378</v>
       </c>
       <c r="C871" t="n">
-        <v>0.026885</v>
+        <v>0.055026</v>
       </c>
     </row>
     <row r="872">
@@ -11753,7 +11753,7 @@
         <v>379</v>
       </c>
       <c r="C872" t="n">
-        <v>0.026943</v>
+        <v>0.055452</v>
       </c>
     </row>
     <row r="873">
@@ -11766,7 +11766,7 @@
         <v>380</v>
       </c>
       <c r="C873" t="n">
-        <v>0.027245</v>
+        <v>0.055659</v>
       </c>
     </row>
     <row r="874">
@@ -11779,7 +11779,7 @@
         <v>381</v>
       </c>
       <c r="C874" t="n">
-        <v>0.027987</v>
+        <v>0.05597</v>
       </c>
     </row>
     <row r="875">
@@ -11792,7 +11792,7 @@
         <v>382</v>
       </c>
       <c r="C875" t="n">
-        <v>0.028182</v>
+        <v>0.056232</v>
       </c>
     </row>
     <row r="876">
@@ -11805,7 +11805,7 @@
         <v>383</v>
       </c>
       <c r="C876" t="n">
-        <v>0.028269</v>
+        <v>0.05658</v>
       </c>
     </row>
     <row r="877">
@@ -11818,7 +11818,7 @@
         <v>384</v>
       </c>
       <c r="C877" t="n">
-        <v>0.028736</v>
+        <v>0.056651</v>
       </c>
     </row>
     <row r="878">
@@ -11831,7 +11831,7 @@
         <v>385</v>
       </c>
       <c r="C878" t="n">
-        <v>0.028956</v>
+        <v>0.056749</v>
       </c>
     </row>
     <row r="879">
@@ -11844,7 +11844,7 @@
         <v>386</v>
       </c>
       <c r="C879" t="n">
-        <v>0.029126</v>
+        <v>0.057165</v>
       </c>
     </row>
     <row r="880">
@@ -11857,7 +11857,7 @@
         <v>387</v>
       </c>
       <c r="C880" t="n">
-        <v>0.029377</v>
+        <v>0.057551</v>
       </c>
     </row>
     <row r="881">
@@ -11870,7 +11870,7 @@
         <v>388</v>
       </c>
       <c r="C881" t="n">
-        <v>0.029599</v>
+        <v>0.059257</v>
       </c>
     </row>
     <row r="882">
@@ -11883,7 +11883,7 @@
         <v>389</v>
       </c>
       <c r="C882" t="n">
-        <v>0.029869</v>
+        <v>0.059655</v>
       </c>
     </row>
     <row r="883">
@@ -11896,7 +11896,7 @@
         <v>390</v>
       </c>
       <c r="C883" t="n">
-        <v>0.030116</v>
+        <v>0.059707</v>
       </c>
     </row>
     <row r="884">
@@ -11909,7 +11909,7 @@
         <v>391</v>
       </c>
       <c r="C884" t="n">
-        <v>0.030255</v>
+        <v>0.060872</v>
       </c>
     </row>
     <row r="885">
@@ -11922,7 +11922,7 @@
         <v>392</v>
       </c>
       <c r="C885" t="n">
-        <v>0.030581</v>
+        <v>0.061358</v>
       </c>
     </row>
     <row r="886">
@@ -11935,7 +11935,7 @@
         <v>393</v>
       </c>
       <c r="C886" t="n">
-        <v>0.030616</v>
+        <v>0.061387</v>
       </c>
     </row>
     <row r="887">
@@ -11948,7 +11948,7 @@
         <v>394</v>
       </c>
       <c r="C887" t="n">
-        <v>0.030678</v>
+        <v>0.062085</v>
       </c>
     </row>
     <row r="888">
@@ -11961,7 +11961,7 @@
         <v>395</v>
       </c>
       <c r="C888" t="n">
-        <v>0.030781</v>
+        <v>0.06267300000000001</v>
       </c>
     </row>
     <row r="889">
@@ -11974,7 +11974,7 @@
         <v>396</v>
       </c>
       <c r="C889" t="n">
-        <v>0.031745</v>
+        <v>0.06267499999999999</v>
       </c>
     </row>
     <row r="890">
@@ -11987,7 +11987,7 @@
         <v>397</v>
       </c>
       <c r="C890" t="n">
-        <v>0.031934</v>
+        <v>0.06379600000000001</v>
       </c>
     </row>
     <row r="891">
@@ -12000,7 +12000,7 @@
         <v>398</v>
       </c>
       <c r="C891" t="n">
-        <v>0.032162</v>
+        <v>0.064073</v>
       </c>
     </row>
     <row r="892">
@@ -12013,7 +12013,7 @@
         <v>399</v>
       </c>
       <c r="C892" t="n">
-        <v>0.032185</v>
+        <v>0.064293</v>
       </c>
     </row>
     <row r="893">
@@ -12026,7 +12026,7 @@
         <v>400</v>
       </c>
       <c r="C893" t="n">
-        <v>0.032224</v>
+        <v>0.06522</v>
       </c>
     </row>
     <row r="894">
@@ -12039,7 +12039,7 @@
         <v>401</v>
       </c>
       <c r="C894" t="n">
-        <v>0.03231</v>
+        <v>0.065396</v>
       </c>
     </row>
     <row r="895">
@@ -12052,7 +12052,7 @@
         <v>402</v>
       </c>
       <c r="C895" t="n">
-        <v>0.032833</v>
+        <v>0.06540899999999999</v>
       </c>
     </row>
     <row r="896">
@@ -12065,7 +12065,7 @@
         <v>403</v>
       </c>
       <c r="C896" t="n">
-        <v>0.03304</v>
+        <v>0.065549</v>
       </c>
     </row>
     <row r="897">
@@ -12078,7 +12078,7 @@
         <v>404</v>
       </c>
       <c r="C897" t="n">
-        <v>0.033169</v>
+        <v>0.065835</v>
       </c>
     </row>
     <row r="898">
@@ -12091,7 +12091,7 @@
         <v>405</v>
       </c>
       <c r="C898" t="n">
-        <v>0.033449</v>
+        <v>0.065854</v>
       </c>
     </row>
     <row r="899">
@@ -12104,7 +12104,7 @@
         <v>406</v>
       </c>
       <c r="C899" t="n">
-        <v>0.033794</v>
+        <v>0.066054</v>
       </c>
     </row>
     <row r="900">
@@ -12117,7 +12117,7 @@
         <v>407</v>
       </c>
       <c r="C900" t="n">
-        <v>0.033828</v>
+        <v>0.066236</v>
       </c>
     </row>
     <row r="901">
@@ -12130,7 +12130,7 @@
         <v>408</v>
       </c>
       <c r="C901" t="n">
-        <v>0.03412</v>
+        <v>0.066301</v>
       </c>
     </row>
     <row r="902">
@@ -12143,7 +12143,7 @@
         <v>409</v>
       </c>
       <c r="C902" t="n">
-        <v>0.034726</v>
+        <v>0.06659</v>
       </c>
     </row>
     <row r="903">
@@ -12156,7 +12156,7 @@
         <v>410</v>
       </c>
       <c r="C903" t="n">
-        <v>0.035027</v>
+        <v>0.06712700000000001</v>
       </c>
     </row>
     <row r="904">
@@ -12169,7 +12169,7 @@
         <v>411</v>
       </c>
       <c r="C904" t="n">
-        <v>0.035812</v>
+        <v>0.067445</v>
       </c>
     </row>
     <row r="905">
@@ -12182,7 +12182,7 @@
         <v>412</v>
       </c>
       <c r="C905" t="n">
-        <v>0.036437</v>
+        <v>0.067527</v>
       </c>
     </row>
     <row r="906">
@@ -12195,7 +12195,7 @@
         <v>413</v>
       </c>
       <c r="C906" t="n">
-        <v>0.036503</v>
+        <v>0.068061</v>
       </c>
     </row>
     <row r="907">
@@ -12208,7 +12208,7 @@
         <v>414</v>
       </c>
       <c r="C907" t="n">
-        <v>0.036617</v>
+        <v>0.068568</v>
       </c>
     </row>
     <row r="908">
@@ -12221,7 +12221,7 @@
         <v>415</v>
       </c>
       <c r="C908" t="n">
-        <v>0.036663</v>
+        <v>0.07224899999999999</v>
       </c>
     </row>
     <row r="909">
@@ -12234,7 +12234,7 @@
         <v>416</v>
       </c>
       <c r="C909" t="n">
-        <v>0.036886</v>
+        <v>0.07235900000000001</v>
       </c>
     </row>
     <row r="910">
@@ -12247,7 +12247,7 @@
         <v>417</v>
       </c>
       <c r="C910" t="n">
-        <v>0.036911</v>
+        <v>0.073559</v>
       </c>
     </row>
     <row r="911">
@@ -12260,7 +12260,7 @@
         <v>418</v>
       </c>
       <c r="C911" t="n">
-        <v>0.037927</v>
+        <v>0.073989</v>
       </c>
     </row>
     <row r="912">
@@ -12273,7 +12273,7 @@
         <v>419</v>
       </c>
       <c r="C912" t="n">
-        <v>0.038785</v>
+        <v>0.075611</v>
       </c>
     </row>
     <row r="913">
@@ -12286,7 +12286,7 @@
         <v>420</v>
       </c>
       <c r="C913" t="n">
-        <v>0.039428</v>
+        <v>0.07609100000000001</v>
       </c>
     </row>
     <row r="914">
@@ -12299,7 +12299,7 @@
         <v>421</v>
       </c>
       <c r="C914" t="n">
-        <v>0.039677</v>
+        <v>0.07639799999999999</v>
       </c>
     </row>
     <row r="915">
@@ -12312,7 +12312,7 @@
         <v>422</v>
       </c>
       <c r="C915" t="n">
-        <v>0.040093</v>
+        <v>0.07662099999999999</v>
       </c>
     </row>
     <row r="916">
@@ -12325,7 +12325,7 @@
         <v>423</v>
       </c>
       <c r="C916" t="n">
-        <v>0.040198</v>
+        <v>0.077016</v>
       </c>
     </row>
     <row r="917">
@@ -12338,7 +12338,7 @@
         <v>424</v>
       </c>
       <c r="C917" t="n">
-        <v>0.040359</v>
+        <v>0.077292</v>
       </c>
     </row>
     <row r="918">
@@ -12351,7 +12351,7 @@
         <v>425</v>
       </c>
       <c r="C918" t="n">
-        <v>0.040386</v>
+        <v>0.07875799999999999</v>
       </c>
     </row>
     <row r="919">
@@ -12364,7 +12364,7 @@
         <v>426</v>
       </c>
       <c r="C919" t="n">
-        <v>0.041434</v>
+        <v>0.079572</v>
       </c>
     </row>
     <row r="920">
@@ -12377,7 +12377,7 @@
         <v>427</v>
       </c>
       <c r="C920" t="n">
-        <v>0.041858</v>
+        <v>0.081721</v>
       </c>
     </row>
     <row r="921">
@@ -12390,7 +12390,7 @@
         <v>428</v>
       </c>
       <c r="C921" t="n">
-        <v>0.044093</v>
+        <v>0.08204</v>
       </c>
     </row>
     <row r="922">
@@ -12403,7 +12403,7 @@
         <v>429</v>
       </c>
       <c r="C922" t="n">
-        <v>0.044155</v>
+        <v>0.082191</v>
       </c>
     </row>
     <row r="923">
@@ -12416,7 +12416,7 @@
         <v>430</v>
       </c>
       <c r="C923" t="n">
-        <v>0.044606</v>
+        <v>0.082369</v>
       </c>
     </row>
     <row r="924">
@@ -12429,7 +12429,7 @@
         <v>431</v>
       </c>
       <c r="C924" t="n">
-        <v>0.046074</v>
+        <v>0.084845</v>
       </c>
     </row>
     <row r="925">
@@ -12442,7 +12442,7 @@
         <v>432</v>
       </c>
       <c r="C925" t="n">
-        <v>0.046472</v>
+        <v>0.08505699999999999</v>
       </c>
     </row>
     <row r="926">
@@ -12455,7 +12455,7 @@
         <v>433</v>
       </c>
       <c r="C926" t="n">
-        <v>0.046755</v>
+        <v>0.085952</v>
       </c>
     </row>
     <row r="927">
@@ -12468,7 +12468,7 @@
         <v>434</v>
       </c>
       <c r="C927" t="n">
-        <v>0.04738</v>
+        <v>0.086106</v>
       </c>
     </row>
     <row r="928">
@@ -12481,7 +12481,7 @@
         <v>435</v>
       </c>
       <c r="C928" t="n">
-        <v>0.047669</v>
+        <v>0.08666</v>
       </c>
     </row>
     <row r="929">
@@ -12494,7 +12494,7 @@
         <v>436</v>
       </c>
       <c r="C929" t="n">
-        <v>0.048278</v>
+        <v>0.088506</v>
       </c>
     </row>
     <row r="930">
@@ -12507,7 +12507,7 @@
         <v>437</v>
       </c>
       <c r="C930" t="n">
-        <v>0.049686</v>
+        <v>0.089291</v>
       </c>
     </row>
     <row r="931">
@@ -12520,7 +12520,7 @@
         <v>438</v>
       </c>
       <c r="C931" t="n">
-        <v>0.050192</v>
+        <v>0.09160600000000001</v>
       </c>
     </row>
     <row r="932">
@@ -12533,7 +12533,7 @@
         <v>439</v>
       </c>
       <c r="C932" t="n">
-        <v>0.050352</v>
+        <v>0.092195</v>
       </c>
     </row>
     <row r="933">
@@ -12546,7 +12546,7 @@
         <v>440</v>
       </c>
       <c r="C933" t="n">
-        <v>0.051384</v>
+        <v>0.09248000000000001</v>
       </c>
     </row>
     <row r="934">
@@ -12559,7 +12559,7 @@
         <v>441</v>
       </c>
       <c r="C934" t="n">
-        <v>0.05139</v>
+        <v>0.09504600000000001</v>
       </c>
     </row>
     <row r="935">
@@ -12572,7 +12572,7 @@
         <v>442</v>
       </c>
       <c r="C935" t="n">
-        <v>0.051947</v>
+        <v>0.096599</v>
       </c>
     </row>
     <row r="936">
@@ -12585,7 +12585,7 @@
         <v>443</v>
       </c>
       <c r="C936" t="n">
-        <v>0.052199</v>
+        <v>0.09758699999999999</v>
       </c>
     </row>
     <row r="937">
@@ -12598,7 +12598,7 @@
         <v>444</v>
       </c>
       <c r="C937" t="n">
-        <v>0.052256</v>
+        <v>0.09983599999999999</v>
       </c>
     </row>
     <row r="938">
@@ -12611,7 +12611,7 @@
         <v>445</v>
       </c>
       <c r="C938" t="n">
-        <v>0.052602</v>
+        <v>0.103271</v>
       </c>
     </row>
     <row r="939">
@@ -12624,7 +12624,7 @@
         <v>446</v>
       </c>
       <c r="C939" t="n">
-        <v>0.052804</v>
+        <v>0.106162</v>
       </c>
     </row>
     <row r="940">
@@ -12637,7 +12637,7 @@
         <v>447</v>
       </c>
       <c r="C940" t="n">
-        <v>0.054048</v>
+        <v>0.108018</v>
       </c>
     </row>
     <row r="941">
@@ -12650,7 +12650,7 @@
         <v>448</v>
       </c>
       <c r="C941" t="n">
-        <v>0.054273</v>
+        <v>0.108468</v>
       </c>
     </row>
     <row r="942">
@@ -12663,7 +12663,7 @@
         <v>449</v>
       </c>
       <c r="C942" t="n">
-        <v>0.055704</v>
+        <v>0.110991</v>
       </c>
     </row>
     <row r="943">
@@ -12676,7 +12676,7 @@
         <v>450</v>
       </c>
       <c r="C943" t="n">
-        <v>0.056461</v>
+        <v>0.111192</v>
       </c>
     </row>
     <row r="944">
@@ -12689,7 +12689,7 @@
         <v>451</v>
       </c>
       <c r="C944" t="n">
-        <v>0.056525</v>
+        <v>0.111406</v>
       </c>
     </row>
     <row r="945">
@@ -12702,7 +12702,7 @@
         <v>452</v>
       </c>
       <c r="C945" t="n">
-        <v>0.056937</v>
+        <v>0.111661</v>
       </c>
     </row>
     <row r="946">
@@ -12715,7 +12715,7 @@
         <v>453</v>
       </c>
       <c r="C946" t="n">
-        <v>0.059473</v>
+        <v>0.111915</v>
       </c>
     </row>
     <row r="947">
@@ -12728,7 +12728,7 @@
         <v>454</v>
       </c>
       <c r="C947" t="n">
-        <v>0.060802</v>
+        <v>0.114749</v>
       </c>
     </row>
     <row r="948">
@@ -12741,7 +12741,7 @@
         <v>455</v>
       </c>
       <c r="C948" t="n">
-        <v>0.063125</v>
+        <v>0.119806</v>
       </c>
     </row>
     <row r="949">
@@ -12754,7 +12754,7 @@
         <v>456</v>
       </c>
       <c r="C949" t="n">
-        <v>0.065479</v>
+        <v>0.120543</v>
       </c>
     </row>
     <row r="950">
@@ -12767,7 +12767,7 @@
         <v>457</v>
       </c>
       <c r="C950" t="n">
-        <v>0.06578199999999999</v>
+        <v>0.121385</v>
       </c>
     </row>
     <row r="951">
@@ -12780,7 +12780,7 @@
         <v>458</v>
       </c>
       <c r="C951" t="n">
-        <v>0.068022</v>
+        <v>0.121551</v>
       </c>
     </row>
     <row r="952">
@@ -12793,7 +12793,7 @@
         <v>459</v>
       </c>
       <c r="C952" t="n">
-        <v>0.070881</v>
+        <v>0.12327</v>
       </c>
     </row>
     <row r="953">
@@ -12806,7 +12806,7 @@
         <v>460</v>
       </c>
       <c r="C953" t="n">
-        <v>0.07101200000000001</v>
+        <v>0.124229</v>
       </c>
     </row>
     <row r="954">
@@ -12819,7 +12819,7 @@
         <v>461</v>
       </c>
       <c r="C954" t="n">
-        <v>0.073532</v>
+        <v>0.125255</v>
       </c>
     </row>
     <row r="955">
@@ -12832,7 +12832,7 @@
         <v>462</v>
       </c>
       <c r="C955" t="n">
-        <v>0.074841</v>
+        <v>0.125971</v>
       </c>
     </row>
     <row r="956">
@@ -12845,7 +12845,7 @@
         <v>463</v>
       </c>
       <c r="C956" t="n">
-        <v>0.07573000000000001</v>
+        <v>0.128853</v>
       </c>
     </row>
     <row r="957">
@@ -12858,7 +12858,7 @@
         <v>464</v>
       </c>
       <c r="C957" t="n">
-        <v>0.077164</v>
+        <v>0.13469</v>
       </c>
     </row>
     <row r="958">
@@ -12871,7 +12871,7 @@
         <v>465</v>
       </c>
       <c r="C958" t="n">
-        <v>0.077178</v>
+        <v>0.13761</v>
       </c>
     </row>
     <row r="959">
@@ -12884,7 +12884,7 @@
         <v>466</v>
       </c>
       <c r="C959" t="n">
-        <v>0.079801</v>
+        <v>0.138713</v>
       </c>
     </row>
     <row r="960">
@@ -12897,7 +12897,7 @@
         <v>467</v>
       </c>
       <c r="C960" t="n">
-        <v>0.081141</v>
+        <v>0.141686</v>
       </c>
     </row>
     <row r="961">
@@ -12910,7 +12910,7 @@
         <v>468</v>
       </c>
       <c r="C961" t="n">
-        <v>0.089948</v>
+        <v>0.143512</v>
       </c>
     </row>
     <row r="962">
@@ -12923,7 +12923,7 @@
         <v>469</v>
       </c>
       <c r="C962" t="n">
-        <v>0.090404</v>
+        <v>0.14578</v>
       </c>
     </row>
     <row r="963">
@@ -12936,7 +12936,7 @@
         <v>470</v>
       </c>
       <c r="C963" t="n">
-        <v>0.090902</v>
+        <v>0.160411</v>
       </c>
     </row>
     <row r="964">
@@ -12949,7 +12949,7 @@
         <v>471</v>
       </c>
       <c r="C964" t="n">
-        <v>0.09255099999999999</v>
+        <v>0.162199</v>
       </c>
     </row>
     <row r="965">
@@ -12962,7 +12962,7 @@
         <v>472</v>
       </c>
       <c r="C965" t="n">
-        <v>0.09404800000000001</v>
+        <v>0.164193</v>
       </c>
     </row>
     <row r="966">
@@ -12975,7 +12975,7 @@
         <v>473</v>
       </c>
       <c r="C966" t="n">
-        <v>0.095627</v>
+        <v>0.164251</v>
       </c>
     </row>
     <row r="967">
@@ -12988,7 +12988,7 @@
         <v>474</v>
       </c>
       <c r="C967" t="n">
-        <v>0.097673</v>
+        <v>0.165046</v>
       </c>
     </row>
     <row r="968">
@@ -13001,7 +13001,7 @@
         <v>475</v>
       </c>
       <c r="C968" t="n">
-        <v>0.102613</v>
+        <v>0.170766</v>
       </c>
     </row>
     <row r="969">
@@ -13014,7 +13014,7 @@
         <v>476</v>
       </c>
       <c r="C969" t="n">
-        <v>0.103855</v>
+        <v>0.185261</v>
       </c>
     </row>
     <row r="970">
@@ -13027,7 +13027,7 @@
         <v>477</v>
       </c>
       <c r="C970" t="n">
-        <v>0.11022</v>
+        <v>0.198079</v>
       </c>
     </row>
     <row r="971">
@@ -13040,7 +13040,7 @@
         <v>478</v>
       </c>
       <c r="C971" t="n">
-        <v>0.114933</v>
+        <v>0.221354</v>
       </c>
     </row>
     <row r="972">
@@ -13053,7 +13053,7 @@
         <v>479</v>
       </c>
       <c r="C972" t="n">
-        <v>0.117592</v>
+        <v>0.223016</v>
       </c>
     </row>
     <row r="973">
@@ -13066,7 +13066,7 @@
         <v>480</v>
       </c>
       <c r="C973" t="n">
-        <v>0.121006</v>
+        <v>0.241107</v>
       </c>
     </row>
     <row r="974">
@@ -13079,7 +13079,7 @@
         <v>481</v>
       </c>
       <c r="C974" t="n">
-        <v>0.12411</v>
+        <v>0.272102</v>
       </c>
     </row>
     <row r="975">
@@ -13092,7 +13092,7 @@
         <v>482</v>
       </c>
       <c r="C975" t="n">
-        <v>0.1412</v>
+        <v>0.288091</v>
       </c>
     </row>
     <row r="976">
@@ -13105,7 +13105,7 @@
         <v>483</v>
       </c>
       <c r="C976" t="n">
-        <v>0.147889</v>
+        <v>0.305357</v>
       </c>
     </row>
     <row r="977">
@@ -13118,7 +13118,7 @@
         <v>484</v>
       </c>
       <c r="C977" t="n">
-        <v>0.158456</v>
+        <v>0.330018</v>
       </c>
     </row>
     <row r="978">
@@ -13131,7 +13131,7 @@
         <v>485</v>
       </c>
       <c r="C978" t="n">
-        <v>0.159842</v>
+        <v>0.361398</v>
       </c>
     </row>
     <row r="979">
@@ -13144,7 +13144,7 @@
         <v>486</v>
       </c>
       <c r="C979" t="n">
-        <v>0.231725</v>
+        <v>0.373207</v>
       </c>
     </row>
     <row r="980">
@@ -13157,7 +13157,7 @@
         <v>487</v>
       </c>
       <c r="C980" t="n">
-        <v>0.265458</v>
+        <v>0.486711</v>
       </c>
     </row>
     <row r="981">
@@ -13170,7 +13170,7 @@
         <v>488</v>
       </c>
       <c r="C981" t="n">
-        <v>0.292037</v>
+        <v>0.61993</v>
       </c>
     </row>
     <row r="982">
@@ -13183,7 +13183,7 @@
         <v>489</v>
       </c>
       <c r="C982" t="n">
-        <v>0.295023</v>
+        <v>0.870505</v>
       </c>
     </row>
     <row r="983">
@@ -13196,7 +13196,7 @@
         <v>490</v>
       </c>
       <c r="C983" t="n">
-        <v>0.434987</v>
+        <v>0.880089</v>
       </c>
     </row>
     <row r="984">
@@ -13209,7 +13209,7 @@
         <v>0</v>
       </c>
       <c r="C984" t="n">
-        <v>-1.116645</v>
+        <v>-0.523145</v>
       </c>
     </row>
     <row r="985">
@@ -13222,7 +13222,7 @@
         <v>1</v>
       </c>
       <c r="C985" t="n">
-        <v>-0.851912</v>
+        <v>-0.437677</v>
       </c>
     </row>
     <row r="986">
@@ -13235,7 +13235,7 @@
         <v>2</v>
       </c>
       <c r="C986" t="n">
-        <v>-0.444597</v>
+        <v>-0.319432</v>
       </c>
     </row>
     <row r="987">
@@ -13248,7 +13248,7 @@
         <v>3</v>
       </c>
       <c r="C987" t="n">
-        <v>-0.332713</v>
+        <v>-0.304196</v>
       </c>
     </row>
     <row r="988">
@@ -13261,7 +13261,7 @@
         <v>4</v>
       </c>
       <c r="C988" t="n">
-        <v>-0.27234</v>
+        <v>-0.300601</v>
       </c>
     </row>
     <row r="989">
@@ -13274,7 +13274,7 @@
         <v>5</v>
       </c>
       <c r="C989" t="n">
-        <v>-0.242966</v>
+        <v>-0.225023</v>
       </c>
     </row>
     <row r="990">
@@ -13287,7 +13287,7 @@
         <v>6</v>
       </c>
       <c r="C990" t="n">
-        <v>-0.216048</v>
+        <v>-0.208893</v>
       </c>
     </row>
     <row r="991">
@@ -13300,7 +13300,7 @@
         <v>7</v>
       </c>
       <c r="C991" t="n">
-        <v>-0.178278</v>
+        <v>-0.200859</v>
       </c>
     </row>
     <row r="992">
@@ -13313,7 +13313,7 @@
         <v>8</v>
       </c>
       <c r="C992" t="n">
-        <v>-0.175626</v>
+        <v>-0.153364</v>
       </c>
     </row>
     <row r="993">
@@ -13326,7 +13326,7 @@
         <v>9</v>
       </c>
       <c r="C993" t="n">
-        <v>-0.166237</v>
+        <v>-0.140329</v>
       </c>
     </row>
     <row r="994">
@@ -13339,7 +13339,7 @@
         <v>10</v>
       </c>
       <c r="C994" t="n">
-        <v>-0.153622</v>
+        <v>-0.139544</v>
       </c>
     </row>
     <row r="995">
@@ -13352,7 +13352,7 @@
         <v>11</v>
       </c>
       <c r="C995" t="n">
-        <v>-0.151528</v>
+        <v>-0.135511</v>
       </c>
     </row>
     <row r="996">
@@ -13365,7 +13365,7 @@
         <v>12</v>
       </c>
       <c r="C996" t="n">
-        <v>-0.140488</v>
+        <v>-0.124122</v>
       </c>
     </row>
     <row r="997">
@@ -13378,7 +13378,7 @@
         <v>13</v>
       </c>
       <c r="C997" t="n">
-        <v>-0.131433</v>
+        <v>-0.119966</v>
       </c>
     </row>
     <row r="998">
@@ -13391,7 +13391,7 @@
         <v>14</v>
       </c>
       <c r="C998" t="n">
-        <v>-0.118137</v>
+        <v>-0.118068</v>
       </c>
     </row>
     <row r="999">
@@ -13404,7 +13404,7 @@
         <v>15</v>
       </c>
       <c r="C999" t="n">
-        <v>-0.113096</v>
+        <v>-0.116828</v>
       </c>
     </row>
     <row r="1000">
@@ -13417,7 +13417,7 @@
         <v>16</v>
       </c>
       <c r="C1000" t="n">
-        <v>-0.11086</v>
+        <v>-0.1089</v>
       </c>
     </row>
     <row r="1001">
@@ -13430,7 +13430,7 @@
         <v>17</v>
       </c>
       <c r="C1001" t="n">
-        <v>-0.104584</v>
+        <v>-0.106322</v>
       </c>
     </row>
     <row r="1002">
@@ -13443,7 +13443,7 @@
         <v>18</v>
       </c>
       <c r="C1002" t="n">
-        <v>-0.10101</v>
+        <v>-0.105569</v>
       </c>
     </row>
     <row r="1003">
@@ -13456,7 +13456,7 @@
         <v>19</v>
       </c>
       <c r="C1003" t="n">
-        <v>-0.09733799999999999</v>
+        <v>-0.104964</v>
       </c>
     </row>
     <row r="1004">
@@ -13469,7 +13469,7 @@
         <v>20</v>
       </c>
       <c r="C1004" t="n">
-        <v>-0.091447</v>
+        <v>-0.104742</v>
       </c>
     </row>
     <row r="1005">
@@ -13482,7 +13482,7 @@
         <v>21</v>
       </c>
       <c r="C1005" t="n">
-        <v>-0.084621</v>
+        <v>-0.102793</v>
       </c>
     </row>
     <row r="1006">
@@ -13495,7 +13495,7 @@
         <v>22</v>
       </c>
       <c r="C1006" t="n">
-        <v>-0.084415</v>
+        <v>-0.096611</v>
       </c>
     </row>
     <row r="1007">
@@ -13508,7 +13508,7 @@
         <v>23</v>
       </c>
       <c r="C1007" t="n">
-        <v>-0.082082</v>
+        <v>-0.095458</v>
       </c>
     </row>
     <row r="1008">
@@ -13521,7 +13521,7 @@
         <v>24</v>
       </c>
       <c r="C1008" t="n">
-        <v>-0.080869</v>
+        <v>-0.09526900000000001</v>
       </c>
     </row>
     <row r="1009">
@@ -13534,7 +13534,7 @@
         <v>25</v>
       </c>
       <c r="C1009" t="n">
-        <v>-0.080454</v>
+        <v>-0.09177299999999999</v>
       </c>
     </row>
     <row r="1010">
@@ -13547,7 +13547,7 @@
         <v>26</v>
       </c>
       <c r="C1010" t="n">
-        <v>-0.080263</v>
+        <v>-0.090211</v>
       </c>
     </row>
     <row r="1011">
@@ -13560,7 +13560,7 @@
         <v>27</v>
       </c>
       <c r="C1011" t="n">
-        <v>-0.079127</v>
+        <v>-0.08869199999999999</v>
       </c>
     </row>
     <row r="1012">
@@ -13573,7 +13573,7 @@
         <v>28</v>
       </c>
       <c r="C1012" t="n">
-        <v>-0.073772</v>
+        <v>-0.087266</v>
       </c>
     </row>
     <row r="1013">
@@ -13586,7 +13586,7 @@
         <v>29</v>
       </c>
       <c r="C1013" t="n">
-        <v>-0.073478</v>
+        <v>-0.08505600000000001</v>
       </c>
     </row>
     <row r="1014">
@@ -13599,7 +13599,7 @@
         <v>30</v>
       </c>
       <c r="C1014" t="n">
-        <v>-0.073322</v>
+        <v>-0.084899</v>
       </c>
     </row>
     <row r="1015">
@@ -13612,7 +13612,7 @@
         <v>31</v>
       </c>
       <c r="C1015" t="n">
-        <v>-0.07230399999999999</v>
+        <v>-0.08489099999999999</v>
       </c>
     </row>
     <row r="1016">
@@ -13625,7 +13625,7 @@
         <v>32</v>
       </c>
       <c r="C1016" t="n">
-        <v>-0.069873</v>
+        <v>-0.0825</v>
       </c>
     </row>
     <row r="1017">
@@ -13638,7 +13638,7 @@
         <v>33</v>
       </c>
       <c r="C1017" t="n">
-        <v>-0.069617</v>
+        <v>-0.08214</v>
       </c>
     </row>
     <row r="1018">
@@ -13651,7 +13651,7 @@
         <v>34</v>
       </c>
       <c r="C1018" t="n">
-        <v>-0.06789199999999999</v>
+        <v>-0.081638</v>
       </c>
     </row>
     <row r="1019">
@@ -13664,7 +13664,7 @@
         <v>35</v>
       </c>
       <c r="C1019" t="n">
-        <v>-0.06777900000000001</v>
+        <v>-0.08075599999999999</v>
       </c>
     </row>
     <row r="1020">
@@ -13677,7 +13677,7 @@
         <v>36</v>
       </c>
       <c r="C1020" t="n">
-        <v>-0.065798</v>
+        <v>-0.07849100000000001</v>
       </c>
     </row>
     <row r="1021">
@@ -13690,7 +13690,7 @@
         <v>37</v>
       </c>
       <c r="C1021" t="n">
-        <v>-0.065207</v>
+        <v>-0.077321</v>
       </c>
     </row>
     <row r="1022">
@@ -13703,7 +13703,7 @@
         <v>38</v>
       </c>
       <c r="C1022" t="n">
-        <v>-0.06479500000000001</v>
+        <v>-0.075324</v>
       </c>
     </row>
     <row r="1023">
@@ -13716,7 +13716,7 @@
         <v>39</v>
       </c>
       <c r="C1023" t="n">
-        <v>-0.063134</v>
+        <v>-0.074294</v>
       </c>
     </row>
     <row r="1024">
@@ -13729,7 +13729,7 @@
         <v>40</v>
       </c>
       <c r="C1024" t="n">
-        <v>-0.060875</v>
+        <v>-0.07222000000000001</v>
       </c>
     </row>
     <row r="1025">
@@ -13742,7 +13742,7 @@
         <v>41</v>
       </c>
       <c r="C1025" t="n">
-        <v>-0.059722</v>
+        <v>-0.068301</v>
       </c>
     </row>
     <row r="1026">
@@ -13755,7 +13755,7 @@
         <v>42</v>
       </c>
       <c r="C1026" t="n">
-        <v>-0.057669</v>
+        <v>-0.067853</v>
       </c>
     </row>
     <row r="1027">
@@ -13768,7 +13768,7 @@
         <v>43</v>
       </c>
       <c r="C1027" t="n">
-        <v>-0.055974</v>
+        <v>-0.066515</v>
       </c>
     </row>
     <row r="1028">
@@ -13781,7 +13781,7 @@
         <v>44</v>
       </c>
       <c r="C1028" t="n">
-        <v>-0.055887</v>
+        <v>-0.065833</v>
       </c>
     </row>
     <row r="1029">
@@ -13794,7 +13794,7 @@
         <v>45</v>
       </c>
       <c r="C1029" t="n">
-        <v>-0.0557</v>
+        <v>-0.06259199999999999</v>
       </c>
     </row>
     <row r="1030">
@@ -13807,7 +13807,7 @@
         <v>46</v>
       </c>
       <c r="C1030" t="n">
-        <v>-0.055601</v>
+        <v>-0.062293</v>
       </c>
     </row>
     <row r="1031">
@@ -13820,7 +13820,7 @@
         <v>47</v>
       </c>
       <c r="C1031" t="n">
-        <v>-0.05454</v>
+        <v>-0.062047</v>
       </c>
     </row>
     <row r="1032">
@@ -13833,7 +13833,7 @@
         <v>48</v>
       </c>
       <c r="C1032" t="n">
-        <v>-0.053417</v>
+        <v>-0.061861</v>
       </c>
     </row>
     <row r="1033">
@@ -13846,7 +13846,7 @@
         <v>49</v>
       </c>
       <c r="C1033" t="n">
-        <v>-0.053085</v>
+        <v>-0.060617</v>
       </c>
     </row>
     <row r="1034">
@@ -13859,7 +13859,7 @@
         <v>50</v>
       </c>
       <c r="C1034" t="n">
-        <v>-0.051565</v>
+        <v>-0.060423</v>
       </c>
     </row>
     <row r="1035">
@@ -13872,7 +13872,7 @@
         <v>51</v>
       </c>
       <c r="C1035" t="n">
-        <v>-0.051436</v>
+        <v>-0.060382</v>
       </c>
     </row>
     <row r="1036">
@@ -13885,7 +13885,7 @@
         <v>52</v>
       </c>
       <c r="C1036" t="n">
-        <v>-0.050671</v>
+        <v>-0.060179</v>
       </c>
     </row>
     <row r="1037">
@@ -13898,7 +13898,7 @@
         <v>53</v>
       </c>
       <c r="C1037" t="n">
-        <v>-0.049549</v>
+        <v>-0.057973</v>
       </c>
     </row>
     <row r="1038">
@@ -13911,7 +13911,7 @@
         <v>54</v>
       </c>
       <c r="C1038" t="n">
-        <v>-0.04947</v>
+        <v>-0.05769</v>
       </c>
     </row>
     <row r="1039">
@@ -13924,7 +13924,7 @@
         <v>55</v>
       </c>
       <c r="C1039" t="n">
-        <v>-0.048572</v>
+        <v>-0.056224</v>
       </c>
     </row>
     <row r="1040">
@@ -13937,7 +13937,7 @@
         <v>56</v>
       </c>
       <c r="C1040" t="n">
-        <v>-0.047992</v>
+        <v>-0.05582</v>
       </c>
     </row>
     <row r="1041">
@@ -13950,7 +13950,7 @@
         <v>57</v>
       </c>
       <c r="C1041" t="n">
-        <v>-0.044754</v>
+        <v>-0.054978</v>
       </c>
     </row>
     <row r="1042">
@@ -13963,7 +13963,7 @@
         <v>58</v>
       </c>
       <c r="C1042" t="n">
-        <v>-0.044516</v>
+        <v>-0.054905</v>
       </c>
     </row>
     <row r="1043">
@@ -13976,7 +13976,7 @@
         <v>59</v>
       </c>
       <c r="C1043" t="n">
-        <v>-0.044122</v>
+        <v>-0.054477</v>
       </c>
     </row>
     <row r="1044">
@@ -13989,7 +13989,7 @@
         <v>60</v>
       </c>
       <c r="C1044" t="n">
-        <v>-0.04388</v>
+        <v>-0.053681</v>
       </c>
     </row>
     <row r="1045">
@@ -14002,7 +14002,7 @@
         <v>61</v>
       </c>
       <c r="C1045" t="n">
-        <v>-0.043073</v>
+        <v>-0.053206</v>
       </c>
     </row>
     <row r="1046">
@@ -14015,7 +14015,7 @@
         <v>62</v>
       </c>
       <c r="C1046" t="n">
-        <v>-0.042928</v>
+        <v>-0.052425</v>
       </c>
     </row>
     <row r="1047">
@@ -14028,7 +14028,7 @@
         <v>63</v>
       </c>
       <c r="C1047" t="n">
-        <v>-0.042216</v>
+        <v>-0.051707</v>
       </c>
     </row>
     <row r="1048">
@@ -14041,7 +14041,7 @@
         <v>64</v>
       </c>
       <c r="C1048" t="n">
-        <v>-0.041537</v>
+        <v>-0.050791</v>
       </c>
     </row>
     <row r="1049">
@@ -14054,7 +14054,7 @@
         <v>65</v>
       </c>
       <c r="C1049" t="n">
-        <v>-0.040788</v>
+        <v>-0.050269</v>
       </c>
     </row>
     <row r="1050">
@@ -14067,7 +14067,7 @@
         <v>66</v>
       </c>
       <c r="C1050" t="n">
-        <v>-0.040451</v>
+        <v>-0.04922</v>
       </c>
     </row>
     <row r="1051">
@@ -14080,7 +14080,7 @@
         <v>67</v>
       </c>
       <c r="C1051" t="n">
-        <v>-0.03997</v>
+        <v>-0.049098</v>
       </c>
     </row>
     <row r="1052">
@@ -14093,7 +14093,7 @@
         <v>68</v>
       </c>
       <c r="C1052" t="n">
-        <v>-0.039898</v>
+        <v>-0.048813</v>
       </c>
     </row>
     <row r="1053">
@@ -14106,7 +14106,7 @@
         <v>69</v>
       </c>
       <c r="C1053" t="n">
-        <v>-0.039862</v>
+        <v>-0.047993</v>
       </c>
     </row>
     <row r="1054">
@@ -14119,7 +14119,7 @@
         <v>70</v>
       </c>
       <c r="C1054" t="n">
-        <v>-0.039544</v>
+        <v>-0.047976</v>
       </c>
     </row>
     <row r="1055">
@@ -14132,7 +14132,7 @@
         <v>71</v>
       </c>
       <c r="C1055" t="n">
-        <v>-0.039465</v>
+        <v>-0.047838</v>
       </c>
     </row>
     <row r="1056">
@@ -14145,7 +14145,7 @@
         <v>72</v>
       </c>
       <c r="C1056" t="n">
-        <v>-0.03884</v>
+        <v>-0.047831</v>
       </c>
     </row>
     <row r="1057">
@@ -14158,7 +14158,7 @@
         <v>73</v>
       </c>
       <c r="C1057" t="n">
-        <v>-0.038469</v>
+        <v>-0.04718</v>
       </c>
     </row>
     <row r="1058">
@@ -14171,7 +14171,7 @@
         <v>74</v>
       </c>
       <c r="C1058" t="n">
-        <v>-0.038412</v>
+        <v>-0.046835</v>
       </c>
     </row>
     <row r="1059">
@@ -14184,7 +14184,7 @@
         <v>75</v>
       </c>
       <c r="C1059" t="n">
-        <v>-0.037751</v>
+        <v>-0.046388</v>
       </c>
     </row>
     <row r="1060">
@@ -14197,7 +14197,7 @@
         <v>76</v>
       </c>
       <c r="C1060" t="n">
-        <v>-0.037553</v>
+        <v>-0.046241</v>
       </c>
     </row>
     <row r="1061">
@@ -14210,7 +14210,7 @@
         <v>77</v>
       </c>
       <c r="C1061" t="n">
-        <v>-0.036022</v>
+        <v>-0.045205</v>
       </c>
     </row>
     <row r="1062">
@@ -14223,7 +14223,7 @@
         <v>78</v>
       </c>
       <c r="C1062" t="n">
-        <v>-0.035931</v>
+        <v>-0.0449</v>
       </c>
     </row>
     <row r="1063">
@@ -14236,7 +14236,7 @@
         <v>79</v>
       </c>
       <c r="C1063" t="n">
-        <v>-0.035059</v>
+        <v>-0.044864</v>
       </c>
     </row>
     <row r="1064">
@@ -14249,7 +14249,7 @@
         <v>80</v>
       </c>
       <c r="C1064" t="n">
-        <v>-0.03495</v>
+        <v>-0.04424</v>
       </c>
     </row>
     <row r="1065">
@@ -14262,7 +14262,7 @@
         <v>81</v>
       </c>
       <c r="C1065" t="n">
-        <v>-0.034869</v>
+        <v>-0.044186</v>
       </c>
     </row>
     <row r="1066">
@@ -14275,7 +14275,7 @@
         <v>82</v>
       </c>
       <c r="C1066" t="n">
-        <v>-0.034298</v>
+        <v>-0.043952</v>
       </c>
     </row>
     <row r="1067">
@@ -14288,7 +14288,7 @@
         <v>83</v>
       </c>
       <c r="C1067" t="n">
-        <v>-0.033114</v>
+        <v>-0.043377</v>
       </c>
     </row>
     <row r="1068">
@@ -14301,7 +14301,7 @@
         <v>84</v>
       </c>
       <c r="C1068" t="n">
-        <v>-0.03254</v>
+        <v>-0.04332</v>
       </c>
     </row>
     <row r="1069">
@@ -14314,7 +14314,7 @@
         <v>85</v>
       </c>
       <c r="C1069" t="n">
-        <v>-0.032503</v>
+        <v>-0.043047</v>
       </c>
     </row>
     <row r="1070">
@@ -14327,7 +14327,7 @@
         <v>86</v>
       </c>
       <c r="C1070" t="n">
-        <v>-0.032236</v>
+        <v>-0.042834</v>
       </c>
     </row>
     <row r="1071">
@@ -14340,7 +14340,7 @@
         <v>87</v>
       </c>
       <c r="C1071" t="n">
-        <v>-0.032204</v>
+        <v>-0.041444</v>
       </c>
     </row>
     <row r="1072">
@@ -14353,7 +14353,7 @@
         <v>88</v>
       </c>
       <c r="C1072" t="n">
-        <v>-0.032177</v>
+        <v>-0.040936</v>
       </c>
     </row>
     <row r="1073">
@@ -14366,7 +14366,7 @@
         <v>89</v>
       </c>
       <c r="C1073" t="n">
-        <v>-0.032119</v>
+        <v>-0.040523</v>
       </c>
     </row>
     <row r="1074">
@@ -14379,7 +14379,7 @@
         <v>90</v>
       </c>
       <c r="C1074" t="n">
-        <v>-0.032026</v>
+        <v>-0.040277</v>
       </c>
     </row>
     <row r="1075">
@@ -14392,7 +14392,7 @@
         <v>91</v>
       </c>
       <c r="C1075" t="n">
-        <v>-0.031778</v>
+        <v>-0.039593</v>
       </c>
     </row>
     <row r="1076">
@@ -14405,7 +14405,7 @@
         <v>92</v>
       </c>
       <c r="C1076" t="n">
-        <v>-0.031642</v>
+        <v>-0.039498</v>
       </c>
     </row>
     <row r="1077">
@@ -14418,7 +14418,7 @@
         <v>93</v>
       </c>
       <c r="C1077" t="n">
-        <v>-0.031586</v>
+        <v>-0.039169</v>
       </c>
     </row>
     <row r="1078">
@@ -14431,7 +14431,7 @@
         <v>94</v>
       </c>
       <c r="C1078" t="n">
-        <v>-0.031254</v>
+        <v>-0.039113</v>
       </c>
     </row>
     <row r="1079">
@@ -14444,7 +14444,7 @@
         <v>95</v>
       </c>
       <c r="C1079" t="n">
-        <v>-0.030732</v>
+        <v>-0.038739</v>
       </c>
     </row>
     <row r="1080">
@@ -14457,7 +14457,7 @@
         <v>96</v>
       </c>
       <c r="C1080" t="n">
-        <v>-0.02881</v>
+        <v>-0.037891</v>
       </c>
     </row>
     <row r="1081">
@@ -14470,7 +14470,7 @@
         <v>97</v>
       </c>
       <c r="C1081" t="n">
-        <v>-0.028534</v>
+        <v>-0.035866</v>
       </c>
     </row>
     <row r="1082">
@@ -14483,7 +14483,7 @@
         <v>98</v>
       </c>
       <c r="C1082" t="n">
-        <v>-0.027869</v>
+        <v>-0.035534</v>
       </c>
     </row>
     <row r="1083">
@@ -14496,7 +14496,7 @@
         <v>99</v>
       </c>
       <c r="C1083" t="n">
-        <v>-0.027334</v>
+        <v>-0.035292</v>
       </c>
     </row>
     <row r="1084">
@@ -14509,7 +14509,7 @@
         <v>100</v>
       </c>
       <c r="C1084" t="n">
-        <v>-0.027288</v>
+        <v>-0.03516</v>
       </c>
     </row>
     <row r="1085">
@@ -14522,7 +14522,7 @@
         <v>101</v>
       </c>
       <c r="C1085" t="n">
-        <v>-0.027263</v>
+        <v>-0.033837</v>
       </c>
     </row>
     <row r="1086">
@@ -14535,7 +14535,7 @@
         <v>102</v>
       </c>
       <c r="C1086" t="n">
-        <v>-0.026587</v>
+        <v>-0.032704</v>
       </c>
     </row>
     <row r="1087">
@@ -14548,7 +14548,7 @@
         <v>103</v>
       </c>
       <c r="C1087" t="n">
-        <v>-0.026448</v>
+        <v>-0.031955</v>
       </c>
     </row>
     <row r="1088">
@@ -14561,7 +14561,7 @@
         <v>104</v>
       </c>
       <c r="C1088" t="n">
-        <v>-0.026342</v>
+        <v>-0.031263</v>
       </c>
     </row>
     <row r="1089">
@@ -14574,7 +14574,7 @@
         <v>105</v>
       </c>
       <c r="C1089" t="n">
-        <v>-0.026262</v>
+        <v>-0.031116</v>
       </c>
     </row>
     <row r="1090">
@@ -14587,7 +14587,7 @@
         <v>106</v>
       </c>
       <c r="C1090" t="n">
-        <v>-0.026198</v>
+        <v>-0.031097</v>
       </c>
     </row>
     <row r="1091">
@@ -14600,7 +14600,7 @@
         <v>107</v>
       </c>
       <c r="C1091" t="n">
-        <v>-0.02593</v>
+        <v>-0.030931</v>
       </c>
     </row>
     <row r="1092">
@@ -14613,7 +14613,7 @@
         <v>108</v>
       </c>
       <c r="C1092" t="n">
-        <v>-0.0257</v>
+        <v>-0.030919</v>
       </c>
     </row>
     <row r="1093">
@@ -14626,7 +14626,7 @@
         <v>109</v>
       </c>
       <c r="C1093" t="n">
-        <v>-0.025514</v>
+        <v>-0.030751</v>
       </c>
     </row>
     <row r="1094">
@@ -14639,7 +14639,7 @@
         <v>110</v>
       </c>
       <c r="C1094" t="n">
-        <v>-0.025354</v>
+        <v>-0.029916</v>
       </c>
     </row>
     <row r="1095">
@@ -14652,7 +14652,7 @@
         <v>111</v>
       </c>
       <c r="C1095" t="n">
-        <v>-0.025046</v>
+        <v>-0.029208</v>
       </c>
     </row>
     <row r="1096">
@@ -14665,7 +14665,7 @@
         <v>112</v>
       </c>
       <c r="C1096" t="n">
-        <v>-0.02398</v>
+        <v>-0.029063</v>
       </c>
     </row>
     <row r="1097">
@@ -14678,7 +14678,7 @@
         <v>113</v>
       </c>
       <c r="C1097" t="n">
-        <v>-0.023819</v>
+        <v>-0.02855</v>
       </c>
     </row>
     <row r="1098">
@@ -14691,7 +14691,7 @@
         <v>114</v>
       </c>
       <c r="C1098" t="n">
-        <v>-0.023241</v>
+        <v>-0.028125</v>
       </c>
     </row>
     <row r="1099">
@@ -14704,7 +14704,7 @@
         <v>115</v>
       </c>
       <c r="C1099" t="n">
-        <v>-0.022834</v>
+        <v>-0.027407</v>
       </c>
     </row>
     <row r="1100">
@@ -14717,7 +14717,7 @@
         <v>116</v>
       </c>
       <c r="C1100" t="n">
-        <v>-0.022694</v>
+        <v>-0.027013</v>
       </c>
     </row>
     <row r="1101">
@@ -14730,7 +14730,7 @@
         <v>117</v>
       </c>
       <c r="C1101" t="n">
-        <v>-0.022676</v>
+        <v>-0.026967</v>
       </c>
     </row>
     <row r="1102">
@@ -14743,7 +14743,7 @@
         <v>118</v>
       </c>
       <c r="C1102" t="n">
-        <v>-0.0221</v>
+        <v>-0.026764</v>
       </c>
     </row>
     <row r="1103">
@@ -14756,7 +14756,7 @@
         <v>119</v>
       </c>
       <c r="C1103" t="n">
-        <v>-0.021763</v>
+        <v>-0.026244</v>
       </c>
     </row>
     <row r="1104">
@@ -14769,7 +14769,7 @@
         <v>120</v>
       </c>
       <c r="C1104" t="n">
-        <v>-0.02135</v>
+        <v>-0.025935</v>
       </c>
     </row>
     <row r="1105">
@@ -14782,7 +14782,7 @@
         <v>121</v>
       </c>
       <c r="C1105" t="n">
-        <v>-0.021071</v>
+        <v>-0.02573</v>
       </c>
     </row>
     <row r="1106">
@@ -14795,7 +14795,7 @@
         <v>122</v>
       </c>
       <c r="C1106" t="n">
-        <v>-0.020867</v>
+        <v>-0.025514</v>
       </c>
     </row>
     <row r="1107">
@@ -14808,7 +14808,7 @@
         <v>123</v>
       </c>
       <c r="C1107" t="n">
-        <v>-0.020807</v>
+        <v>-0.024997</v>
       </c>
     </row>
     <row r="1108">
@@ -14821,7 +14821,7 @@
         <v>124</v>
       </c>
       <c r="C1108" t="n">
-        <v>-0.020782</v>
+        <v>-0.024767</v>
       </c>
     </row>
     <row r="1109">
@@ -14834,7 +14834,7 @@
         <v>125</v>
       </c>
       <c r="C1109" t="n">
-        <v>-0.020471</v>
+        <v>-0.024606</v>
       </c>
     </row>
     <row r="1110">
@@ -14847,7 +14847,7 @@
         <v>126</v>
       </c>
       <c r="C1110" t="n">
-        <v>-0.020396</v>
+        <v>-0.024342</v>
       </c>
     </row>
     <row r="1111">
@@ -14860,7 +14860,7 @@
         <v>127</v>
       </c>
       <c r="C1111" t="n">
-        <v>-0.020021</v>
+        <v>-0.024101</v>
       </c>
     </row>
     <row r="1112">
@@ -14873,7 +14873,7 @@
         <v>128</v>
       </c>
       <c r="C1112" t="n">
-        <v>-0.019971</v>
+        <v>-0.023783</v>
       </c>
     </row>
     <row r="1113">
@@ -14886,7 +14886,7 @@
         <v>129</v>
       </c>
       <c r="C1113" t="n">
-        <v>-0.019548</v>
+        <v>-0.023628</v>
       </c>
     </row>
     <row r="1114">
@@ -14899,7 +14899,7 @@
         <v>130</v>
       </c>
       <c r="C1114" t="n">
-        <v>-0.019544</v>
+        <v>-0.023179</v>
       </c>
     </row>
     <row r="1115">
@@ -14912,7 +14912,7 @@
         <v>131</v>
       </c>
       <c r="C1115" t="n">
-        <v>-0.019227</v>
+        <v>-0.021418</v>
       </c>
     </row>
     <row r="1116">
@@ -14925,7 +14925,7 @@
         <v>132</v>
       </c>
       <c r="C1116" t="n">
-        <v>-0.018974</v>
+        <v>-0.020747</v>
       </c>
     </row>
     <row r="1117">
@@ -14938,7 +14938,7 @@
         <v>133</v>
       </c>
       <c r="C1117" t="n">
-        <v>-0.01869</v>
+        <v>-0.020354</v>
       </c>
     </row>
     <row r="1118">
@@ -14951,7 +14951,7 @@
         <v>134</v>
       </c>
       <c r="C1118" t="n">
-        <v>-0.018434</v>
+        <v>-0.019221</v>
       </c>
     </row>
     <row r="1119">
@@ -14964,7 +14964,7 @@
         <v>135</v>
       </c>
       <c r="C1119" t="n">
-        <v>-0.018158</v>
+        <v>-0.019146</v>
       </c>
     </row>
     <row r="1120">
@@ -14977,7 +14977,7 @@
         <v>136</v>
       </c>
       <c r="C1120" t="n">
-        <v>-0.018117</v>
+        <v>-0.018463</v>
       </c>
     </row>
     <row r="1121">
@@ -14990,7 +14990,7 @@
         <v>137</v>
       </c>
       <c r="C1121" t="n">
-        <v>-0.018082</v>
+        <v>-0.018448</v>
       </c>
     </row>
     <row r="1122">
@@ -15003,7 +15003,7 @@
         <v>138</v>
       </c>
       <c r="C1122" t="n">
-        <v>-0.017647</v>
+        <v>-0.018366</v>
       </c>
     </row>
     <row r="1123">
@@ -15016,7 +15016,7 @@
         <v>139</v>
       </c>
       <c r="C1123" t="n">
-        <v>-0.017569</v>
+        <v>-0.018233</v>
       </c>
     </row>
     <row r="1124">
@@ -15029,7 +15029,7 @@
         <v>140</v>
       </c>
       <c r="C1124" t="n">
-        <v>-0.017519</v>
+        <v>-0.017774</v>
       </c>
     </row>
     <row r="1125">
@@ -15042,7 +15042,7 @@
         <v>141</v>
       </c>
       <c r="C1125" t="n">
-        <v>-0.017123</v>
+        <v>-0.017673</v>
       </c>
     </row>
     <row r="1126">
@@ -15055,7 +15055,7 @@
         <v>142</v>
       </c>
       <c r="C1126" t="n">
-        <v>-0.016975</v>
+        <v>-0.0175</v>
       </c>
     </row>
     <row r="1127">
@@ -15068,7 +15068,7 @@
         <v>143</v>
       </c>
       <c r="C1127" t="n">
-        <v>-0.016909</v>
+        <v>-0.017451</v>
       </c>
     </row>
     <row r="1128">
@@ -15081,7 +15081,7 @@
         <v>144</v>
       </c>
       <c r="C1128" t="n">
-        <v>-0.016747</v>
+        <v>-0.017445</v>
       </c>
     </row>
     <row r="1129">
@@ -15094,7 +15094,7 @@
         <v>145</v>
       </c>
       <c r="C1129" t="n">
-        <v>-0.016446</v>
+        <v>-0.017159</v>
       </c>
     </row>
     <row r="1130">
@@ -15107,7 +15107,7 @@
         <v>146</v>
       </c>
       <c r="C1130" t="n">
-        <v>-0.016278</v>
+        <v>-0.016977</v>
       </c>
     </row>
     <row r="1131">
@@ -15120,7 +15120,7 @@
         <v>147</v>
       </c>
       <c r="C1131" t="n">
-        <v>-0.015646</v>
+        <v>-0.016902</v>
       </c>
     </row>
     <row r="1132">
@@ -15133,7 +15133,7 @@
         <v>148</v>
       </c>
       <c r="C1132" t="n">
-        <v>-0.015102</v>
+        <v>-0.016845</v>
       </c>
     </row>
     <row r="1133">
@@ -15146,7 +15146,7 @@
         <v>149</v>
       </c>
       <c r="C1133" t="n">
-        <v>-0.014933</v>
+        <v>-0.016799</v>
       </c>
     </row>
     <row r="1134">
@@ -15159,7 +15159,7 @@
         <v>150</v>
       </c>
       <c r="C1134" t="n">
-        <v>-0.013853</v>
+        <v>-0.016742</v>
       </c>
     </row>
     <row r="1135">
@@ -15172,7 +15172,7 @@
         <v>151</v>
       </c>
       <c r="C1135" t="n">
-        <v>-0.013546</v>
+        <v>-0.016634</v>
       </c>
     </row>
     <row r="1136">
@@ -15185,7 +15185,7 @@
         <v>152</v>
       </c>
       <c r="C1136" t="n">
-        <v>-0.012823</v>
+        <v>-0.016453</v>
       </c>
     </row>
     <row r="1137">
@@ -15198,7 +15198,7 @@
         <v>153</v>
       </c>
       <c r="C1137" t="n">
-        <v>-0.012822</v>
+        <v>-0.016122</v>
       </c>
     </row>
     <row r="1138">
@@ -15211,7 +15211,7 @@
         <v>154</v>
       </c>
       <c r="C1138" t="n">
-        <v>-0.012469</v>
+        <v>-0.014909</v>
       </c>
     </row>
     <row r="1139">
@@ -15224,7 +15224,7 @@
         <v>155</v>
       </c>
       <c r="C1139" t="n">
-        <v>-0.012303</v>
+        <v>-0.014723</v>
       </c>
     </row>
     <row r="1140">
@@ -15237,7 +15237,7 @@
         <v>156</v>
       </c>
       <c r="C1140" t="n">
-        <v>-0.011899</v>
+        <v>-0.014591</v>
       </c>
     </row>
     <row r="1141">
@@ -15250,7 +15250,7 @@
         <v>157</v>
       </c>
       <c r="C1141" t="n">
-        <v>-0.011862</v>
+        <v>-0.014471</v>
       </c>
     </row>
     <row r="1142">
@@ -15263,7 +15263,7 @@
         <v>158</v>
       </c>
       <c r="C1142" t="n">
-        <v>-0.011834</v>
+        <v>-0.014403</v>
       </c>
     </row>
     <row r="1143">
@@ -15276,7 +15276,7 @@
         <v>159</v>
       </c>
       <c r="C1143" t="n">
-        <v>-0.011744</v>
+        <v>-0.013998</v>
       </c>
     </row>
     <row r="1144">
@@ -15289,7 +15289,7 @@
         <v>160</v>
       </c>
       <c r="C1144" t="n">
-        <v>-0.011734</v>
+        <v>-0.013485</v>
       </c>
     </row>
     <row r="1145">
@@ -15302,7 +15302,7 @@
         <v>161</v>
       </c>
       <c r="C1145" t="n">
-        <v>-0.011682</v>
+        <v>-0.012974</v>
       </c>
     </row>
     <row r="1146">
@@ -15315,7 +15315,7 @@
         <v>162</v>
       </c>
       <c r="C1146" t="n">
-        <v>-0.011643</v>
+        <v>-0.012399</v>
       </c>
     </row>
     <row r="1147">
@@ -15328,7 +15328,7 @@
         <v>163</v>
       </c>
       <c r="C1147" t="n">
-        <v>-0.011349</v>
+        <v>-0.012384</v>
       </c>
     </row>
     <row r="1148">
@@ -15341,7 +15341,7 @@
         <v>164</v>
       </c>
       <c r="C1148" t="n">
-        <v>-0.011297</v>
+        <v>-0.012143</v>
       </c>
     </row>
     <row r="1149">
@@ -15354,7 +15354,7 @@
         <v>165</v>
       </c>
       <c r="C1149" t="n">
-        <v>-0.011107</v>
+        <v>-0.012094</v>
       </c>
     </row>
     <row r="1150">
@@ -15367,7 +15367,7 @@
         <v>166</v>
       </c>
       <c r="C1150" t="n">
-        <v>-0.010664</v>
+        <v>-0.011883</v>
       </c>
     </row>
     <row r="1151">
@@ -15380,7 +15380,7 @@
         <v>167</v>
       </c>
       <c r="C1151" t="n">
-        <v>-0.010598</v>
+        <v>-0.011013</v>
       </c>
     </row>
     <row r="1152">
@@ -15393,7 +15393,7 @@
         <v>168</v>
       </c>
       <c r="C1152" t="n">
-        <v>-0.010442</v>
+        <v>-0.010273</v>
       </c>
     </row>
     <row r="1153">
@@ -15406,7 +15406,7 @@
         <v>169</v>
       </c>
       <c r="C1153" t="n">
-        <v>-0.009903</v>
+        <v>-0.010007</v>
       </c>
     </row>
     <row r="1154">
@@ -15419,7 +15419,7 @@
         <v>170</v>
       </c>
       <c r="C1154" t="n">
-        <v>-0.009815000000000001</v>
+        <v>-0.009513000000000001</v>
       </c>
     </row>
     <row r="1155">
@@ -15432,7 +15432,7 @@
         <v>171</v>
       </c>
       <c r="C1155" t="n">
-        <v>-0.009415</v>
+        <v>-0.009386</v>
       </c>
     </row>
     <row r="1156">
@@ -15445,7 +15445,7 @@
         <v>172</v>
       </c>
       <c r="C1156" t="n">
-        <v>-0.008984000000000001</v>
+        <v>-0.009254999999999999</v>
       </c>
     </row>
     <row r="1157">
@@ -15458,7 +15458,7 @@
         <v>173</v>
       </c>
       <c r="C1157" t="n">
-        <v>-0.008487</v>
+        <v>-0.008460000000000001</v>
       </c>
     </row>
     <row r="1158">
@@ -15471,7 +15471,7 @@
         <v>174</v>
       </c>
       <c r="C1158" t="n">
-        <v>-0.008352999999999999</v>
+        <v>-0.008441000000000001</v>
       </c>
     </row>
     <row r="1159">
@@ -15484,7 +15484,7 @@
         <v>175</v>
       </c>
       <c r="C1159" t="n">
-        <v>-0.008252000000000001</v>
+        <v>-0.008003</v>
       </c>
     </row>
     <row r="1160">
@@ -15497,7 +15497,7 @@
         <v>176</v>
       </c>
       <c r="C1160" t="n">
-        <v>-0.008233000000000001</v>
+        <v>-0.007982</v>
       </c>
     </row>
     <row r="1161">
@@ -15510,7 +15510,7 @@
         <v>177</v>
       </c>
       <c r="C1161" t="n">
-        <v>-0.008174000000000001</v>
+        <v>-0.007960999999999999</v>
       </c>
     </row>
     <row r="1162">
@@ -15523,7 +15523,7 @@
         <v>178</v>
       </c>
       <c r="C1162" t="n">
-        <v>-0.007525</v>
+        <v>-0.007625</v>
       </c>
     </row>
     <row r="1163">
@@ -15536,7 +15536,7 @@
         <v>179</v>
       </c>
       <c r="C1163" t="n">
-        <v>-0.00717</v>
+        <v>-0.007247</v>
       </c>
     </row>
     <row r="1164">
@@ -15549,7 +15549,7 @@
         <v>180</v>
       </c>
       <c r="C1164" t="n">
-        <v>-0.007104</v>
+        <v>-0.007128</v>
       </c>
     </row>
     <row r="1165">
@@ -15562,7 +15562,7 @@
         <v>181</v>
       </c>
       <c r="C1165" t="n">
-        <v>-0.006938</v>
+        <v>-0.007021</v>
       </c>
     </row>
     <row r="1166">
@@ -15575,7 +15575,7 @@
         <v>182</v>
       </c>
       <c r="C1166" t="n">
-        <v>-0.006873</v>
+        <v>-0.006645</v>
       </c>
     </row>
     <row r="1167">
@@ -15588,7 +15588,7 @@
         <v>183</v>
       </c>
       <c r="C1167" t="n">
-        <v>-0.005894</v>
+        <v>-0.006461</v>
       </c>
     </row>
     <row r="1168">
@@ -15601,7 +15601,7 @@
         <v>184</v>
       </c>
       <c r="C1168" t="n">
-        <v>-0.005614</v>
+        <v>-0.005941</v>
       </c>
     </row>
     <row r="1169">
@@ -15614,7 +15614,7 @@
         <v>185</v>
       </c>
       <c r="C1169" t="n">
-        <v>-0.005242</v>
+        <v>-0.005933</v>
       </c>
     </row>
     <row r="1170">
@@ -15627,7 +15627,7 @@
         <v>186</v>
       </c>
       <c r="C1170" t="n">
-        <v>-0.005174</v>
+        <v>-0.005514</v>
       </c>
     </row>
     <row r="1171">
@@ -15640,7 +15640,7 @@
         <v>187</v>
       </c>
       <c r="C1171" t="n">
-        <v>-0.00517</v>
+        <v>-0.004923</v>
       </c>
     </row>
     <row r="1172">
@@ -15653,7 +15653,7 @@
         <v>188</v>
       </c>
       <c r="C1172" t="n">
-        <v>-0.005044</v>
+        <v>-0.004634</v>
       </c>
     </row>
     <row r="1173">
@@ -15666,7 +15666,7 @@
         <v>189</v>
       </c>
       <c r="C1173" t="n">
-        <v>-0.005026</v>
+        <v>-0.004446</v>
       </c>
     </row>
     <row r="1174">
@@ -15679,7 +15679,7 @@
         <v>190</v>
       </c>
       <c r="C1174" t="n">
-        <v>-0.004856</v>
+        <v>-0.004362</v>
       </c>
     </row>
     <row r="1175">
@@ -15692,7 +15692,7 @@
         <v>191</v>
       </c>
       <c r="C1175" t="n">
-        <v>-0.004756</v>
+        <v>-0.004008</v>
       </c>
     </row>
     <row r="1176">
@@ -15705,7 +15705,7 @@
         <v>192</v>
       </c>
       <c r="C1176" t="n">
-        <v>-0.004345</v>
+        <v>-0.003388</v>
       </c>
     </row>
     <row r="1177">
@@ -15718,7 +15718,7 @@
         <v>193</v>
       </c>
       <c r="C1177" t="n">
-        <v>-0.00404</v>
+        <v>-0.003041</v>
       </c>
     </row>
     <row r="1178">
@@ -15731,7 +15731,7 @@
         <v>194</v>
       </c>
       <c r="C1178" t="n">
-        <v>-0.004008</v>
+        <v>-0.003025</v>
       </c>
     </row>
     <row r="1179">
@@ -15744,7 +15744,7 @@
         <v>195</v>
       </c>
       <c r="C1179" t="n">
-        <v>-0.003908</v>
+        <v>-0.002754</v>
       </c>
     </row>
     <row r="1180">
@@ -15757,7 +15757,7 @@
         <v>196</v>
       </c>
       <c r="C1180" t="n">
-        <v>-0.003777</v>
+        <v>-0.002701</v>
       </c>
     </row>
     <row r="1181">
@@ -15770,7 +15770,7 @@
         <v>197</v>
       </c>
       <c r="C1181" t="n">
-        <v>-0.00363</v>
+        <v>-0.002148</v>
       </c>
     </row>
     <row r="1182">
@@ -15783,7 +15783,7 @@
         <v>198</v>
       </c>
       <c r="C1182" t="n">
-        <v>-0.003182</v>
+        <v>-0.001595</v>
       </c>
     </row>
     <row r="1183">
@@ -15796,7 +15796,7 @@
         <v>199</v>
       </c>
       <c r="C1183" t="n">
-        <v>-0.003094</v>
+        <v>-0.001466</v>
       </c>
     </row>
     <row r="1184">
@@ -15809,7 +15809,7 @@
         <v>200</v>
       </c>
       <c r="C1184" t="n">
-        <v>-0.003066</v>
+        <v>-0.001046</v>
       </c>
     </row>
     <row r="1185">
@@ -15822,7 +15822,7 @@
         <v>201</v>
       </c>
       <c r="C1185" t="n">
-        <v>-0.003017</v>
+        <v>-0.000947</v>
       </c>
     </row>
     <row r="1186">
@@ -15835,7 +15835,7 @@
         <v>202</v>
       </c>
       <c r="C1186" t="n">
-        <v>-0.002714</v>
+        <v>-0.000829</v>
       </c>
     </row>
     <row r="1187">
@@ -15848,7 +15848,7 @@
         <v>203</v>
       </c>
       <c r="C1187" t="n">
-        <v>-0.002645</v>
+        <v>-0.000606</v>
       </c>
     </row>
     <row r="1188">
@@ -15861,7 +15861,7 @@
         <v>204</v>
       </c>
       <c r="C1188" t="n">
-        <v>-0.002596</v>
+        <v>-0.000414</v>
       </c>
     </row>
     <row r="1189">
@@ -15874,7 +15874,7 @@
         <v>205</v>
       </c>
       <c r="C1189" t="n">
-        <v>-0.002523</v>
+        <v>-0.000371</v>
       </c>
     </row>
     <row r="1190">
@@ -15887,7 +15887,7 @@
         <v>206</v>
       </c>
       <c r="C1190" t="n">
-        <v>-0.002445</v>
+        <v>0.000487</v>
       </c>
     </row>
     <row r="1191">
@@ -15900,7 +15900,7 @@
         <v>207</v>
       </c>
       <c r="C1191" t="n">
-        <v>-0.002221</v>
+        <v>0.000497</v>
       </c>
     </row>
     <row r="1192">
@@ -15913,7 +15913,7 @@
         <v>208</v>
       </c>
       <c r="C1192" t="n">
-        <v>-0.002132</v>
+        <v>0.001697</v>
       </c>
     </row>
     <row r="1193">
@@ -15926,7 +15926,7 @@
         <v>209</v>
       </c>
       <c r="C1193" t="n">
-        <v>-0.00213</v>
+        <v>0.001891</v>
       </c>
     </row>
     <row r="1194">
@@ -15939,7 +15939,7 @@
         <v>210</v>
       </c>
       <c r="C1194" t="n">
-        <v>-0.001918</v>
+        <v>0.002469</v>
       </c>
     </row>
     <row r="1195">
@@ -15952,7 +15952,7 @@
         <v>211</v>
       </c>
       <c r="C1195" t="n">
-        <v>-0.001551</v>
+        <v>0.002527</v>
       </c>
     </row>
     <row r="1196">
@@ -15965,7 +15965,7 @@
         <v>212</v>
       </c>
       <c r="C1196" t="n">
-        <v>-0.001494</v>
+        <v>0.002808</v>
       </c>
     </row>
     <row r="1197">
@@ -15978,7 +15978,7 @@
         <v>213</v>
       </c>
       <c r="C1197" t="n">
-        <v>-0.001421</v>
+        <v>0.003707</v>
       </c>
     </row>
     <row r="1198">
@@ -15991,7 +15991,7 @@
         <v>214</v>
       </c>
       <c r="C1198" t="n">
-        <v>-0.000484</v>
+        <v>0.00379</v>
       </c>
     </row>
     <row r="1199">
@@ -16004,7 +16004,7 @@
         <v>215</v>
       </c>
       <c r="C1199" t="n">
-        <v>-0.000437</v>
+        <v>0.004029</v>
       </c>
     </row>
     <row r="1200">
@@ -16017,7 +16017,7 @@
         <v>216</v>
       </c>
       <c r="C1200" t="n">
-        <v>-0.000316</v>
+        <v>0.004072</v>
       </c>
     </row>
     <row r="1201">
@@ -16030,7 +16030,7 @@
         <v>217</v>
       </c>
       <c r="C1201" t="n">
-        <v>0</v>
+        <v>0.004235</v>
       </c>
     </row>
     <row r="1202">
@@ -16043,7 +16043,7 @@
         <v>218</v>
       </c>
       <c r="C1202" t="n">
-        <v>0</v>
+        <v>0.004293</v>
       </c>
     </row>
     <row r="1203">
@@ -16056,7 +16056,7 @@
         <v>219</v>
       </c>
       <c r="C1203" t="n">
-        <v>0</v>
+        <v>0.004622</v>
       </c>
     </row>
     <row r="1204">
@@ -16069,7 +16069,7 @@
         <v>220</v>
       </c>
       <c r="C1204" t="n">
-        <v>0</v>
+        <v>0.004838</v>
       </c>
     </row>
     <row r="1205">
@@ -16082,7 +16082,7 @@
         <v>221</v>
       </c>
       <c r="C1205" t="n">
-        <v>0</v>
+        <v>0.004935</v>
       </c>
     </row>
     <row r="1206">
@@ -16095,7 +16095,7 @@
         <v>222</v>
       </c>
       <c r="C1206" t="n">
-        <v>0</v>
+        <v>0.005142</v>
       </c>
     </row>
     <row r="1207">
@@ -16108,7 +16108,7 @@
         <v>223</v>
       </c>
       <c r="C1207" t="n">
-        <v>0</v>
+        <v>0.005223</v>
       </c>
     </row>
     <row r="1208">
@@ -16121,7 +16121,7 @@
         <v>224</v>
       </c>
       <c r="C1208" t="n">
-        <v>0</v>
+        <v>0.00526</v>
       </c>
     </row>
     <row r="1209">
@@ -16134,7 +16134,7 @@
         <v>225</v>
       </c>
       <c r="C1209" t="n">
-        <v>0</v>
+        <v>0.005335</v>
       </c>
     </row>
     <row r="1210">
@@ -16147,7 +16147,7 @@
         <v>226</v>
       </c>
       <c r="C1210" t="n">
-        <v>0</v>
+        <v>0.005658</v>
       </c>
     </row>
     <row r="1211">
@@ -16160,7 +16160,7 @@
         <v>227</v>
       </c>
       <c r="C1211" t="n">
-        <v>0</v>
+        <v>0.005716</v>
       </c>
     </row>
     <row r="1212">
@@ -16173,7 +16173,7 @@
         <v>228</v>
       </c>
       <c r="C1212" t="n">
-        <v>0</v>
+        <v>0.005957</v>
       </c>
     </row>
     <row r="1213">
@@ -16186,7 +16186,7 @@
         <v>229</v>
       </c>
       <c r="C1213" t="n">
-        <v>0</v>
+        <v>0.007614</v>
       </c>
     </row>
     <row r="1214">
@@ -16199,7 +16199,7 @@
         <v>230</v>
       </c>
       <c r="C1214" t="n">
-        <v>0</v>
+        <v>0.008116</v>
       </c>
     </row>
     <row r="1215">
@@ -16212,7 +16212,7 @@
         <v>231</v>
       </c>
       <c r="C1215" t="n">
-        <v>0</v>
+        <v>0.008288999999999999</v>
       </c>
     </row>
     <row r="1216">
@@ -16225,7 +16225,7 @@
         <v>232</v>
       </c>
       <c r="C1216" t="n">
-        <v>0</v>
+        <v>0.008359</v>
       </c>
     </row>
     <row r="1217">
@@ -16238,7 +16238,7 @@
         <v>233</v>
       </c>
       <c r="C1217" t="n">
-        <v>0</v>
+        <v>0.00919</v>
       </c>
     </row>
     <row r="1218">
@@ -16251,7 +16251,7 @@
         <v>234</v>
       </c>
       <c r="C1218" t="n">
-        <v>0</v>
+        <v>0.009423000000000001</v>
       </c>
     </row>
     <row r="1219">
@@ -16264,7 +16264,7 @@
         <v>235</v>
       </c>
       <c r="C1219" t="n">
-        <v>0</v>
+        <v>0.009490999999999999</v>
       </c>
     </row>
     <row r="1220">
@@ -16277,7 +16277,7 @@
         <v>236</v>
       </c>
       <c r="C1220" t="n">
-        <v>0</v>
+        <v>0.009582</v>
       </c>
     </row>
     <row r="1221">
@@ -16290,7 +16290,7 @@
         <v>237</v>
       </c>
       <c r="C1221" t="n">
-        <v>0</v>
+        <v>0.009665</v>
       </c>
     </row>
     <row r="1222">
@@ -16303,7 +16303,7 @@
         <v>238</v>
       </c>
       <c r="C1222" t="n">
-        <v>0</v>
+        <v>0.009991</v>
       </c>
     </row>
     <row r="1223">
@@ -16316,7 +16316,7 @@
         <v>239</v>
       </c>
       <c r="C1223" t="n">
-        <v>0</v>
+        <v>0.010355</v>
       </c>
     </row>
     <row r="1224">
@@ -16329,7 +16329,7 @@
         <v>240</v>
       </c>
       <c r="C1224" t="n">
-        <v>0</v>
+        <v>0.010465</v>
       </c>
     </row>
     <row r="1225">
@@ -16342,7 +16342,7 @@
         <v>241</v>
       </c>
       <c r="C1225" t="n">
-        <v>0</v>
+        <v>0.010633</v>
       </c>
     </row>
     <row r="1226">
@@ -16355,7 +16355,7 @@
         <v>242</v>
       </c>
       <c r="C1226" t="n">
-        <v>0.000393</v>
+        <v>0.010726</v>
       </c>
     </row>
     <row r="1227">
@@ -16368,7 +16368,7 @@
         <v>243</v>
       </c>
       <c r="C1227" t="n">
-        <v>0.00044</v>
+        <v>0.010738</v>
       </c>
     </row>
     <row r="1228">
@@ -16381,7 +16381,7 @@
         <v>244</v>
       </c>
       <c r="C1228" t="n">
-        <v>0.00135</v>
+        <v>0.010919</v>
       </c>
     </row>
     <row r="1229">
@@ -16394,7 +16394,7 @@
         <v>245</v>
       </c>
       <c r="C1229" t="n">
-        <v>0.001558</v>
+        <v>0.011099</v>
       </c>
     </row>
     <row r="1230">
@@ -16407,7 +16407,7 @@
         <v>246</v>
       </c>
       <c r="C1230" t="n">
-        <v>0.00162</v>
+        <v>0.012096</v>
       </c>
     </row>
     <row r="1231">
@@ -16420,7 +16420,7 @@
         <v>247</v>
       </c>
       <c r="C1231" t="n">
-        <v>0.001657</v>
+        <v>0.012216</v>
       </c>
     </row>
     <row r="1232">
@@ -16433,7 +16433,7 @@
         <v>248</v>
       </c>
       <c r="C1232" t="n">
-        <v>0.001705</v>
+        <v>0.012946</v>
       </c>
     </row>
     <row r="1233">
@@ -16446,7 +16446,7 @@
         <v>249</v>
       </c>
       <c r="C1233" t="n">
-        <v>0.001811</v>
+        <v>0.013189</v>
       </c>
     </row>
     <row r="1234">
@@ -16459,7 +16459,7 @@
         <v>250</v>
       </c>
       <c r="C1234" t="n">
-        <v>0.001859</v>
+        <v>0.013261</v>
       </c>
     </row>
     <row r="1235">
@@ -16472,7 +16472,7 @@
         <v>251</v>
       </c>
       <c r="C1235" t="n">
-        <v>0.002103</v>
+        <v>0.013266</v>
       </c>
     </row>
     <row r="1236">
@@ -16485,7 +16485,7 @@
         <v>252</v>
       </c>
       <c r="C1236" t="n">
-        <v>0.002846</v>
+        <v>0.0141</v>
       </c>
     </row>
     <row r="1237">
@@ -16498,7 +16498,7 @@
         <v>253</v>
       </c>
       <c r="C1237" t="n">
-        <v>0.002868</v>
+        <v>0.014558</v>
       </c>
     </row>
     <row r="1238">
@@ -16511,7 +16511,7 @@
         <v>254</v>
       </c>
       <c r="C1238" t="n">
-        <v>0.002967</v>
+        <v>0.014561</v>
       </c>
     </row>
     <row r="1239">
@@ -16524,7 +16524,7 @@
         <v>255</v>
       </c>
       <c r="C1239" t="n">
-        <v>0.002982</v>
+        <v>0.015133</v>
       </c>
     </row>
     <row r="1240">
@@ -16537,7 +16537,7 @@
         <v>256</v>
       </c>
       <c r="C1240" t="n">
-        <v>0.003053</v>
+        <v>0.01525</v>
       </c>
     </row>
     <row r="1241">
@@ -16550,7 +16550,7 @@
         <v>257</v>
       </c>
       <c r="C1241" t="n">
-        <v>0.003273</v>
+        <v>0.015704</v>
       </c>
     </row>
     <row r="1242">
@@ -16563,7 +16563,7 @@
         <v>258</v>
       </c>
       <c r="C1242" t="n">
-        <v>0.003431</v>
+        <v>0.015829</v>
       </c>
     </row>
     <row r="1243">
@@ -16576,7 +16576,7 @@
         <v>259</v>
       </c>
       <c r="C1243" t="n">
-        <v>0.003935</v>
+        <v>0.015897</v>
       </c>
     </row>
     <row r="1244">
@@ -16589,7 +16589,7 @@
         <v>260</v>
       </c>
       <c r="C1244" t="n">
-        <v>0.004109</v>
+        <v>0.016176</v>
       </c>
     </row>
     <row r="1245">
@@ -16602,7 +16602,7 @@
         <v>261</v>
       </c>
       <c r="C1245" t="n">
-        <v>0.00415</v>
+        <v>0.016713</v>
       </c>
     </row>
     <row r="1246">
@@ -16615,7 +16615,7 @@
         <v>262</v>
       </c>
       <c r="C1246" t="n">
-        <v>0.004377</v>
+        <v>0.016898</v>
       </c>
     </row>
     <row r="1247">
@@ -16628,7 +16628,7 @@
         <v>263</v>
       </c>
       <c r="C1247" t="n">
-        <v>0.00464</v>
+        <v>0.017008</v>
       </c>
     </row>
     <row r="1248">
@@ -16641,7 +16641,7 @@
         <v>264</v>
       </c>
       <c r="C1248" t="n">
-        <v>0.004692</v>
+        <v>0.017627</v>
       </c>
     </row>
     <row r="1249">
@@ -16654,7 +16654,7 @@
         <v>265</v>
       </c>
       <c r="C1249" t="n">
-        <v>0.005028</v>
+        <v>0.017812</v>
       </c>
     </row>
     <row r="1250">
@@ -16667,7 +16667,7 @@
         <v>266</v>
       </c>
       <c r="C1250" t="n">
-        <v>0.005531</v>
+        <v>0.018</v>
       </c>
     </row>
     <row r="1251">
@@ -16680,7 +16680,7 @@
         <v>267</v>
       </c>
       <c r="C1251" t="n">
-        <v>0.005643</v>
+        <v>0.01838</v>
       </c>
     </row>
     <row r="1252">
@@ -16693,7 +16693,7 @@
         <v>268</v>
       </c>
       <c r="C1252" t="n">
-        <v>0.005893</v>
+        <v>0.018445</v>
       </c>
     </row>
     <row r="1253">
@@ -16706,7 +16706,7 @@
         <v>269</v>
       </c>
       <c r="C1253" t="n">
-        <v>0.006437</v>
+        <v>0.019131</v>
       </c>
     </row>
     <row r="1254">
@@ -16719,7 +16719,7 @@
         <v>270</v>
       </c>
       <c r="C1254" t="n">
-        <v>0.006614</v>
+        <v>0.019344</v>
       </c>
     </row>
     <row r="1255">
@@ -16732,7 +16732,7 @@
         <v>271</v>
       </c>
       <c r="C1255" t="n">
-        <v>0.006745</v>
+        <v>0.019568</v>
       </c>
     </row>
     <row r="1256">
@@ -16745,7 +16745,7 @@
         <v>272</v>
       </c>
       <c r="C1256" t="n">
-        <v>0.006791</v>
+        <v>0.020159</v>
       </c>
     </row>
     <row r="1257">
@@ -16758,7 +16758,7 @@
         <v>273</v>
       </c>
       <c r="C1257" t="n">
-        <v>0.00744</v>
+        <v>0.02063</v>
       </c>
     </row>
     <row r="1258">
@@ -16771,7 +16771,7 @@
         <v>274</v>
       </c>
       <c r="C1258" t="n">
-        <v>0.007479</v>
+        <v>0.020889</v>
       </c>
     </row>
     <row r="1259">
@@ -16784,7 +16784,7 @@
         <v>275</v>
       </c>
       <c r="C1259" t="n">
-        <v>0.007749</v>
+        <v>0.021096</v>
       </c>
     </row>
     <row r="1260">
@@ -16797,7 +16797,7 @@
         <v>276</v>
       </c>
       <c r="C1260" t="n">
-        <v>0.007804</v>
+        <v>0.021355</v>
       </c>
     </row>
     <row r="1261">
@@ -16810,7 +16810,7 @@
         <v>277</v>
       </c>
       <c r="C1261" t="n">
-        <v>0.00812</v>
+        <v>0.022045</v>
       </c>
     </row>
     <row r="1262">
@@ -16823,7 +16823,7 @@
         <v>278</v>
       </c>
       <c r="C1262" t="n">
-        <v>0.008144999999999999</v>
+        <v>0.0223</v>
       </c>
     </row>
     <row r="1263">
@@ -16836,7 +16836,7 @@
         <v>279</v>
       </c>
       <c r="C1263" t="n">
-        <v>0.008246</v>
+        <v>0.023224</v>
       </c>
     </row>
     <row r="1264">
@@ -16849,7 +16849,7 @@
         <v>280</v>
       </c>
       <c r="C1264" t="n">
-        <v>0.008370000000000001</v>
+        <v>0.02374</v>
       </c>
     </row>
     <row r="1265">
@@ -16862,7 +16862,7 @@
         <v>281</v>
       </c>
       <c r="C1265" t="n">
-        <v>0.008966</v>
+        <v>0.023828</v>
       </c>
     </row>
     <row r="1266">
@@ -16875,7 +16875,7 @@
         <v>282</v>
       </c>
       <c r="C1266" t="n">
-        <v>0.008971</v>
+        <v>0.024041</v>
       </c>
     </row>
     <row r="1267">
@@ -16888,7 +16888,7 @@
         <v>283</v>
       </c>
       <c r="C1267" t="n">
-        <v>0.009084999999999999</v>
+        <v>0.02419</v>
       </c>
     </row>
     <row r="1268">
@@ -16901,7 +16901,7 @@
         <v>284</v>
       </c>
       <c r="C1268" t="n">
-        <v>0.009087</v>
+        <v>0.024295</v>
       </c>
     </row>
     <row r="1269">
@@ -16914,7 +16914,7 @@
         <v>285</v>
       </c>
       <c r="C1269" t="n">
-        <v>0.009332999999999999</v>
+        <v>0.024468</v>
       </c>
     </row>
     <row r="1270">
@@ -16927,7 +16927,7 @@
         <v>286</v>
       </c>
       <c r="C1270" t="n">
-        <v>0.009395000000000001</v>
+        <v>0.024847</v>
       </c>
     </row>
     <row r="1271">
@@ -16940,7 +16940,7 @@
         <v>287</v>
       </c>
       <c r="C1271" t="n">
-        <v>0.009651</v>
+        <v>0.026529</v>
       </c>
     </row>
     <row r="1272">
@@ -16953,7 +16953,7 @@
         <v>288</v>
       </c>
       <c r="C1272" t="n">
-        <v>0.009663</v>
+        <v>0.026915</v>
       </c>
     </row>
     <row r="1273">
@@ -16966,7 +16966,7 @@
         <v>289</v>
       </c>
       <c r="C1273" t="n">
-        <v>0.00974</v>
+        <v>0.027084</v>
       </c>
     </row>
     <row r="1274">
@@ -16979,7 +16979,7 @@
         <v>290</v>
       </c>
       <c r="C1274" t="n">
-        <v>0.010226</v>
+        <v>0.02761</v>
       </c>
     </row>
     <row r="1275">
@@ -16992,7 +16992,7 @@
         <v>291</v>
       </c>
       <c r="C1275" t="n">
-        <v>0.010316</v>
+        <v>0.027777</v>
       </c>
     </row>
     <row r="1276">
@@ -17005,7 +17005,7 @@
         <v>292</v>
       </c>
       <c r="C1276" t="n">
-        <v>0.01043</v>
+        <v>0.02788</v>
       </c>
     </row>
     <row r="1277">
@@ -17018,7 +17018,7 @@
         <v>293</v>
       </c>
       <c r="C1277" t="n">
-        <v>0.010525</v>
+        <v>0.027927</v>
       </c>
     </row>
     <row r="1278">
@@ -17031,7 +17031,7 @@
         <v>294</v>
       </c>
       <c r="C1278" t="n">
-        <v>0.010611</v>
+        <v>0.028339</v>
       </c>
     </row>
     <row r="1279">
@@ -17044,7 +17044,7 @@
         <v>295</v>
       </c>
       <c r="C1279" t="n">
-        <v>0.010743</v>
+        <v>0.029373</v>
       </c>
     </row>
     <row r="1280">
@@ -17057,7 +17057,7 @@
         <v>296</v>
       </c>
       <c r="C1280" t="n">
-        <v>0.011307</v>
+        <v>0.029462</v>
       </c>
     </row>
     <row r="1281">
@@ -17070,7 +17070,7 @@
         <v>297</v>
       </c>
       <c r="C1281" t="n">
-        <v>0.01133</v>
+        <v>0.02992</v>
       </c>
     </row>
     <row r="1282">
@@ -17083,7 +17083,7 @@
         <v>298</v>
       </c>
       <c r="C1282" t="n">
-        <v>0.011563</v>
+        <v>0.030165</v>
       </c>
     </row>
     <row r="1283">
@@ -17096,7 +17096,7 @@
         <v>299</v>
       </c>
       <c r="C1283" t="n">
-        <v>0.011852</v>
+        <v>0.030918</v>
       </c>
     </row>
     <row r="1284">
@@ -17109,7 +17109,7 @@
         <v>300</v>
       </c>
       <c r="C1284" t="n">
-        <v>0.011856</v>
+        <v>0.030932</v>
       </c>
     </row>
     <row r="1285">
@@ -17122,7 +17122,7 @@
         <v>301</v>
       </c>
       <c r="C1285" t="n">
-        <v>0.011907</v>
+        <v>0.031097</v>
       </c>
     </row>
     <row r="1286">
@@ -17135,7 +17135,7 @@
         <v>302</v>
       </c>
       <c r="C1286" t="n">
-        <v>0.011971</v>
+        <v>0.031157</v>
       </c>
     </row>
     <row r="1287">
@@ -17148,7 +17148,7 @@
         <v>303</v>
       </c>
       <c r="C1287" t="n">
-        <v>0.011978</v>
+        <v>0.031333</v>
       </c>
     </row>
     <row r="1288">
@@ -17161,7 +17161,7 @@
         <v>304</v>
       </c>
       <c r="C1288" t="n">
-        <v>0.012377</v>
+        <v>0.031999</v>
       </c>
     </row>
     <row r="1289">
@@ -17174,7 +17174,7 @@
         <v>305</v>
       </c>
       <c r="C1289" t="n">
-        <v>0.012544</v>
+        <v>0.03205</v>
       </c>
     </row>
     <row r="1290">
@@ -17187,7 +17187,7 @@
         <v>306</v>
       </c>
       <c r="C1290" t="n">
-        <v>0.012732</v>
+        <v>0.032635</v>
       </c>
     </row>
     <row r="1291">
@@ -17200,7 +17200,7 @@
         <v>307</v>
       </c>
       <c r="C1291" t="n">
-        <v>0.012956</v>
+        <v>0.033001</v>
       </c>
     </row>
     <row r="1292">
@@ -17213,7 +17213,7 @@
         <v>308</v>
       </c>
       <c r="C1292" t="n">
-        <v>0.012976</v>
+        <v>0.033469</v>
       </c>
     </row>
     <row r="1293">
@@ -17226,7 +17226,7 @@
         <v>309</v>
       </c>
       <c r="C1293" t="n">
-        <v>0.01345</v>
+        <v>0.033845</v>
       </c>
     </row>
     <row r="1294">
@@ -17239,7 +17239,7 @@
         <v>310</v>
       </c>
       <c r="C1294" t="n">
-        <v>0.013549</v>
+        <v>0.033914</v>
       </c>
     </row>
     <row r="1295">
@@ -17252,7 +17252,7 @@
         <v>311</v>
       </c>
       <c r="C1295" t="n">
-        <v>0.013824</v>
+        <v>0.034753</v>
       </c>
     </row>
     <row r="1296">
@@ -17265,7 +17265,7 @@
         <v>312</v>
       </c>
       <c r="C1296" t="n">
-        <v>0.014014</v>
+        <v>0.034784</v>
       </c>
     </row>
     <row r="1297">
@@ -17278,7 +17278,7 @@
         <v>313</v>
       </c>
       <c r="C1297" t="n">
-        <v>0.01403</v>
+        <v>0.034794</v>
       </c>
     </row>
     <row r="1298">
@@ -17291,7 +17291,7 @@
         <v>314</v>
       </c>
       <c r="C1298" t="n">
-        <v>0.014148</v>
+        <v>0.035312</v>
       </c>
     </row>
     <row r="1299">
@@ -17304,7 +17304,7 @@
         <v>315</v>
       </c>
       <c r="C1299" t="n">
-        <v>0.014184</v>
+        <v>0.035795</v>
       </c>
     </row>
     <row r="1300">
@@ -17317,7 +17317,7 @@
         <v>316</v>
       </c>
       <c r="C1300" t="n">
-        <v>0.014446</v>
+        <v>0.03587</v>
       </c>
     </row>
     <row r="1301">
@@ -17330,7 +17330,7 @@
         <v>317</v>
       </c>
       <c r="C1301" t="n">
-        <v>0.014474</v>
+        <v>0.036294</v>
       </c>
     </row>
     <row r="1302">
@@ -17343,7 +17343,7 @@
         <v>318</v>
       </c>
       <c r="C1302" t="n">
-        <v>0.015235</v>
+        <v>0.036623</v>
       </c>
     </row>
     <row r="1303">
@@ -17356,7 +17356,7 @@
         <v>319</v>
       </c>
       <c r="C1303" t="n">
-        <v>0.015581</v>
+        <v>0.036695</v>
       </c>
     </row>
     <row r="1304">
@@ -17369,7 +17369,7 @@
         <v>320</v>
       </c>
       <c r="C1304" t="n">
-        <v>0.015958</v>
+        <v>0.037054</v>
       </c>
     </row>
     <row r="1305">
@@ -17382,7 +17382,7 @@
         <v>321</v>
       </c>
       <c r="C1305" t="n">
-        <v>0.016344</v>
+        <v>0.037247</v>
       </c>
     </row>
     <row r="1306">
@@ -17395,7 +17395,7 @@
         <v>322</v>
       </c>
       <c r="C1306" t="n">
-        <v>0.016434</v>
+        <v>0.037874</v>
       </c>
     </row>
     <row r="1307">
@@ -17408,7 +17408,7 @@
         <v>323</v>
       </c>
       <c r="C1307" t="n">
-        <v>0.016482</v>
+        <v>0.038695</v>
       </c>
     </row>
     <row r="1308">
@@ -17421,7 +17421,7 @@
         <v>324</v>
       </c>
       <c r="C1308" t="n">
-        <v>0.01685</v>
+        <v>0.038946</v>
       </c>
     </row>
     <row r="1309">
@@ -17434,7 +17434,7 @@
         <v>325</v>
       </c>
       <c r="C1309" t="n">
-        <v>0.017116</v>
+        <v>0.039079</v>
       </c>
     </row>
     <row r="1310">
@@ -17447,7 +17447,7 @@
         <v>326</v>
       </c>
       <c r="C1310" t="n">
-        <v>0.017131</v>
+        <v>0.039245</v>
       </c>
     </row>
     <row r="1311">
@@ -17460,7 +17460,7 @@
         <v>327</v>
       </c>
       <c r="C1311" t="n">
-        <v>0.017322</v>
+        <v>0.03951</v>
       </c>
     </row>
     <row r="1312">
@@ -17473,7 +17473,7 @@
         <v>328</v>
       </c>
       <c r="C1312" t="n">
-        <v>0.017365</v>
+        <v>0.039963</v>
       </c>
     </row>
     <row r="1313">
@@ -17486,7 +17486,7 @@
         <v>329</v>
       </c>
       <c r="C1313" t="n">
-        <v>0.01746</v>
+        <v>0.04026</v>
       </c>
     </row>
     <row r="1314">
@@ -17499,7 +17499,7 @@
         <v>330</v>
       </c>
       <c r="C1314" t="n">
-        <v>0.018011</v>
+        <v>0.040369</v>
       </c>
     </row>
     <row r="1315">
@@ -17512,7 +17512,7 @@
         <v>331</v>
       </c>
       <c r="C1315" t="n">
-        <v>0.018065</v>
+        <v>0.040411</v>
       </c>
     </row>
     <row r="1316">
@@ -17525,7 +17525,7 @@
         <v>332</v>
       </c>
       <c r="C1316" t="n">
-        <v>0.018516</v>
+        <v>0.040966</v>
       </c>
     </row>
     <row r="1317">
@@ -17538,7 +17538,7 @@
         <v>333</v>
       </c>
       <c r="C1317" t="n">
-        <v>0.018698</v>
+        <v>0.041062</v>
       </c>
     </row>
     <row r="1318">
@@ -17551,7 +17551,7 @@
         <v>334</v>
       </c>
       <c r="C1318" t="n">
-        <v>0.019385</v>
+        <v>0.041518</v>
       </c>
     </row>
     <row r="1319">
@@ -17564,7 +17564,7 @@
         <v>335</v>
       </c>
       <c r="C1319" t="n">
-        <v>0.019637</v>
+        <v>0.041572</v>
       </c>
     </row>
     <row r="1320">
@@ -17577,7 +17577,7 @@
         <v>336</v>
       </c>
       <c r="C1320" t="n">
-        <v>0.019862</v>
+        <v>0.041672</v>
       </c>
     </row>
     <row r="1321">
@@ -17590,7 +17590,7 @@
         <v>337</v>
       </c>
       <c r="C1321" t="n">
-        <v>0.019965</v>
+        <v>0.041706</v>
       </c>
     </row>
     <row r="1322">
@@ -17603,7 +17603,7 @@
         <v>338</v>
       </c>
       <c r="C1322" t="n">
-        <v>0.019973</v>
+        <v>0.041719</v>
       </c>
     </row>
     <row r="1323">
@@ -17616,7 +17616,7 @@
         <v>339</v>
       </c>
       <c r="C1323" t="n">
-        <v>0.020041</v>
+        <v>0.041981</v>
       </c>
     </row>
     <row r="1324">
@@ -17629,7 +17629,7 @@
         <v>340</v>
       </c>
       <c r="C1324" t="n">
-        <v>0.020489</v>
+        <v>0.041998</v>
       </c>
     </row>
     <row r="1325">
@@ -17642,7 +17642,7 @@
         <v>341</v>
       </c>
       <c r="C1325" t="n">
-        <v>0.02071</v>
+        <v>0.043166</v>
       </c>
     </row>
     <row r="1326">
@@ -17655,7 +17655,7 @@
         <v>342</v>
       </c>
       <c r="C1326" t="n">
-        <v>0.020961</v>
+        <v>0.04317</v>
       </c>
     </row>
     <row r="1327">
@@ -17668,7 +17668,7 @@
         <v>343</v>
       </c>
       <c r="C1327" t="n">
-        <v>0.021125</v>
+        <v>0.043922</v>
       </c>
     </row>
     <row r="1328">
@@ -17681,7 +17681,7 @@
         <v>344</v>
       </c>
       <c r="C1328" t="n">
-        <v>0.021326</v>
+        <v>0.044141</v>
       </c>
     </row>
     <row r="1329">
@@ -17694,7 +17694,7 @@
         <v>345</v>
       </c>
       <c r="C1329" t="n">
-        <v>0.02157</v>
+        <v>0.044241</v>
       </c>
     </row>
     <row r="1330">
@@ -17707,7 +17707,7 @@
         <v>346</v>
       </c>
       <c r="C1330" t="n">
-        <v>0.022123</v>
+        <v>0.044581</v>
       </c>
     </row>
     <row r="1331">
@@ -17720,7 +17720,7 @@
         <v>347</v>
       </c>
       <c r="C1331" t="n">
-        <v>0.022294</v>
+        <v>0.045171</v>
       </c>
     </row>
     <row r="1332">
@@ -17733,7 +17733,7 @@
         <v>348</v>
       </c>
       <c r="C1332" t="n">
-        <v>0.022312</v>
+        <v>0.045507</v>
       </c>
     </row>
     <row r="1333">
@@ -17746,7 +17746,7 @@
         <v>349</v>
       </c>
       <c r="C1333" t="n">
-        <v>0.022373</v>
+        <v>0.046032</v>
       </c>
     </row>
     <row r="1334">
@@ -17759,7 +17759,7 @@
         <v>350</v>
       </c>
       <c r="C1334" t="n">
-        <v>0.02263</v>
+        <v>0.046117</v>
       </c>
     </row>
     <row r="1335">
@@ -17772,7 +17772,7 @@
         <v>351</v>
       </c>
       <c r="C1335" t="n">
-        <v>0.022891</v>
+        <v>0.046458</v>
       </c>
     </row>
     <row r="1336">
@@ -17785,7 +17785,7 @@
         <v>352</v>
       </c>
       <c r="C1336" t="n">
-        <v>0.023474</v>
+        <v>0.046628</v>
       </c>
     </row>
     <row r="1337">
@@ -17798,7 +17798,7 @@
         <v>353</v>
       </c>
       <c r="C1337" t="n">
-        <v>0.023523</v>
+        <v>0.047062</v>
       </c>
     </row>
     <row r="1338">
@@ -17811,7 +17811,7 @@
         <v>354</v>
       </c>
       <c r="C1338" t="n">
-        <v>0.024075</v>
+        <v>0.047973</v>
       </c>
     </row>
     <row r="1339">
@@ -17824,7 +17824,7 @@
         <v>355</v>
       </c>
       <c r="C1339" t="n">
-        <v>0.024129</v>
+        <v>0.048098</v>
       </c>
     </row>
     <row r="1340">
@@ -17837,7 +17837,7 @@
         <v>356</v>
       </c>
       <c r="C1340" t="n">
-        <v>0.024456</v>
+        <v>0.048257</v>
       </c>
     </row>
     <row r="1341">
@@ -17850,7 +17850,7 @@
         <v>357</v>
       </c>
       <c r="C1341" t="n">
-        <v>0.024577</v>
+        <v>0.048698</v>
       </c>
     </row>
     <row r="1342">
@@ -17863,7 +17863,7 @@
         <v>358</v>
       </c>
       <c r="C1342" t="n">
-        <v>0.024631</v>
+        <v>0.04912</v>
       </c>
     </row>
     <row r="1343">
@@ -17876,7 +17876,7 @@
         <v>359</v>
       </c>
       <c r="C1343" t="n">
-        <v>0.024814</v>
+        <v>0.049338</v>
       </c>
     </row>
     <row r="1344">
@@ -17889,7 +17889,7 @@
         <v>360</v>
       </c>
       <c r="C1344" t="n">
-        <v>0.025036</v>
+        <v>0.049732</v>
       </c>
     </row>
     <row r="1345">
@@ -17902,7 +17902,7 @@
         <v>361</v>
       </c>
       <c r="C1345" t="n">
-        <v>0.025244</v>
+        <v>0.049752</v>
       </c>
     </row>
     <row r="1346">
@@ -17915,7 +17915,7 @@
         <v>362</v>
       </c>
       <c r="C1346" t="n">
-        <v>0.025315</v>
+        <v>0.050294</v>
       </c>
     </row>
     <row r="1347">
@@ -17928,7 +17928,7 @@
         <v>363</v>
       </c>
       <c r="C1347" t="n">
-        <v>0.025637</v>
+        <v>0.050666</v>
       </c>
     </row>
     <row r="1348">
@@ -17941,7 +17941,7 @@
         <v>364</v>
       </c>
       <c r="C1348" t="n">
-        <v>0.02636</v>
+        <v>0.050755</v>
       </c>
     </row>
     <row r="1349">
@@ -17954,7 +17954,7 @@
         <v>365</v>
       </c>
       <c r="C1349" t="n">
-        <v>0.0264</v>
+        <v>0.050789</v>
       </c>
     </row>
     <row r="1350">
@@ -17967,7 +17967,7 @@
         <v>366</v>
       </c>
       <c r="C1350" t="n">
-        <v>0.026462</v>
+        <v>0.05118</v>
       </c>
     </row>
     <row r="1351">
@@ -17980,7 +17980,7 @@
         <v>367</v>
       </c>
       <c r="C1351" t="n">
-        <v>0.026513</v>
+        <v>0.051607</v>
       </c>
     </row>
     <row r="1352">
@@ -17993,7 +17993,7 @@
         <v>368</v>
       </c>
       <c r="C1352" t="n">
-        <v>0.027366</v>
+        <v>0.051764</v>
       </c>
     </row>
     <row r="1353">
@@ -18006,7 +18006,7 @@
         <v>369</v>
       </c>
       <c r="C1353" t="n">
-        <v>0.027372</v>
+        <v>0.052001</v>
       </c>
     </row>
     <row r="1354">
@@ -18019,7 +18019,7 @@
         <v>370</v>
       </c>
       <c r="C1354" t="n">
-        <v>0.028877</v>
+        <v>0.052315</v>
       </c>
     </row>
     <row r="1355">
@@ -18032,7 +18032,7 @@
         <v>371</v>
       </c>
       <c r="C1355" t="n">
-        <v>0.029087</v>
+        <v>0.053462</v>
       </c>
     </row>
     <row r="1356">
@@ -18045,7 +18045,7 @@
         <v>372</v>
       </c>
       <c r="C1356" t="n">
-        <v>0.029422</v>
+        <v>0.056411</v>
       </c>
     </row>
     <row r="1357">
@@ -18058,7 +18058,7 @@
         <v>373</v>
       </c>
       <c r="C1357" t="n">
-        <v>0.030342</v>
+        <v>0.056792</v>
       </c>
     </row>
     <row r="1358">
@@ -18071,7 +18071,7 @@
         <v>374</v>
       </c>
       <c r="C1358" t="n">
-        <v>0.030389</v>
+        <v>0.057817</v>
       </c>
     </row>
     <row r="1359">
@@ -18084,7 +18084,7 @@
         <v>375</v>
       </c>
       <c r="C1359" t="n">
-        <v>0.030649</v>
+        <v>0.058325</v>
       </c>
     </row>
     <row r="1360">
@@ -18097,7 +18097,7 @@
         <v>376</v>
       </c>
       <c r="C1360" t="n">
-        <v>0.030657</v>
+        <v>0.058695</v>
       </c>
     </row>
     <row r="1361">
@@ -18110,7 +18110,7 @@
         <v>377</v>
       </c>
       <c r="C1361" t="n">
-        <v>0.031119</v>
+        <v>0.059187</v>
       </c>
     </row>
     <row r="1362">
@@ -18123,7 +18123,7 @@
         <v>378</v>
       </c>
       <c r="C1362" t="n">
-        <v>0.031472</v>
+        <v>0.059331</v>
       </c>
     </row>
     <row r="1363">
@@ -18136,7 +18136,7 @@
         <v>379</v>
       </c>
       <c r="C1363" t="n">
-        <v>0.031585</v>
+        <v>0.05979</v>
       </c>
     </row>
     <row r="1364">
@@ -18149,7 +18149,7 @@
         <v>380</v>
       </c>
       <c r="C1364" t="n">
-        <v>0.031861</v>
+        <v>0.060013</v>
       </c>
     </row>
     <row r="1365">
@@ -18162,7 +18162,7 @@
         <v>381</v>
       </c>
       <c r="C1365" t="n">
-        <v>0.032011</v>
+        <v>0.060348</v>
       </c>
     </row>
     <row r="1366">
@@ -18175,7 +18175,7 @@
         <v>382</v>
       </c>
       <c r="C1366" t="n">
-        <v>0.032048</v>
+        <v>0.060631</v>
       </c>
     </row>
     <row r="1367">
@@ -18188,7 +18188,7 @@
         <v>383</v>
       </c>
       <c r="C1367" t="n">
-        <v>0.03237</v>
+        <v>0.061006</v>
       </c>
     </row>
     <row r="1368">
@@ -18201,7 +18201,7 @@
         <v>384</v>
       </c>
       <c r="C1368" t="n">
-        <v>0.0325</v>
+        <v>0.061083</v>
       </c>
     </row>
     <row r="1369">
@@ -18214,7 +18214,7 @@
         <v>385</v>
       </c>
       <c r="C1369" t="n">
-        <v>0.032663</v>
+        <v>0.061189</v>
       </c>
     </row>
     <row r="1370">
@@ -18227,7 +18227,7 @@
         <v>386</v>
       </c>
       <c r="C1370" t="n">
-        <v>0.033538</v>
+        <v>0.061637</v>
       </c>
     </row>
     <row r="1371">
@@ -18240,7 +18240,7 @@
         <v>387</v>
       </c>
       <c r="C1371" t="n">
-        <v>0.034112</v>
+        <v>0.062053</v>
       </c>
     </row>
     <row r="1372">
@@ -18253,7 +18253,7 @@
         <v>388</v>
       </c>
       <c r="C1372" t="n">
-        <v>0.034451</v>
+        <v>0.063892</v>
       </c>
     </row>
     <row r="1373">
@@ -18266,7 +18266,7 @@
         <v>389</v>
       </c>
       <c r="C1373" t="n">
-        <v>0.03469</v>
+        <v>0.064322</v>
       </c>
     </row>
     <row r="1374">
@@ -18279,7 +18279,7 @@
         <v>390</v>
       </c>
       <c r="C1374" t="n">
-        <v>0.03486</v>
+        <v>0.064378</v>
       </c>
     </row>
     <row r="1375">
@@ -18292,7 +18292,7 @@
         <v>391</v>
       </c>
       <c r="C1375" t="n">
-        <v>0.034884</v>
+        <v>0.065635</v>
       </c>
     </row>
     <row r="1376">
@@ -18305,7 +18305,7 @@
         <v>392</v>
       </c>
       <c r="C1376" t="n">
-        <v>0.034923</v>
+        <v>0.06615799999999999</v>
       </c>
     </row>
     <row r="1377">
@@ -18318,7 +18318,7 @@
         <v>393</v>
       </c>
       <c r="C1377" t="n">
-        <v>0.035103</v>
+        <v>0.06619</v>
       </c>
     </row>
     <row r="1378">
@@ -18331,7 +18331,7 @@
         <v>394</v>
       </c>
       <c r="C1378" t="n">
-        <v>0.035483</v>
+        <v>0.066942</v>
       </c>
     </row>
     <row r="1379">
@@ -18344,7 +18344,7 @@
         <v>395</v>
       </c>
       <c r="C1379" t="n">
-        <v>0.035882</v>
+        <v>0.067576</v>
       </c>
     </row>
     <row r="1380">
@@ -18357,7 +18357,7 @@
         <v>396</v>
       </c>
       <c r="C1380" t="n">
-        <v>0.036042</v>
+        <v>0.067578</v>
       </c>
     </row>
     <row r="1381">
@@ -18370,7 +18370,7 @@
         <v>397</v>
       </c>
       <c r="C1381" t="n">
-        <v>0.036211</v>
+        <v>0.068787</v>
       </c>
     </row>
     <row r="1382">
@@ -18383,7 +18383,7 @@
         <v>398</v>
       </c>
       <c r="C1382" t="n">
-        <v>0.036643</v>
+        <v>0.06908499999999999</v>
       </c>
     </row>
     <row r="1383">
@@ -18396,7 +18396,7 @@
         <v>399</v>
       </c>
       <c r="C1383" t="n">
-        <v>0.036678</v>
+        <v>0.06932199999999999</v>
       </c>
     </row>
     <row r="1384">
@@ -18409,7 +18409,7 @@
         <v>400</v>
       </c>
       <c r="C1384" t="n">
-        <v>0.036944</v>
+        <v>0.070322</v>
       </c>
     </row>
     <row r="1385">
@@ -18422,7 +18422,7 @@
         <v>401</v>
       </c>
       <c r="C1385" t="n">
-        <v>0.037073</v>
+        <v>0.07051200000000001</v>
       </c>
     </row>
     <row r="1386">
@@ -18435,7 +18435,7 @@
         <v>402</v>
       </c>
       <c r="C1386" t="n">
-        <v>0.037191</v>
+        <v>0.07052600000000001</v>
       </c>
     </row>
     <row r="1387">
@@ -18448,7 +18448,7 @@
         <v>403</v>
       </c>
       <c r="C1387" t="n">
-        <v>0.037316</v>
+        <v>0.070677</v>
       </c>
     </row>
     <row r="1388">
@@ -18461,7 +18461,7 @@
         <v>404</v>
       </c>
       <c r="C1388" t="n">
-        <v>0.037747</v>
+        <v>0.07098500000000001</v>
       </c>
     </row>
     <row r="1389">
@@ -18474,7 +18474,7 @@
         <v>405</v>
       </c>
       <c r="C1389" t="n">
-        <v>0.03842</v>
+        <v>0.071005</v>
       </c>
     </row>
     <row r="1390">
@@ -18487,7 +18487,7 @@
         <v>406</v>
       </c>
       <c r="C1390" t="n">
-        <v>0.038714</v>
+        <v>0.07122100000000001</v>
       </c>
     </row>
     <row r="1391">
@@ -18500,7 +18500,7 @@
         <v>407</v>
       </c>
       <c r="C1391" t="n">
-        <v>0.03899</v>
+        <v>0.071418</v>
       </c>
     </row>
     <row r="1392">
@@ -18513,7 +18513,7 @@
         <v>408</v>
       </c>
       <c r="C1392" t="n">
-        <v>0.039065</v>
+        <v>0.071488</v>
       </c>
     </row>
     <row r="1393">
@@ -18526,7 +18526,7 @@
         <v>409</v>
       </c>
       <c r="C1393" t="n">
-        <v>0.039169</v>
+        <v>0.0718</v>
       </c>
     </row>
     <row r="1394">
@@ -18539,7 +18539,7 @@
         <v>410</v>
       </c>
       <c r="C1394" t="n">
-        <v>0.039785</v>
+        <v>0.072379</v>
       </c>
     </row>
     <row r="1395">
@@ -18552,7 +18552,7 @@
         <v>411</v>
       </c>
       <c r="C1395" t="n">
-        <v>0.039804</v>
+        <v>0.07272099999999999</v>
       </c>
     </row>
     <row r="1396">
@@ -18565,7 +18565,7 @@
         <v>412</v>
       </c>
       <c r="C1396" t="n">
-        <v>0.039871</v>
+        <v>0.07281</v>
       </c>
     </row>
     <row r="1397">
@@ -18578,7 +18578,7 @@
         <v>413</v>
       </c>
       <c r="C1397" t="n">
-        <v>0.041009</v>
+        <v>0.07338600000000001</v>
       </c>
     </row>
     <row r="1398">
@@ -18591,7 +18591,7 @@
         <v>414</v>
       </c>
       <c r="C1398" t="n">
-        <v>0.041599</v>
+        <v>0.073932</v>
       </c>
     </row>
     <row r="1399">
@@ -18604,7 +18604,7 @@
         <v>415</v>
       </c>
       <c r="C1399" t="n">
-        <v>0.042098</v>
+        <v>0.077901</v>
       </c>
     </row>
     <row r="1400">
@@ -18617,7 +18617,7 @@
         <v>416</v>
       </c>
       <c r="C1400" t="n">
-        <v>0.04216</v>
+        <v>0.07801900000000001</v>
       </c>
     </row>
     <row r="1401">
@@ -18630,7 +18630,7 @@
         <v>417</v>
       </c>
       <c r="C1401" t="n">
-        <v>0.042463</v>
+        <v>0.079314</v>
       </c>
     </row>
     <row r="1402">
@@ -18643,7 +18643,7 @@
         <v>418</v>
       </c>
       <c r="C1402" t="n">
-        <v>0.044151</v>
+        <v>0.079777</v>
       </c>
     </row>
     <row r="1403">
@@ -18656,7 +18656,7 @@
         <v>419</v>
       </c>
       <c r="C1403" t="n">
-        <v>0.044173</v>
+        <v>0.081527</v>
       </c>
     </row>
     <row r="1404">
@@ -18669,7 +18669,7 @@
         <v>420</v>
       </c>
       <c r="C1404" t="n">
-        <v>0.044266</v>
+        <v>0.08204400000000001</v>
       </c>
     </row>
     <row r="1405">
@@ -18682,7 +18682,7 @@
         <v>421</v>
       </c>
       <c r="C1405" t="n">
-        <v>0.044391</v>
+        <v>0.082374</v>
       </c>
     </row>
     <row r="1406">
@@ -18695,7 +18695,7 @@
         <v>422</v>
       </c>
       <c r="C1406" t="n">
-        <v>0.045406</v>
+        <v>0.08261499999999999</v>
       </c>
     </row>
     <row r="1407">
@@ -18708,7 +18708,7 @@
         <v>423</v>
       </c>
       <c r="C1407" t="n">
-        <v>0.045657</v>
+        <v>0.083041</v>
       </c>
     </row>
     <row r="1408">
@@ -18721,7 +18721,7 @@
         <v>424</v>
       </c>
       <c r="C1408" t="n">
-        <v>0.045979</v>
+        <v>0.083339</v>
       </c>
     </row>
     <row r="1409">
@@ -18734,7 +18734,7 @@
         <v>425</v>
       </c>
       <c r="C1409" t="n">
-        <v>0.047484</v>
+        <v>0.08491899999999999</v>
       </c>
     </row>
     <row r="1410">
@@ -18747,7 +18747,7 @@
         <v>426</v>
       </c>
       <c r="C1410" t="n">
-        <v>0.048606</v>
+        <v>0.085797</v>
       </c>
     </row>
     <row r="1411">
@@ -18760,7 +18760,7 @@
         <v>427</v>
       </c>
       <c r="C1411" t="n">
-        <v>0.048925</v>
+        <v>0.088114</v>
       </c>
     </row>
     <row r="1412">
@@ -18773,7 +18773,7 @@
         <v>428</v>
       </c>
       <c r="C1412" t="n">
-        <v>0.04895</v>
+        <v>0.08845799999999999</v>
       </c>
     </row>
     <row r="1413">
@@ -18786,7 +18786,7 @@
         <v>429</v>
       </c>
       <c r="C1413" t="n">
-        <v>0.048967</v>
+        <v>0.08862100000000001</v>
       </c>
     </row>
     <row r="1414">
@@ -18799,7 +18799,7 @@
         <v>430</v>
       </c>
       <c r="C1414" t="n">
-        <v>0.049776</v>
+        <v>0.088813</v>
       </c>
     </row>
     <row r="1415">
@@ -18812,7 +18812,7 @@
         <v>431</v>
       </c>
       <c r="C1415" t="n">
-        <v>0.05023</v>
+        <v>0.09148299999999999</v>
       </c>
     </row>
     <row r="1416">
@@ -18825,7 +18825,7 @@
         <v>432</v>
       </c>
       <c r="C1416" t="n">
-        <v>0.051482</v>
+        <v>0.091712</v>
       </c>
     </row>
     <row r="1417">
@@ -18838,7 +18838,7 @@
         <v>433</v>
       </c>
       <c r="C1417" t="n">
-        <v>0.052844</v>
+        <v>0.09267599999999999</v>
       </c>
     </row>
     <row r="1418">
@@ -18851,7 +18851,7 @@
         <v>434</v>
       </c>
       <c r="C1418" t="n">
-        <v>0.05306</v>
+        <v>0.09284199999999999</v>
       </c>
     </row>
     <row r="1419">
@@ -18864,7 +18864,7 @@
         <v>435</v>
       </c>
       <c r="C1419" t="n">
-        <v>0.053383</v>
+        <v>0.09343899999999999</v>
       </c>
     </row>
     <row r="1420">
@@ -18877,7 +18877,7 @@
         <v>436</v>
       </c>
       <c r="C1420" t="n">
-        <v>0.053454</v>
+        <v>0.095429</v>
       </c>
     </row>
     <row r="1421">
@@ -18890,7 +18890,7 @@
         <v>437</v>
       </c>
       <c r="C1421" t="n">
-        <v>0.054234</v>
+        <v>0.096276</v>
       </c>
     </row>
     <row r="1422">
@@ -18903,7 +18903,7 @@
         <v>438</v>
       </c>
       <c r="C1422" t="n">
-        <v>0.05585</v>
+        <v>0.098773</v>
       </c>
     </row>
     <row r="1423">
@@ -18916,7 +18916,7 @@
         <v>439</v>
       </c>
       <c r="C1423" t="n">
-        <v>0.05665</v>
+        <v>0.099407</v>
       </c>
     </row>
     <row r="1424">
@@ -18929,7 +18929,7 @@
         <v>440</v>
       </c>
       <c r="C1424" t="n">
-        <v>0.056676</v>
+        <v>0.099714</v>
       </c>
     </row>
     <row r="1425">
@@ -18942,7 +18942,7 @@
         <v>441</v>
       </c>
       <c r="C1425" t="n">
-        <v>0.057916</v>
+        <v>0.102482</v>
       </c>
     </row>
     <row r="1426">
@@ -18955,7 +18955,7 @@
         <v>442</v>
       </c>
       <c r="C1426" t="n">
-        <v>0.058528</v>
+        <v>0.104156</v>
       </c>
     </row>
     <row r="1427">
@@ -18968,7 +18968,7 @@
         <v>443</v>
       </c>
       <c r="C1427" t="n">
-        <v>0.058708</v>
+        <v>0.105221</v>
       </c>
     </row>
     <row r="1428">
@@ -18981,7 +18981,7 @@
         <v>444</v>
       </c>
       <c r="C1428" t="n">
-        <v>0.059462</v>
+        <v>0.107647</v>
       </c>
     </row>
     <row r="1429">
@@ -18994,7 +18994,7 @@
         <v>445</v>
       </c>
       <c r="C1429" t="n">
-        <v>0.060848</v>
+        <v>0.11135</v>
       </c>
     </row>
     <row r="1430">
@@ -19007,7 +19007,7 @@
         <v>446</v>
       </c>
       <c r="C1430" t="n">
-        <v>0.061981</v>
+        <v>0.114467</v>
       </c>
     </row>
     <row r="1431">
@@ -19020,7 +19020,7 @@
         <v>447</v>
       </c>
       <c r="C1431" t="n">
-        <v>0.062293</v>
+        <v>0.116468</v>
       </c>
     </row>
     <row r="1432">
@@ -19033,7 +19033,7 @@
         <v>448</v>
       </c>
       <c r="C1432" t="n">
-        <v>0.06237</v>
+        <v>0.116954</v>
       </c>
     </row>
     <row r="1433">
@@ -19046,7 +19046,7 @@
         <v>449</v>
       </c>
       <c r="C1433" t="n">
-        <v>0.062976</v>
+        <v>0.119674</v>
       </c>
     </row>
     <row r="1434">
@@ -19059,7 +19059,7 @@
         <v>450</v>
       </c>
       <c r="C1434" t="n">
-        <v>0.06328</v>
+        <v>0.11989</v>
       </c>
     </row>
     <row r="1435">
@@ -19072,7 +19072,7 @@
         <v>451</v>
       </c>
       <c r="C1435" t="n">
-        <v>0.06376999999999999</v>
+        <v>0.120121</v>
       </c>
     </row>
     <row r="1436">
@@ -19085,7 +19085,7 @@
         <v>452</v>
       </c>
       <c r="C1436" t="n">
-        <v>0.064015</v>
+        <v>0.120397</v>
       </c>
     </row>
     <row r="1437">
@@ -19098,7 +19098,7 @@
         <v>453</v>
       </c>
       <c r="C1437" t="n">
-        <v>0.064793</v>
+        <v>0.120671</v>
       </c>
     </row>
     <row r="1438">
@@ -19111,7 +19111,7 @@
         <v>454</v>
       </c>
       <c r="C1438" t="n">
-        <v>0.06579500000000001</v>
+        <v>0.123725</v>
       </c>
     </row>
     <row r="1439">
@@ -19124,7 +19124,7 @@
         <v>455</v>
       </c>
       <c r="C1439" t="n">
-        <v>0.06751600000000001</v>
+        <v>0.129178</v>
       </c>
     </row>
     <row r="1440">
@@ -19137,7 +19137,7 @@
         <v>456</v>
       </c>
       <c r="C1440" t="n">
-        <v>0.067647</v>
+        <v>0.129973</v>
       </c>
     </row>
     <row r="1441">
@@ -19150,7 +19150,7 @@
         <v>457</v>
       </c>
       <c r="C1441" t="n">
-        <v>0.06846099999999999</v>
+        <v>0.130881</v>
       </c>
     </row>
     <row r="1442">
@@ -19163,7 +19163,7 @@
         <v>458</v>
       </c>
       <c r="C1442" t="n">
-        <v>0.07009700000000001</v>
+        <v>0.13106</v>
       </c>
     </row>
     <row r="1443">
@@ -19176,7 +19176,7 @@
         <v>459</v>
       </c>
       <c r="C1443" t="n">
-        <v>0.072502</v>
+        <v>0.132913</v>
       </c>
     </row>
     <row r="1444">
@@ -19189,7 +19189,7 @@
         <v>460</v>
       </c>
       <c r="C1444" t="n">
-        <v>0.073514</v>
+        <v>0.133947</v>
       </c>
     </row>
     <row r="1445">
@@ -19202,7 +19202,7 @@
         <v>461</v>
       </c>
       <c r="C1445" t="n">
-        <v>0.076013</v>
+        <v>0.135054</v>
       </c>
     </row>
     <row r="1446">
@@ -19215,7 +19215,7 @@
         <v>462</v>
       </c>
       <c r="C1446" t="n">
-        <v>0.078112</v>
+        <v>0.135826</v>
       </c>
     </row>
     <row r="1447">
@@ -19228,7 +19228,7 @@
         <v>463</v>
       </c>
       <c r="C1447" t="n">
-        <v>0.079748</v>
+        <v>0.138934</v>
       </c>
     </row>
     <row r="1448">
@@ -19241,7 +19241,7 @@
         <v>464</v>
       </c>
       <c r="C1448" t="n">
-        <v>0.086088</v>
+        <v>0.145226</v>
       </c>
     </row>
     <row r="1449">
@@ -19254,7 +19254,7 @@
         <v>465</v>
       </c>
       <c r="C1449" t="n">
-        <v>0.088157</v>
+        <v>0.148376</v>
       </c>
     </row>
     <row r="1450">
@@ -19267,7 +19267,7 @@
         <v>466</v>
       </c>
       <c r="C1450" t="n">
-        <v>0.08956699999999999</v>
+        <v>0.149564</v>
       </c>
     </row>
     <row r="1451">
@@ -19280,7 +19280,7 @@
         <v>467</v>
       </c>
       <c r="C1451" t="n">
-        <v>0.09303599999999999</v>
+        <v>0.15277</v>
       </c>
     </row>
     <row r="1452">
@@ -19293,7 +19293,7 @@
         <v>468</v>
       </c>
       <c r="C1452" t="n">
-        <v>0.094985</v>
+        <v>0.154739</v>
       </c>
     </row>
     <row r="1453">
@@ -19306,7 +19306,7 @@
         <v>469</v>
       </c>
       <c r="C1453" t="n">
-        <v>0.097107</v>
+        <v>0.157185</v>
       </c>
     </row>
     <row r="1454">
@@ -19319,7 +19319,7 @@
         <v>470</v>
       </c>
       <c r="C1454" t="n">
-        <v>0.097742</v>
+        <v>0.17296</v>
       </c>
     </row>
     <row r="1455">
@@ -19332,7 +19332,7 @@
         <v>471</v>
       </c>
       <c r="C1455" t="n">
-        <v>0.105341</v>
+        <v>0.174888</v>
       </c>
     </row>
     <row r="1456">
@@ -19345,7 +19345,7 @@
         <v>472</v>
       </c>
       <c r="C1456" t="n">
-        <v>0.109044</v>
+        <v>0.177038</v>
       </c>
     </row>
     <row r="1457">
@@ -19358,7 +19358,7 @@
         <v>473</v>
       </c>
       <c r="C1457" t="n">
-        <v>0.109588</v>
+        <v>0.177101</v>
       </c>
     </row>
     <row r="1458">
@@ -19371,7 +19371,7 @@
         <v>474</v>
       </c>
       <c r="C1458" t="n">
-        <v>0.110202</v>
+        <v>0.177957</v>
       </c>
     </row>
     <row r="1459">
@@ -19384,7 +19384,7 @@
         <v>475</v>
       </c>
       <c r="C1459" t="n">
-        <v>0.112577</v>
+        <v>0.184125</v>
       </c>
     </row>
     <row r="1460">
@@ -19397,7 +19397,7 @@
         <v>476</v>
       </c>
       <c r="C1460" t="n">
-        <v>0.117432</v>
+        <v>0.199754</v>
       </c>
     </row>
     <row r="1461">
@@ -19410,7 +19410,7 @@
         <v>477</v>
       </c>
       <c r="C1461" t="n">
-        <v>0.12429</v>
+        <v>0.213575</v>
       </c>
     </row>
     <row r="1462">
@@ -19423,7 +19423,7 @@
         <v>478</v>
       </c>
       <c r="C1462" t="n">
-        <v>0.139334</v>
+        <v>0.238671</v>
       </c>
     </row>
     <row r="1463">
@@ -19436,7 +19436,7 @@
         <v>479</v>
       </c>
       <c r="C1463" t="n">
-        <v>0.142558</v>
+        <v>0.240463</v>
       </c>
     </row>
     <row r="1464">
@@ -19449,7 +19449,7 @@
         <v>480</v>
       </c>
       <c r="C1464" t="n">
-        <v>0.146697</v>
+        <v>0.259969</v>
       </c>
     </row>
     <row r="1465">
@@ -19462,7 +19462,7 @@
         <v>481</v>
       </c>
       <c r="C1465" t="n">
-        <v>0.148531</v>
+        <v>0.293388</v>
       </c>
     </row>
     <row r="1466">
@@ -19475,7 +19475,7 @@
         <v>482</v>
       </c>
       <c r="C1466" t="n">
-        <v>0.150934</v>
+        <v>0.310629</v>
       </c>
     </row>
     <row r="1467">
@@ -19488,7 +19488,7 @@
         <v>483</v>
       </c>
       <c r="C1467" t="n">
-        <v>0.153026</v>
+        <v>0.329245</v>
       </c>
     </row>
     <row r="1468">
@@ -19501,7 +19501,7 @@
         <v>484</v>
       </c>
       <c r="C1468" t="n">
-        <v>0.173811</v>
+        <v>0.355835</v>
       </c>
     </row>
     <row r="1469">
@@ -19514,7 +19514,7 @@
         <v>485</v>
       </c>
       <c r="C1469" t="n">
-        <v>0.179284</v>
+        <v>0.38967</v>
       </c>
     </row>
     <row r="1470">
@@ -19527,7 +19527,7 @@
         <v>486</v>
       </c>
       <c r="C1470" t="n">
-        <v>0.220725</v>
+        <v>0.402404</v>
       </c>
     </row>
     <row r="1471">
@@ -19540,7 +19540,7 @@
         <v>487</v>
       </c>
       <c r="C1471" t="n">
-        <v>0.281018</v>
+        <v>0.524787</v>
       </c>
     </row>
     <row r="1472">
@@ -19553,7 +19553,7 @@
         <v>488</v>
       </c>
       <c r="C1472" t="n">
-        <v>0.321817</v>
+        <v>0.668428</v>
       </c>
     </row>
     <row r="1473">
@@ -19566,7 +19566,7 @@
         <v>489</v>
       </c>
       <c r="C1473" t="n">
-        <v>0.354039</v>
+        <v>0.9386060000000001</v>
       </c>
     </row>
     <row r="1474">
@@ -19579,7 +19579,7 @@
         <v>490</v>
       </c>
       <c r="C1474" t="n">
-        <v>0.520578</v>
+        <v>0.948939</v>
       </c>
     </row>
   </sheetData>
